--- a/Versão5/AMBI/Ontologia_AMBIENTES.xlsx
+++ b/Versão5/AMBI/Ontologia_AMBIENTES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\AMBI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EEE240-A046-4E8B-938D-39B1B5AE0981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15491EAA-8657-460C-8A5A-27B51FF17C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4098" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4307" uniqueCount="733">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -1580,9 +1580,6 @@
     <t>tipo.revit</t>
   </si>
   <si>
-    <t>identificador</t>
-  </si>
-  <si>
     <t>"Nome da familia Room Tag usada em Revit"</t>
   </si>
   <si>
@@ -2283,6 +2280,18 @@
   </si>
   <si>
     <t>"[ IfcSpace ]"</t>
+  </si>
+  <si>
+    <t>Elemento.01</t>
+  </si>
+  <si>
+    <t>ponto.xyz</t>
+  </si>
+  <si>
+    <t>"[ 10.0 29.0 0.0 ]"</t>
+  </si>
+  <si>
+    <t>identificador.ifc</t>
   </si>
 </sst>
 </file>
@@ -2865,14 +2874,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2900,6 +2901,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -3059,14 +3068,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3094,6 +3095,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -3994,7 +4003,7 @@
       </c>
       <c r="B18" s="22">
         <f ca="1">NOW()</f>
-        <v>46144.391255671297</v>
+        <v>46152.487211111111</v>
       </c>
       <c r="C18" s="55" t="s">
         <v>283</v>
@@ -4217,7 +4226,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C2" s="39" t="s">
         <v>334</v>
@@ -4226,10 +4235,10 @@
         <v>333</v>
       </c>
       <c r="E2" s="38" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F2" s="39" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G2" s="40" t="s">
         <v>10</v>
@@ -4263,7 +4272,7 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="42" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="Q2" s="42" t="str">
         <f>_xlfn.TRANSLATE(P2,"pt","es")</f>
@@ -4310,7 +4319,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C3" s="39" t="s">
         <v>334</v>
@@ -4319,10 +4328,10 @@
         <v>333</v>
       </c>
       <c r="E3" s="38" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F3" s="39" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="G3" s="40" t="s">
         <v>10</v>
@@ -4356,7 +4365,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="42" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="Q3" s="42" t="str">
         <f t="shared" ref="Q3:Q7" si="4">_xlfn.TRANSLATE(P3,"pt","es")</f>
@@ -4403,7 +4412,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C4" s="39" t="s">
         <v>334</v>
@@ -4412,10 +4421,10 @@
         <v>333</v>
       </c>
       <c r="E4" s="38" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F4" s="39" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="G4" s="40" t="s">
         <v>10</v>
@@ -4449,7 +4458,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="42" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="Q4" s="42" t="str">
         <f t="shared" si="4"/>
@@ -4496,7 +4505,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C5" s="39" t="s">
         <v>334</v>
@@ -4505,10 +4514,10 @@
         <v>333</v>
       </c>
       <c r="E5" s="38" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F5" s="39" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="G5" s="40" t="s">
         <v>10</v>
@@ -4542,7 +4551,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="42" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="Q5" s="42" t="str">
         <f t="shared" si="4"/>
@@ -4589,7 +4598,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C6" s="39" t="s">
         <v>334</v>
@@ -4598,10 +4607,10 @@
         <v>333</v>
       </c>
       <c r="E6" s="38" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F6" s="39" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="G6" s="40" t="s">
         <v>10</v>
@@ -4635,7 +4644,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="42" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="Q6" s="42" t="str">
         <f t="shared" si="4"/>
@@ -5937,7 +5946,7 @@
         <v>Gabarito Freático</v>
       </c>
       <c r="P20" s="42" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="Q20" s="42" t="str">
         <f t="shared" si="14"/>
@@ -6030,7 +6039,7 @@
         <v>Gabarito Subterrâneo</v>
       </c>
       <c r="P21" s="42" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="Q21" s="42" t="str">
         <f t="shared" si="14"/>
@@ -6216,7 +6225,7 @@
         <v>Gabarito Hídrico</v>
       </c>
       <c r="P23" s="42" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="Q23" s="42" t="str">
         <f t="shared" si="14"/>
@@ -6402,7 +6411,7 @@
         <v>Fachada Principal</v>
       </c>
       <c r="P25" s="42" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="Q25" s="42" t="str">
         <f>_xlfn.TRANSLATE(P25,"pt","es")</f>
@@ -6495,7 +6504,7 @@
         <v>Fachada Fundos</v>
       </c>
       <c r="P26" s="42" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q26" s="42" t="str">
         <f t="shared" si="14"/>
@@ -6554,7 +6563,7 @@
         <v>335</v>
       </c>
       <c r="F27" s="46" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G27" s="40" t="s">
         <v>10</v>
@@ -6588,7 +6597,7 @@
         <v>Fachada Lateral Derecha</v>
       </c>
       <c r="P27" s="42" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="Q27" s="42" t="str">
         <f t="shared" si="14"/>
@@ -6647,7 +6656,7 @@
         <v>335</v>
       </c>
       <c r="F28" s="46" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G28" s="40" t="s">
         <v>10</v>
@@ -6681,7 +6690,7 @@
         <v>Fachada Lateral Esquerda</v>
       </c>
       <c r="P28" s="42" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="Q28" s="42" t="str">
         <f t="shared" si="14"/>
@@ -6774,7 +6783,7 @@
         <v>Fachada Inespecífica</v>
       </c>
       <c r="P29" s="42" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="Q29" s="42" t="str">
         <f t="shared" ref="Q29" si="37">_xlfn.TRANSLATE(P29,"pt","es")</f>
@@ -7481,7 +7490,7 @@
         <v>332</v>
       </c>
       <c r="E37" s="38" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F37" s="39" t="s">
         <v>427</v>
@@ -7574,7 +7583,7 @@
         <v>332</v>
       </c>
       <c r="E38" s="38" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F38" s="39" t="s">
         <v>426</v>
@@ -7664,10 +7673,10 @@
         <v>425</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E39" s="38" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F39" s="39" t="s">
         <v>382</v>
@@ -7704,7 +7713,7 @@
         <v>Campus</v>
       </c>
       <c r="P39" s="42" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="Q39" s="42" t="str">
         <f t="shared" si="56"/>
@@ -7739,7 +7748,7 @@
         <v>355</v>
       </c>
       <c r="Z39" s="43" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AA39" s="42" t="str">
         <f t="shared" si="46"/>
@@ -7757,13 +7766,13 @@
         <v>425</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E40" s="38" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F40" s="39" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G40" s="40" t="s">
         <v>10</v>
@@ -7797,7 +7806,7 @@
         <v>Lote Urbano</v>
       </c>
       <c r="P40" s="42" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Q40" s="42" t="str">
         <f t="shared" si="14"/>
@@ -7832,7 +7841,7 @@
         <v>355</v>
       </c>
       <c r="Z40" s="43" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AA40" s="42" t="str">
         <f t="shared" si="17"/>
@@ -7850,10 +7859,10 @@
         <v>425</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E41" s="38" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F41" s="39" t="s">
         <v>233</v>
@@ -7890,7 +7899,7 @@
         <v>Área Bruta</v>
       </c>
       <c r="P41" s="42" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="Q41" s="42" t="str">
         <f t="shared" ref="Q41:Q43" si="63">_xlfn.TRANSLATE(P41,"pt","es")</f>
@@ -7925,7 +7934,7 @@
         <v>355</v>
       </c>
       <c r="Z41" s="43" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AA41" s="42" t="str">
         <f t="shared" si="17"/>
@@ -7943,13 +7952,13 @@
         <v>425</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E42" s="38" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F42" s="39" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G42" s="40" t="s">
         <v>10</v>
@@ -7983,7 +7992,7 @@
         <v>Área Edificavel</v>
       </c>
       <c r="P42" s="42" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="Q42" s="42" t="str">
         <f t="shared" si="63"/>
@@ -8018,7 +8027,7 @@
         <v>356</v>
       </c>
       <c r="Z42" s="43" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AA42" s="42" t="str">
         <f t="shared" ref="AA42" si="68">_xlfn.TRANSLATE(P42,"pt","en")</f>
@@ -8036,13 +8045,13 @@
         <v>425</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E43" s="38" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F43" s="39" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G43" s="40" t="s">
         <v>10</v>
@@ -8076,7 +8085,7 @@
         <v>Recuo</v>
       </c>
       <c r="P43" s="42" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="Q43" s="42" t="str">
         <f t="shared" si="63"/>
@@ -8111,7 +8120,7 @@
         <v>355</v>
       </c>
       <c r="Z43" s="61" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AA43" s="42" t="str">
         <f t="shared" si="17"/>
@@ -8129,13 +8138,13 @@
         <v>425</v>
       </c>
       <c r="D44" s="38" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E44" s="38" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F44" s="39" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G44" s="40" t="s">
         <v>10</v>
@@ -8169,7 +8178,7 @@
         <v>Afastamento</v>
       </c>
       <c r="P44" s="42" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="Q44" s="42" t="str">
         <f t="shared" si="14"/>
@@ -8204,7 +8213,7 @@
         <v>355</v>
       </c>
       <c r="Z44" s="61" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AA44" s="42" t="str">
         <f t="shared" ref="AA44" si="73">_xlfn.TRANSLATE(P44,"pt","en")</f>
@@ -8222,13 +8231,13 @@
         <v>425</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E45" s="38" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F45" s="39" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G45" s="40" t="s">
         <v>10</v>
@@ -8262,7 +8271,7 @@
         <v>Construção Vizinha</v>
       </c>
       <c r="P45" s="42" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="Q45" s="42" t="str">
         <f t="shared" si="14"/>
@@ -8297,7 +8306,7 @@
         <v>357</v>
       </c>
       <c r="Z45" s="43" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AA45" s="42" t="str">
         <f t="shared" si="17"/>
@@ -8315,13 +8324,13 @@
         <v>425</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F46" s="39" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G46" s="40" t="s">
         <v>10</v>
@@ -8355,7 +8364,7 @@
         <v>Áreas Exteriores</v>
       </c>
       <c r="P46" s="42" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="Q46" s="42" t="str">
         <f t="shared" si="14"/>
@@ -8390,7 +8399,7 @@
         <v>359</v>
       </c>
       <c r="Z46" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA46" s="42" t="str">
         <f t="shared" si="17"/>
@@ -8408,13 +8417,13 @@
         <v>425</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E47" s="38" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F47" s="39" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G47" s="40" t="s">
         <v>10</v>
@@ -8448,7 +8457,7 @@
         <v>Áreas Exteriores Hídricas</v>
       </c>
       <c r="P47" s="42" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q47" s="42" t="str">
         <f t="shared" si="14"/>
@@ -8483,7 +8492,7 @@
         <v>358</v>
       </c>
       <c r="Z47" s="43" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AA47" s="42" t="str">
         <f t="shared" si="17"/>
@@ -8501,13 +8510,13 @@
         <v>425</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E48" s="38" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F48" s="39" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G48" s="40" t="s">
         <v>10</v>
@@ -8541,7 +8550,7 @@
         <v>Áreas Exteriores Arvorizadas</v>
       </c>
       <c r="P48" s="42" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="Q48" s="42" t="str">
         <f t="shared" ref="Q48" si="78">_xlfn.TRANSLATE(P48,"pt","es")</f>
@@ -8576,7 +8585,7 @@
         <v>359</v>
       </c>
       <c r="Z48" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA48" s="42" t="str">
         <f t="shared" ref="AA48" si="82">_xlfn.TRANSLATE(P48,"pt","en")</f>
@@ -8594,13 +8603,13 @@
         <v>425</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E49" s="38" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F49" s="39" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="G49" s="40" t="s">
         <v>10</v>
@@ -8634,7 +8643,7 @@
         <v>Áreas de Preservação</v>
       </c>
       <c r="P49" s="42" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="Q49" s="42" t="str">
         <f t="shared" si="14"/>
@@ -8669,7 +8678,7 @@
         <v>359</v>
       </c>
       <c r="Z49" s="43" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AA49" s="42" t="str">
         <f t="shared" si="17"/>
@@ -8687,10 +8696,10 @@
         <v>425</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E50" s="38" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F50" s="39" t="s">
         <v>472</v>
@@ -8762,7 +8771,7 @@
         <v>360</v>
       </c>
       <c r="Z50" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA50" s="42" t="str">
         <f t="shared" si="17"/>
@@ -8780,10 +8789,10 @@
         <v>425</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E51" s="38" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F51" s="39" t="s">
         <v>477</v>
@@ -8855,7 +8864,7 @@
         <v>360</v>
       </c>
       <c r="Z51" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA51" s="42" t="str">
         <f t="shared" ref="AA51" si="92">_xlfn.TRANSLATE(P51,"pt","en")</f>
@@ -8873,10 +8882,10 @@
         <v>425</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E52" s="38" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="F52" s="39" t="s">
         <v>473</v>
@@ -8948,7 +8957,7 @@
         <v>360</v>
       </c>
       <c r="Z52" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA52" s="42" t="str">
         <f t="shared" si="17"/>
@@ -9041,7 +9050,7 @@
         <v>361</v>
       </c>
       <c r="Z53" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA53" s="42" t="str">
         <f t="shared" ref="AA53:AA54" si="97">_xlfn.TRANSLATE(P53,"pt","en")</f>
@@ -9134,7 +9143,7 @@
         <v>361</v>
       </c>
       <c r="Z54" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA54" s="42" t="str">
         <f t="shared" si="97"/>
@@ -9158,7 +9167,7 @@
         <v>439</v>
       </c>
       <c r="F55" s="39" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="G55" s="40" t="s">
         <v>10</v>
@@ -9192,7 +9201,7 @@
         <v>Ambiente Shaft</v>
       </c>
       <c r="P55" s="42" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="Q55" s="42" t="str">
         <f t="shared" si="14"/>
@@ -9227,7 +9236,7 @@
         <v>361</v>
       </c>
       <c r="Z55" s="43" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AA55" s="42" t="str">
         <f t="shared" si="17"/>
@@ -9248,10 +9257,10 @@
         <v>430</v>
       </c>
       <c r="E56" s="38" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F56" s="39" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G56" s="40" t="s">
         <v>10</v>
@@ -9285,7 +9294,7 @@
         <v>Ambiente Acústico</v>
       </c>
       <c r="P56" s="42" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="Q56" s="42" t="str">
         <f t="shared" si="14"/>
@@ -9320,7 +9329,7 @@
         <v>361</v>
       </c>
       <c r="Z56" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA56" s="42" t="str">
         <f t="shared" ref="AA56:AA57" si="106">_xlfn.TRANSLATE(P56,"pt","en")</f>
@@ -9341,10 +9350,10 @@
         <v>430</v>
       </c>
       <c r="E57" s="38" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F57" s="39" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G57" s="40" t="s">
         <v>10</v>
@@ -9378,7 +9387,7 @@
         <v>Ambiente Anecóico</v>
       </c>
       <c r="P57" s="42" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="Q57" s="42" t="str">
         <f t="shared" si="14"/>
@@ -9413,7 +9422,7 @@
         <v>361</v>
       </c>
       <c r="Z57" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA57" s="42" t="str">
         <f t="shared" si="106"/>
@@ -9434,10 +9443,10 @@
         <v>430</v>
       </c>
       <c r="E58" s="38" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F58" s="39" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G58" s="40" t="s">
         <v>10</v>
@@ -9471,7 +9480,7 @@
         <v>Ambiente Reverberante</v>
       </c>
       <c r="P58" s="42" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="Q58" s="42" t="str">
         <f t="shared" si="14"/>
@@ -9506,7 +9515,7 @@
         <v>361</v>
       </c>
       <c r="Z58" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA58" s="42" t="str">
         <f t="shared" si="17"/>
@@ -9527,10 +9536,10 @@
         <v>430</v>
       </c>
       <c r="E59" s="38" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F59" s="39" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G59" s="40" t="s">
         <v>10</v>
@@ -9564,7 +9573,7 @@
         <v>Ambiente Grande</v>
       </c>
       <c r="P59" s="42" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="Q59" s="42" t="str">
         <f t="shared" si="14"/>
@@ -9599,7 +9608,7 @@
         <v>361</v>
       </c>
       <c r="Z59" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA59" s="42" t="str">
         <f t="shared" si="17"/>
@@ -9620,10 +9629,10 @@
         <v>430</v>
       </c>
       <c r="E60" s="38" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F60" s="39" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G60" s="40" t="s">
         <v>10</v>
@@ -9657,7 +9666,7 @@
         <v>Ambiente Expositivo</v>
       </c>
       <c r="P60" s="42" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="Q60" s="42" t="str">
         <f t="shared" si="14"/>
@@ -9692,7 +9701,7 @@
         <v>361</v>
       </c>
       <c r="Z60" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA60" s="42" t="str">
         <f t="shared" ref="AA60:AA61" si="114">_xlfn.TRANSLATE(P60,"pt","en")</f>
@@ -9713,10 +9722,10 @@
         <v>430</v>
       </c>
       <c r="E61" s="38" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F61" s="39" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G61" s="40" t="s">
         <v>10</v>
@@ -9750,7 +9759,7 @@
         <v>Ambiente Teca</v>
       </c>
       <c r="P61" s="42" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="Q61" s="42" t="str">
         <f t="shared" si="14"/>
@@ -9785,7 +9794,7 @@
         <v>361</v>
       </c>
       <c r="Z61" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA61" s="42" t="str">
         <f t="shared" si="114"/>
@@ -9806,10 +9815,10 @@
         <v>430</v>
       </c>
       <c r="E62" s="38" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F62" s="39" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G62" s="40" t="s">
         <v>10</v>
@@ -9843,7 +9852,7 @@
         <v>Ambiente Frio</v>
       </c>
       <c r="P62" s="42" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="Q62" s="42" t="str">
         <f t="shared" si="14"/>
@@ -9878,7 +9887,7 @@
         <v>361</v>
       </c>
       <c r="Z62" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA62" s="42" t="str">
         <f t="shared" si="17"/>
@@ -9899,10 +9908,10 @@
         <v>430</v>
       </c>
       <c r="E63" s="38" t="s">
+        <v>642</v>
+      </c>
+      <c r="F63" s="39" t="s">
         <v>643</v>
-      </c>
-      <c r="F63" s="39" t="s">
-        <v>644</v>
       </c>
       <c r="G63" s="40" t="s">
         <v>10</v>
@@ -9936,7 +9945,7 @@
         <v>Ambiente Telemático</v>
       </c>
       <c r="P63" s="42" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="Q63" s="42" t="str">
         <f t="shared" si="14"/>
@@ -9971,7 +9980,7 @@
         <v>361</v>
       </c>
       <c r="Z63" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA63" s="42" t="str">
         <f t="shared" si="17"/>
@@ -9992,10 +10001,10 @@
         <v>430</v>
       </c>
       <c r="E64" s="38" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F64" s="39" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G64" s="40" t="s">
         <v>10</v>
@@ -10029,7 +10038,7 @@
         <v>Ambiente Gastronômico</v>
       </c>
       <c r="P64" s="42" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="Q64" s="42" t="str">
         <f t="shared" si="14"/>
@@ -10064,7 +10073,7 @@
         <v>361</v>
       </c>
       <c r="Z64" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA64" s="42" t="str">
         <f t="shared" ref="AA64:AA71" si="122">_xlfn.TRANSLATE(P64,"pt","en")</f>
@@ -10085,10 +10094,10 @@
         <v>430</v>
       </c>
       <c r="E65" s="38" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F65" s="39" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G65" s="40" t="s">
         <v>10</v>
@@ -10122,7 +10131,7 @@
         <v>Ambiente Manutenção</v>
       </c>
       <c r="P65" s="42" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="Q65" s="42" t="str">
         <f t="shared" si="14"/>
@@ -10157,7 +10166,7 @@
         <v>361</v>
       </c>
       <c r="Z65" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA65" s="42" t="str">
         <f t="shared" si="122"/>
@@ -10178,10 +10187,10 @@
         <v>430</v>
       </c>
       <c r="E66" s="38" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F66" s="39" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G66" s="40" t="s">
         <v>10</v>
@@ -10215,7 +10224,7 @@
         <v>Ambiente Logístico</v>
       </c>
       <c r="P66" s="42" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="Q66" s="42" t="str">
         <f t="shared" si="14"/>
@@ -10250,7 +10259,7 @@
         <v>361</v>
       </c>
       <c r="Z66" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA66" s="42" t="str">
         <f t="shared" si="122"/>
@@ -10271,10 +10280,10 @@
         <v>430</v>
       </c>
       <c r="E67" s="38" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F67" s="39" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G67" s="40" t="s">
         <v>10</v>
@@ -10308,7 +10317,7 @@
         <v>Ambiente Blindado</v>
       </c>
       <c r="P67" s="42" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="Q67" s="42" t="str">
         <f t="shared" si="14"/>
@@ -10343,7 +10352,7 @@
         <v>361</v>
       </c>
       <c r="Z67" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA67" s="42" t="str">
         <f t="shared" si="122"/>
@@ -10364,10 +10373,10 @@
         <v>430</v>
       </c>
       <c r="E68" s="38" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F68" s="39" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G68" s="40" t="s">
         <v>10</v>
@@ -10401,7 +10410,7 @@
         <v>Ambiente Tério</v>
       </c>
       <c r="P68" s="42" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q68" s="42" t="str">
         <f t="shared" si="14"/>
@@ -10436,7 +10445,7 @@
         <v>361</v>
       </c>
       <c r="Z68" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA68" s="42" t="str">
         <f t="shared" si="122"/>
@@ -10457,10 +10466,10 @@
         <v>430</v>
       </c>
       <c r="E69" s="38" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F69" s="39" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G69" s="40" t="s">
         <v>10</v>
@@ -10494,7 +10503,7 @@
         <v>Ambiente Quarentena</v>
       </c>
       <c r="P69" s="42" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q69" s="42" t="str">
         <f t="shared" ref="Q69:Q70" si="127">_xlfn.TRANSLATE(P69,"pt","es")</f>
@@ -10529,7 +10538,7 @@
         <v>361</v>
       </c>
       <c r="Z69" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA69" s="42" t="str">
         <f t="shared" ref="AA69:AA70" si="132">_xlfn.TRANSLATE(P69,"pt","en")</f>
@@ -10550,10 +10559,10 @@
         <v>430</v>
       </c>
       <c r="E70" s="38" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F70" s="39" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G70" s="40" t="s">
         <v>10</v>
@@ -10587,7 +10596,7 @@
         <v>Ambiente Tribunal</v>
       </c>
       <c r="P70" s="42" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="Q70" s="42" t="str">
         <f t="shared" si="127"/>
@@ -10622,7 +10631,7 @@
         <v>361</v>
       </c>
       <c r="Z70" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA70" s="42" t="str">
         <f t="shared" si="132"/>
@@ -10643,10 +10652,10 @@
         <v>430</v>
       </c>
       <c r="E71" s="38" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F71" s="39" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G71" s="40" t="s">
         <v>10</v>
@@ -10680,7 +10689,7 @@
         <v>Ambiente Estacionamento</v>
       </c>
       <c r="P71" s="42" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q71" s="42" t="str">
         <f t="shared" si="14"/>
@@ -10715,7 +10724,7 @@
         <v>361</v>
       </c>
       <c r="Z71" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA71" s="42" t="str">
         <f t="shared" si="122"/>
@@ -10736,10 +10745,10 @@
         <v>430</v>
       </c>
       <c r="E72" s="38" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F72" s="39" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G72" s="40" t="s">
         <v>10</v>
@@ -10773,7 +10782,7 @@
         <v>Ambiente Esportivo</v>
       </c>
       <c r="P72" s="42" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="Q72" s="42" t="str">
         <f t="shared" si="14"/>
@@ -10808,7 +10817,7 @@
         <v>361</v>
       </c>
       <c r="Z72" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA72" s="42" t="str">
         <f t="shared" ref="AA72:AA76" si="140">_xlfn.TRANSLATE(P72,"pt","en")</f>
@@ -10829,10 +10838,10 @@
         <v>430</v>
       </c>
       <c r="E73" s="38" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F73" s="39" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G73" s="40" t="s">
         <v>10</v>
@@ -10866,7 +10875,7 @@
         <v>Ambiente Quadra Esportiva</v>
       </c>
       <c r="P73" s="42" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="Q73" s="42" t="str">
         <f t="shared" si="14"/>
@@ -10901,7 +10910,7 @@
         <v>361</v>
       </c>
       <c r="Z73" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA73" s="42" t="e" vm="1">
         <f t="shared" si="140"/>
@@ -10922,10 +10931,10 @@
         <v>430</v>
       </c>
       <c r="E74" s="38" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F74" s="39" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G74" s="40" t="s">
         <v>10</v>
@@ -10959,7 +10968,7 @@
         <v>Ambiente Piscina Esportiva</v>
       </c>
       <c r="P74" s="42" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Q74" s="42" t="str">
         <f t="shared" ref="Q74" si="146">_xlfn.TRANSLATE(P74,"pt","es")</f>
@@ -10994,7 +11003,7 @@
         <v>361</v>
       </c>
       <c r="Z74" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA74" s="42" t="str">
         <f t="shared" ref="AA74" si="150">_xlfn.TRANSLATE(P74,"pt","en")</f>
@@ -11015,10 +11024,10 @@
         <v>430</v>
       </c>
       <c r="E75" s="38" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F75" s="39" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="G75" s="40" t="s">
         <v>10</v>
@@ -11052,7 +11061,7 @@
         <v>Ambiente Pista Esportiva</v>
       </c>
       <c r="P75" s="42" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="Q75" s="42" t="str">
         <f t="shared" si="14"/>
@@ -11087,7 +11096,7 @@
         <v>361</v>
       </c>
       <c r="Z75" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA75" s="42" t="str">
         <f t="shared" si="140"/>
@@ -11108,10 +11117,10 @@
         <v>430</v>
       </c>
       <c r="E76" s="38" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F76" s="39" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="G76" s="40" t="s">
         <v>10</v>
@@ -11145,7 +11154,7 @@
         <v>Ambiente Arquibancada</v>
       </c>
       <c r="P76" s="42" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Q76" s="42" t="str">
         <f t="shared" si="14"/>
@@ -11180,7 +11189,7 @@
         <v>361</v>
       </c>
       <c r="Z76" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA76" s="42" t="str">
         <f t="shared" si="140"/>
@@ -11201,10 +11210,10 @@
         <v>430</v>
       </c>
       <c r="E77" s="38" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F77" s="39" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G77" s="40" t="s">
         <v>10</v>
@@ -11238,7 +11247,7 @@
         <v>Ambiente Vestiário Esportivo</v>
       </c>
       <c r="P77" s="42" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="Q77" s="42" t="str">
         <f t="shared" si="14"/>
@@ -11273,7 +11282,7 @@
         <v>361</v>
       </c>
       <c r="Z77" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA77" s="42" t="str">
         <f t="shared" si="17"/>
@@ -11331,7 +11340,7 @@
         <v>Sanitário Masculino</v>
       </c>
       <c r="P78" s="42" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="Q78" s="42" t="str">
         <f t="shared" si="14"/>
@@ -11424,7 +11433,7 @@
         <v>Sanitário Feminino</v>
       </c>
       <c r="P79" s="42" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="Q79" s="42" t="str">
         <f t="shared" si="14"/>
@@ -11517,7 +11526,7 @@
         <v>Sanitário Indiferenciado</v>
       </c>
       <c r="P80" s="42" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="Q80" s="42" t="str">
         <f t="shared" si="14"/>
@@ -11610,7 +11619,7 @@
         <v>Sanitário PNE</v>
       </c>
       <c r="P81" s="42" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="Q81" s="42" t="str">
         <f t="shared" si="14"/>
@@ -11703,7 +11712,7 @@
         <v>Sanitário WC</v>
       </c>
       <c r="P82" s="42" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="Q82" s="42" t="str">
         <f t="shared" si="14"/>
@@ -11759,10 +11768,10 @@
         <v>430</v>
       </c>
       <c r="E83" s="38" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F83" s="39" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G83" s="40" t="s">
         <v>10</v>
@@ -11796,7 +11805,7 @@
         <v>Ambiente Trabalho</v>
       </c>
       <c r="P83" s="42" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="Q83" s="42" t="str">
         <f t="shared" si="14"/>
@@ -11831,7 +11840,7 @@
         <v>361</v>
       </c>
       <c r="Z83" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA83" s="42" t="str">
         <f t="shared" ref="AA83:AA84" si="161">_xlfn.TRANSLATE(P83,"pt","en")</f>
@@ -11852,10 +11861,10 @@
         <v>430</v>
       </c>
       <c r="E84" s="38" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F84" s="39" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G84" s="40" t="s">
         <v>10</v>
@@ -11889,7 +11898,7 @@
         <v>Ambiente Trocas</v>
       </c>
       <c r="P84" s="42" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="Q84" s="42" t="str">
         <f t="shared" ref="Q84" si="162">_xlfn.TRANSLATE(P84,"pt","es")</f>
@@ -11924,7 +11933,7 @@
         <v>361</v>
       </c>
       <c r="Z84" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA84" s="42" t="str">
         <f t="shared" si="161"/>
@@ -11945,10 +11954,10 @@
         <v>430</v>
       </c>
       <c r="E85" s="38" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F85" s="39" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G85" s="40" t="s">
         <v>10</v>
@@ -11982,7 +11991,7 @@
         <v>Ambiente Social</v>
       </c>
       <c r="P85" s="42" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="Q85" s="42" t="str">
         <f t="shared" si="14"/>
@@ -12017,7 +12026,7 @@
         <v>361</v>
       </c>
       <c r="Z85" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA85" s="42" t="str">
         <f t="shared" si="17"/>
@@ -12038,10 +12047,10 @@
         <v>430</v>
       </c>
       <c r="E86" s="38" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F86" s="39" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G86" s="40" t="s">
         <v>10</v>
@@ -12075,7 +12084,7 @@
         <v>Ambiente Intimo</v>
       </c>
       <c r="P86" s="42" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="Q86" s="42" t="str">
         <f t="shared" si="14"/>
@@ -12110,7 +12119,7 @@
         <v>361</v>
       </c>
       <c r="Z86" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA86" s="42" t="str">
         <f t="shared" si="17"/>
@@ -12131,10 +12140,10 @@
         <v>430</v>
       </c>
       <c r="E87" s="38" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F87" s="39" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G87" s="40" t="s">
         <v>10</v>
@@ -12168,7 +12177,7 @@
         <v>Ambiente Higiene</v>
       </c>
       <c r="P87" s="42" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="Q87" s="42" t="str">
         <f t="shared" si="14"/>
@@ -12203,7 +12212,7 @@
         <v>361</v>
       </c>
       <c r="Z87" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA87" s="42" t="str">
         <f t="shared" si="17"/>
@@ -12224,10 +12233,10 @@
         <v>430</v>
       </c>
       <c r="E88" s="38" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F88" s="39" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G88" s="40" t="s">
         <v>10</v>
@@ -12261,7 +12270,7 @@
         <v>Ambiente Serviço</v>
       </c>
       <c r="P88" s="42" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="Q88" s="42" t="str">
         <f t="shared" ref="Q88:Q160" si="167">_xlfn.TRANSLATE(P88,"pt","es")</f>
@@ -12296,7 +12305,7 @@
         <v>361</v>
       </c>
       <c r="Z88" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA88" s="42" t="str">
         <f t="shared" ref="AA88:AA91" si="168">_xlfn.TRANSLATE(P88,"pt","en")</f>
@@ -12317,10 +12326,10 @@
         <v>430</v>
       </c>
       <c r="E89" s="38" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F89" s="39" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G89" s="40" t="s">
         <v>10</v>
@@ -12354,7 +12363,7 @@
         <v xml:space="preserve">Ambiente Lazer </v>
       </c>
       <c r="P89" s="42" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="Q89" s="42" t="str">
         <f t="shared" si="167"/>
@@ -12389,7 +12398,7 @@
         <v>361</v>
       </c>
       <c r="Z89" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA89" s="42" t="str">
         <f t="shared" si="168"/>
@@ -12410,10 +12419,10 @@
         <v>430</v>
       </c>
       <c r="E90" s="38" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F90" s="39" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G90" s="40" t="s">
         <v>10</v>
@@ -12447,7 +12456,7 @@
         <v>Ambiente Profissional</v>
       </c>
       <c r="P90" s="42" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Q90" s="42" t="str">
         <f t="shared" si="167"/>
@@ -12482,7 +12491,7 @@
         <v>361</v>
       </c>
       <c r="Z90" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA90" s="42" t="str">
         <f t="shared" si="168"/>
@@ -12503,10 +12512,10 @@
         <v>430</v>
       </c>
       <c r="E91" s="38" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F91" s="39" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G91" s="40" t="s">
         <v>10</v>
@@ -12540,7 +12549,7 @@
         <v>Ambiente Saúde</v>
       </c>
       <c r="P91" s="42" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="Q91" s="42" t="str">
         <f t="shared" si="167"/>
@@ -12575,7 +12584,7 @@
         <v>361</v>
       </c>
       <c r="Z91" s="43" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AA91" s="42" t="str">
         <f t="shared" si="168"/>
@@ -12596,10 +12605,10 @@
         <v>430</v>
       </c>
       <c r="E92" s="38" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F92" s="39" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G92" s="40" t="s">
         <v>10</v>
@@ -12633,7 +12642,7 @@
         <v>Ambiente Análises</v>
       </c>
       <c r="P92" s="42" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q92" s="42" t="str">
         <f t="shared" si="167"/>
@@ -12668,7 +12677,7 @@
         <v>361</v>
       </c>
       <c r="Z92" s="43" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AA92" s="42" t="str">
         <f t="shared" ref="AA92" si="178">_xlfn.TRANSLATE(P92,"pt","en")</f>
@@ -12689,10 +12698,10 @@
         <v>430</v>
       </c>
       <c r="E93" s="38" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F93" s="39" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G93" s="40" t="s">
         <v>10</v>
@@ -12726,7 +12735,7 @@
         <v>Ambiente Quirúrgico</v>
       </c>
       <c r="P93" s="42" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q93" s="42" t="str">
         <f t="shared" si="167"/>
@@ -12761,7 +12770,7 @@
         <v>361</v>
       </c>
       <c r="Z93" s="43" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AA93" s="42" t="str">
         <f t="shared" si="17"/>
@@ -12782,10 +12791,10 @@
         <v>430</v>
       </c>
       <c r="E94" s="38" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F94" s="39" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="G94" s="40" t="s">
         <v>10</v>
@@ -12819,7 +12828,7 @@
         <v>Ambiente Internação</v>
       </c>
       <c r="P94" s="42" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q94" s="42" t="str">
         <f t="shared" si="167"/>
@@ -12854,7 +12863,7 @@
         <v>361</v>
       </c>
       <c r="Z94" s="43" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AA94" s="42" t="str">
         <f t="shared" si="17"/>
@@ -12875,10 +12884,10 @@
         <v>430</v>
       </c>
       <c r="E95" s="38" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F95" s="39" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="G95" s="40" t="s">
         <v>10</v>
@@ -12912,7 +12921,7 @@
         <v>Ambiente UTI</v>
       </c>
       <c r="P95" s="42" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="Q95" s="42" t="str">
         <f t="shared" si="167"/>
@@ -12947,7 +12956,7 @@
         <v>361</v>
       </c>
       <c r="Z95" s="43" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AA95" s="42" t="str">
         <f t="shared" ref="AA95:AA96" si="188">_xlfn.TRANSLATE(P95,"pt","en")</f>
@@ -12968,10 +12977,10 @@
         <v>430</v>
       </c>
       <c r="E96" s="38" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F96" s="39" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G96" s="40" t="s">
         <v>10</v>
@@ -13005,7 +13014,7 @@
         <v>Ambiente Imagem</v>
       </c>
       <c r="P96" s="42" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="Q96" s="42" t="str">
         <f t="shared" ref="Q96" si="189">_xlfn.TRANSLATE(P96,"pt","es")</f>
@@ -13040,7 +13049,7 @@
         <v>361</v>
       </c>
       <c r="Z96" s="43" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AA96" s="42" t="str">
         <f t="shared" si="188"/>
@@ -13061,10 +13070,10 @@
         <v>430</v>
       </c>
       <c r="E97" s="38" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F97" s="39" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="G97" s="40" t="s">
         <v>10</v>
@@ -13098,7 +13107,7 @@
         <v>Ambiente Terapia</v>
       </c>
       <c r="P97" s="42" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Q97" s="42" t="str">
         <f t="shared" si="167"/>
@@ -13133,7 +13142,7 @@
         <v>361</v>
       </c>
       <c r="Z97" s="43" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AA97" s="42" t="str">
         <f t="shared" si="17"/>
@@ -13154,10 +13163,10 @@
         <v>430</v>
       </c>
       <c r="E98" s="38" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F98" s="39" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="G98" s="40" t="s">
         <v>10</v>
@@ -13191,7 +13200,7 @@
         <v>Ambiente Hidroterapia</v>
       </c>
       <c r="P98" s="42" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q98" s="42" t="str">
         <f t="shared" si="167"/>
@@ -13226,7 +13235,7 @@
         <v>361</v>
       </c>
       <c r="Z98" s="43" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AA98" s="42" t="str">
         <f t="shared" ref="AA98" si="196">_xlfn.TRANSLATE(P98,"pt","en")</f>
@@ -13247,10 +13256,10 @@
         <v>430</v>
       </c>
       <c r="E99" s="38" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F99" s="39" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="G99" s="40" t="s">
         <v>10</v>
@@ -13284,7 +13293,7 @@
         <v>Ambiente Emergência</v>
       </c>
       <c r="P99" s="42" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="Q99" s="42" t="str">
         <f t="shared" si="167"/>
@@ -13319,7 +13328,7 @@
         <v>361</v>
       </c>
       <c r="Z99" s="43" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AA99" s="42" t="str">
         <f t="shared" si="17"/>
@@ -13340,10 +13349,10 @@
         <v>430</v>
       </c>
       <c r="E100" s="38" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F100" s="39" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="G100" s="40" t="s">
         <v>10</v>
@@ -13377,7 +13386,7 @@
         <v>Ambiente Triagem</v>
       </c>
       <c r="P100" s="42" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="Q100" s="42" t="str">
         <f t="shared" si="167"/>
@@ -13412,7 +13421,7 @@
         <v>361</v>
       </c>
       <c r="Z100" s="43" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AA100" s="42" t="str">
         <f t="shared" ref="AA100:AA104" si="204">_xlfn.TRANSLATE(P100,"pt","en")</f>
@@ -13433,10 +13442,10 @@
         <v>430</v>
       </c>
       <c r="E101" s="38" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F101" s="39" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="G101" s="40" t="s">
         <v>10</v>
@@ -13470,7 +13479,7 @@
         <v>Ambiente Veicular</v>
       </c>
       <c r="P101" s="42" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="Q101" s="42" t="str">
         <f t="shared" si="167"/>
@@ -13505,7 +13514,7 @@
         <v>361</v>
       </c>
       <c r="Z101" s="43" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AA101" s="42" t="str">
         <f t="shared" ref="AA101" si="209">_xlfn.TRANSLATE(P101,"pt","en")</f>
@@ -13526,10 +13535,10 @@
         <v>430</v>
       </c>
       <c r="E102" s="38" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F102" s="39" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G102" s="40" t="s">
         <v>10</v>
@@ -13563,7 +13572,7 @@
         <v>Ambiente Espera</v>
       </c>
       <c r="P102" s="42" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="Q102" s="42" t="str">
         <f t="shared" si="167"/>
@@ -13598,7 +13607,7 @@
         <v>361</v>
       </c>
       <c r="Z102" s="43" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AA102" s="42" t="str">
         <f t="shared" si="204"/>
@@ -13619,10 +13628,10 @@
         <v>430</v>
       </c>
       <c r="E103" s="38" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F103" s="39" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G103" s="40" t="s">
         <v>10</v>
@@ -13656,7 +13665,7 @@
         <v>Ambiente Consultório</v>
       </c>
       <c r="P103" s="42" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="Q103" s="42" t="str">
         <f t="shared" si="167"/>
@@ -13691,7 +13700,7 @@
         <v>361</v>
       </c>
       <c r="Z103" s="43" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AA103" s="42" t="str">
         <f t="shared" ref="AA103" si="217">_xlfn.TRANSLATE(P103,"pt","en")</f>
@@ -13712,10 +13721,10 @@
         <v>430</v>
       </c>
       <c r="E104" s="38" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F104" s="39" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G104" s="40" t="s">
         <v>10</v>
@@ -13749,7 +13758,7 @@
         <v>Ambiente Enfermagem</v>
       </c>
       <c r="P104" s="42" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="Q104" s="42" t="str">
         <f t="shared" si="167"/>
@@ -13784,7 +13793,7 @@
         <v>361</v>
       </c>
       <c r="Z104" s="43" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AA104" s="42" t="str">
         <f t="shared" si="204"/>
@@ -13805,10 +13814,10 @@
         <v>430</v>
       </c>
       <c r="E105" s="38" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F105" s="39" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="G105" s="40" t="s">
         <v>10</v>
@@ -13842,7 +13851,7 @@
         <v>Ambiente Biossegurança NB1</v>
       </c>
       <c r="P105" s="42" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="Q105" s="42" t="str">
         <f t="shared" si="167"/>
@@ -13877,7 +13886,7 @@
         <v>361</v>
       </c>
       <c r="Z105" s="43" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AA105" s="42" t="str">
         <f t="shared" ref="AA105:AA109" si="222">_xlfn.TRANSLATE(P105,"pt","en")</f>
@@ -13898,10 +13907,10 @@
         <v>430</v>
       </c>
       <c r="E106" s="38" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F106" s="39" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="G106" s="40" t="s">
         <v>10</v>
@@ -13935,7 +13944,7 @@
         <v>Ambiente Biossegurança NB2</v>
       </c>
       <c r="P106" s="42" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="Q106" s="42" t="str">
         <f t="shared" si="167"/>
@@ -13970,7 +13979,7 @@
         <v>361</v>
       </c>
       <c r="Z106" s="43" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AA106" s="42" t="str">
         <f t="shared" si="222"/>
@@ -13991,10 +14000,10 @@
         <v>430</v>
       </c>
       <c r="E107" s="38" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F107" s="39" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="G107" s="40" t="s">
         <v>10</v>
@@ -14028,7 +14037,7 @@
         <v>Ambiente Biossegurança NB3</v>
       </c>
       <c r="P107" s="42" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="Q107" s="42" t="str">
         <f t="shared" si="167"/>
@@ -14063,7 +14072,7 @@
         <v>361</v>
       </c>
       <c r="Z107" s="43" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AA107" s="42" t="str">
         <f t="shared" si="222"/>
@@ -14084,10 +14093,10 @@
         <v>430</v>
       </c>
       <c r="E108" s="38" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F108" s="39" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="G108" s="40" t="s">
         <v>10</v>
@@ -14121,7 +14130,7 @@
         <v>Ambiente Biossegurança NB4</v>
       </c>
       <c r="P108" s="42" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="Q108" s="42" t="str">
         <f t="shared" ref="Q108" si="227">_xlfn.TRANSLATE(P108,"pt","es")</f>
@@ -14156,7 +14165,7 @@
         <v>361</v>
       </c>
       <c r="Z108" s="43" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AA108" s="42" t="str">
         <f t="shared" ref="AA108" si="232">_xlfn.TRANSLATE(P108,"pt","en")</f>
@@ -14177,10 +14186,10 @@
         <v>430</v>
       </c>
       <c r="E109" s="38" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F109" s="39" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="G109" s="40" t="s">
         <v>10</v>
@@ -14214,7 +14223,7 @@
         <v>Ambiente Paramentação</v>
       </c>
       <c r="P109" s="42" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="Q109" s="42" t="str">
         <f t="shared" si="167"/>
@@ -14249,7 +14258,7 @@
         <v>361</v>
       </c>
       <c r="Z109" s="43" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AA109" s="42" t="str">
         <f t="shared" si="222"/>
@@ -14270,10 +14279,10 @@
         <v>430</v>
       </c>
       <c r="E110" s="38" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F110" s="39" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G110" s="40" t="s">
         <v>10</v>
@@ -14307,7 +14316,7 @@
         <v>Ambiente Infantil</v>
       </c>
       <c r="P110" s="42" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="Q110" s="42" t="str">
         <f t="shared" si="167"/>
@@ -14342,7 +14351,7 @@
         <v>361</v>
       </c>
       <c r="Z110" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA110" s="42" t="str">
         <f t="shared" ref="AA110:AA113" si="237">_xlfn.TRANSLATE(P110,"pt","en")</f>
@@ -14363,10 +14372,10 @@
         <v>430</v>
       </c>
       <c r="E111" s="38" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F111" s="39" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="G111" s="40" t="s">
         <v>10</v>
@@ -14400,7 +14409,7 @@
         <v>Ambiente Ensino</v>
       </c>
       <c r="P111" s="42" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="Q111" s="42" t="str">
         <f t="shared" si="167"/>
@@ -14435,7 +14444,7 @@
         <v>361</v>
       </c>
       <c r="Z111" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA111" s="42" t="str">
         <f t="shared" si="237"/>
@@ -14456,10 +14465,10 @@
         <v>430</v>
       </c>
       <c r="E112" s="38" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F112" s="39" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G112" s="40" t="s">
         <v>10</v>
@@ -14493,7 +14502,7 @@
         <v>Ambiente Ensino Artístico</v>
       </c>
       <c r="P112" s="42" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="Q112" s="42" t="str">
         <f t="shared" ref="Q112:Q113" si="241">_xlfn.TRANSLATE(P112,"pt","es")</f>
@@ -14528,7 +14537,7 @@
         <v>361</v>
       </c>
       <c r="Z112" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA112" s="42" t="str">
         <f t="shared" si="237"/>
@@ -14549,10 +14558,10 @@
         <v>430</v>
       </c>
       <c r="E113" s="38" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F113" s="39" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="G113" s="40" t="s">
         <v>10</v>
@@ -14586,7 +14595,7 @@
         <v>Ambiente Ensino Científico</v>
       </c>
       <c r="P113" s="42" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="Q113" s="42" t="str">
         <f t="shared" si="241"/>
@@ -14621,7 +14630,7 @@
         <v>361</v>
       </c>
       <c r="Z113" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA113" s="42" t="str">
         <f t="shared" si="237"/>
@@ -14642,10 +14651,10 @@
         <v>430</v>
       </c>
       <c r="E114" s="38" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F114" s="39" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="G114" s="40" t="s">
         <v>10</v>
@@ -14679,7 +14688,7 @@
         <v>Ambiente Ensino Técnico</v>
       </c>
       <c r="P114" s="42" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Q114" s="42" t="str">
         <f t="shared" si="167"/>
@@ -14714,7 +14723,7 @@
         <v>361</v>
       </c>
       <c r="Z114" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA114" s="42" t="str">
         <f t="shared" ref="AA114:AA120" si="246">_xlfn.TRANSLATE(P114,"pt","en")</f>
@@ -14735,10 +14744,10 @@
         <v>430</v>
       </c>
       <c r="E115" s="38" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F115" s="39" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G115" s="40" t="s">
         <v>10</v>
@@ -14772,7 +14781,7 @@
         <v>Ambiente Ensino Informática</v>
       </c>
       <c r="P115" s="42" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="Q115" s="42" t="str">
         <f t="shared" si="167"/>
@@ -14807,7 +14816,7 @@
         <v>361</v>
       </c>
       <c r="Z115" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA115" s="42" t="str">
         <f t="shared" si="246"/>
@@ -14828,10 +14837,10 @@
         <v>430</v>
       </c>
       <c r="E116" s="38" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F116" s="39" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="G116" s="40" t="s">
         <v>10</v>
@@ -14865,7 +14874,7 @@
         <v>Ambiente Ensino Química</v>
       </c>
       <c r="P116" s="42" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="Q116" s="42" t="str">
         <f t="shared" si="167"/>
@@ -14900,7 +14909,7 @@
         <v>361</v>
       </c>
       <c r="Z116" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA116" s="42" t="str">
         <f t="shared" si="246"/>
@@ -14921,10 +14930,10 @@
         <v>430</v>
       </c>
       <c r="E117" s="38" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F117" s="39" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="G117" s="40" t="s">
         <v>10</v>
@@ -14958,7 +14967,7 @@
         <v>Ambiente Ensino Física</v>
       </c>
       <c r="P117" s="42" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="Q117" s="42" t="str">
         <f t="shared" si="167"/>
@@ -14993,7 +15002,7 @@
         <v>361</v>
       </c>
       <c r="Z117" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA117" s="42" t="str">
         <f t="shared" si="246"/>
@@ -15014,10 +15023,10 @@
         <v>430</v>
       </c>
       <c r="E118" s="38" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F118" s="39" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G118" s="40" t="s">
         <v>10</v>
@@ -15051,7 +15060,7 @@
         <v>Ambiente Ensino Biologia</v>
       </c>
       <c r="P118" s="42" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="Q118" s="42" t="str">
         <f t="shared" si="167"/>
@@ -15086,7 +15095,7 @@
         <v>361</v>
       </c>
       <c r="Z118" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA118" s="42" t="str">
         <f t="shared" si="246"/>
@@ -15107,10 +15116,10 @@
         <v>430</v>
       </c>
       <c r="E119" s="38" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F119" s="39" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G119" s="40" t="s">
         <v>10</v>
@@ -15144,7 +15153,7 @@
         <v>Ambiente Ensino Música</v>
       </c>
       <c r="P119" s="42" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="Q119" s="42" t="str">
         <f t="shared" si="167"/>
@@ -15179,7 +15188,7 @@
         <v>361</v>
       </c>
       <c r="Z119" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA119" s="42" t="str">
         <f t="shared" ref="AA119" si="254">_xlfn.TRANSLATE(P119,"pt","en")</f>
@@ -15200,10 +15209,10 @@
         <v>430</v>
       </c>
       <c r="E120" s="38" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F120" s="39" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G120" s="40" t="s">
         <v>10</v>
@@ -15237,7 +15246,7 @@
         <v>Ambiente Ensino FabLab</v>
       </c>
       <c r="P120" s="42" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="Q120" s="42" t="str">
         <f t="shared" si="167"/>
@@ -15272,7 +15281,7 @@
         <v>361</v>
       </c>
       <c r="Z120" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA120" s="42" t="str">
         <f t="shared" si="246"/>
@@ -15293,10 +15302,10 @@
         <v>430</v>
       </c>
       <c r="E121" s="38" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F121" s="39" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="G121" s="40" t="s">
         <v>10</v>
@@ -15330,7 +15339,7 @@
         <v>Ambiente Recreativo</v>
       </c>
       <c r="P121" s="42" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="Q121" s="42" t="str">
         <f t="shared" si="167"/>
@@ -15365,7 +15374,7 @@
         <v>361</v>
       </c>
       <c r="Z121" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA121" s="42" t="str">
         <f t="shared" si="17"/>
@@ -15386,7 +15395,7 @@
         <v>430</v>
       </c>
       <c r="E122" s="38" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F122" s="39" t="s">
         <v>234</v>
@@ -15423,7 +15432,7 @@
         <v>Camarim</v>
       </c>
       <c r="P122" s="42" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="Q122" s="42" t="str">
         <f t="shared" si="167"/>
@@ -15458,7 +15467,7 @@
         <v>361</v>
       </c>
       <c r="Z122" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA122" s="42" t="str">
         <f t="shared" ref="AA122:AA161" si="258">_xlfn.TRANSLATE(P122,"pt","en")</f>
@@ -15479,7 +15488,7 @@
         <v>430</v>
       </c>
       <c r="E123" s="38" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F123" s="39" t="s">
         <v>235</v>
@@ -15551,7 +15560,7 @@
         <v>361</v>
       </c>
       <c r="Z123" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA123" s="42" t="str">
         <f t="shared" si="258"/>
@@ -15572,7 +15581,7 @@
         <v>430</v>
       </c>
       <c r="E124" s="38" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F124" s="39" t="s">
         <v>236</v>
@@ -15644,7 +15653,7 @@
         <v>361</v>
       </c>
       <c r="Z124" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA124" s="42" t="str">
         <f t="shared" si="258"/>
@@ -15665,7 +15674,7 @@
         <v>430</v>
       </c>
       <c r="E125" s="38" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F125" s="39" t="s">
         <v>238</v>
@@ -15737,7 +15746,7 @@
         <v>361</v>
       </c>
       <c r="Z125" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA125" s="42" t="str">
         <f t="shared" si="258"/>
@@ -15758,7 +15767,7 @@
         <v>430</v>
       </c>
       <c r="E126" s="38" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F126" s="39" t="s">
         <v>240</v>
@@ -15830,7 +15839,7 @@
         <v>361</v>
       </c>
       <c r="Z126" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA126" s="42" t="str">
         <f t="shared" si="258"/>
@@ -15851,7 +15860,7 @@
         <v>430</v>
       </c>
       <c r="E127" s="38" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F127" s="39" t="s">
         <v>241</v>
@@ -15923,7 +15932,7 @@
         <v>361</v>
       </c>
       <c r="Z127" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA127" s="42" t="str">
         <f t="shared" si="258"/>
@@ -15944,7 +15953,7 @@
         <v>430</v>
       </c>
       <c r="E128" s="38" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F128" s="39" t="s">
         <v>243</v>
@@ -16016,7 +16025,7 @@
         <v>361</v>
       </c>
       <c r="Z128" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA128" s="42" t="str">
         <f t="shared" si="258"/>
@@ -16037,7 +16046,7 @@
         <v>430</v>
       </c>
       <c r="E129" s="38" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F129" s="39" t="s">
         <v>245</v>
@@ -16109,7 +16118,7 @@
         <v>361</v>
       </c>
       <c r="Z129" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA129" s="42" t="str">
         <f t="shared" si="258"/>
@@ -16130,7 +16139,7 @@
         <v>430</v>
       </c>
       <c r="E130" s="38" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F130" s="39" t="s">
         <v>247</v>
@@ -16202,7 +16211,7 @@
         <v>361</v>
       </c>
       <c r="Z130" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA130" s="42" t="str">
         <f t="shared" si="258"/>
@@ -16223,7 +16232,7 @@
         <v>430</v>
       </c>
       <c r="E131" s="38" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F131" s="39" t="s">
         <v>249</v>
@@ -16295,7 +16304,7 @@
         <v>361</v>
       </c>
       <c r="Z131" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA131" s="42" t="str">
         <f t="shared" ref="AA131:AA136" si="266">_xlfn.TRANSLATE(P131,"pt","en")</f>
@@ -16316,7 +16325,7 @@
         <v>430</v>
       </c>
       <c r="E132" s="38" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F132" s="39" t="s">
         <v>454</v>
@@ -16353,7 +16362,7 @@
         <v>Nave Industrial</v>
       </c>
       <c r="P132" s="57" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="Q132" s="42" t="str">
         <f t="shared" si="167"/>
@@ -16388,7 +16397,7 @@
         <v>361</v>
       </c>
       <c r="Z132" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA132" s="42" t="str">
         <f t="shared" si="266"/>
@@ -16409,7 +16418,7 @@
         <v>430</v>
       </c>
       <c r="E133" s="38" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F133" s="39" t="s">
         <v>455</v>
@@ -16446,7 +16455,7 @@
         <v>Galpão Industrial</v>
       </c>
       <c r="P133" s="57" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="Q133" s="42" t="str">
         <f t="shared" si="167"/>
@@ -16481,7 +16490,7 @@
         <v>361</v>
       </c>
       <c r="Z133" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA133" s="42" t="str">
         <f t="shared" si="266"/>
@@ -16502,10 +16511,10 @@
         <v>430</v>
       </c>
       <c r="E134" s="38" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F134" s="39" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G134" s="40" t="s">
         <v>10</v>
@@ -16539,7 +16548,7 @@
         <v>Siderúrgico</v>
       </c>
       <c r="P134" s="57" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q134" s="42" t="str">
         <f t="shared" si="167"/>
@@ -16574,7 +16583,7 @@
         <v>361</v>
       </c>
       <c r="Z134" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA134" s="42" t="str">
         <f t="shared" si="266"/>
@@ -16595,7 +16604,7 @@
         <v>430</v>
       </c>
       <c r="E135" s="38" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F135" s="39" t="s">
         <v>462</v>
@@ -16632,7 +16641,7 @@
         <v>Manufatura</v>
       </c>
       <c r="P135" s="57" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="Q135" s="42" t="str">
         <f t="shared" ref="Q135:Q136" si="267">_xlfn.TRANSLATE(P135,"pt","es")</f>
@@ -16667,7 +16676,7 @@
         <v>361</v>
       </c>
       <c r="Z135" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA135" s="42" t="str">
         <f t="shared" si="266"/>
@@ -16688,10 +16697,10 @@
         <v>430</v>
       </c>
       <c r="E136" s="38" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F136" s="39" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G136" s="40" t="s">
         <v>10</v>
@@ -16725,7 +16734,7 @@
         <v>Oficina</v>
       </c>
       <c r="P136" s="57" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="Q136" s="42" t="str">
         <f t="shared" si="267"/>
@@ -16760,7 +16769,7 @@
         <v>361</v>
       </c>
       <c r="Z136" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA136" s="42" t="str">
         <f t="shared" si="266"/>
@@ -16781,10 +16790,10 @@
         <v>430</v>
       </c>
       <c r="E137" s="38" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F137" s="39" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G137" s="40" t="s">
         <v>10</v>
@@ -16818,7 +16827,7 @@
         <v>Oficina de Pintura</v>
       </c>
       <c r="P137" s="57" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="Q137" s="42" t="str">
         <f t="shared" si="167"/>
@@ -16853,7 +16862,7 @@
         <v>361</v>
       </c>
       <c r="Z137" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA137" s="42" t="str">
         <f t="shared" si="258"/>
@@ -16871,13 +16880,13 @@
         <v>425</v>
       </c>
       <c r="D138" s="38" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E138" s="38" t="s">
         <v>345</v>
       </c>
       <c r="F138" s="39" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="G138" s="40" t="s">
         <v>10</v>
@@ -16911,7 +16920,7 @@
         <v>HIS</v>
       </c>
       <c r="P138" s="42" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="Q138" s="42" t="str">
         <f t="shared" si="167"/>
@@ -16946,7 +16955,7 @@
         <v>362</v>
       </c>
       <c r="Z138" s="43" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="AA138" s="42" t="str">
         <f t="shared" si="258"/>
@@ -16964,7 +16973,7 @@
         <v>425</v>
       </c>
       <c r="D139" s="38" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E139" s="38" t="s">
         <v>345</v>
@@ -17039,7 +17048,7 @@
         <v>362</v>
       </c>
       <c r="Z139" s="43" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="AA139" s="42" t="str">
         <f t="shared" ref="AA139" si="278">_xlfn.TRANSLATE(P139,"pt","en")</f>
@@ -17057,7 +17066,7 @@
         <v>425</v>
       </c>
       <c r="D140" s="38" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E140" s="38" t="s">
         <v>345</v>
@@ -17132,7 +17141,7 @@
         <v>362</v>
       </c>
       <c r="Z140" s="43" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="AA140" s="42" t="str">
         <f t="shared" ref="AA140" si="288">_xlfn.TRANSLATE(P140,"pt","en")</f>
@@ -17150,7 +17159,7 @@
         <v>425</v>
       </c>
       <c r="D141" s="38" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E141" s="38" t="s">
         <v>345</v>
@@ -17225,7 +17234,7 @@
         <v>362</v>
       </c>
       <c r="Z141" s="43" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="AA141" s="42" t="str">
         <f t="shared" ref="AA141" si="297">_xlfn.TRANSLATE(P141,"pt","en")</f>
@@ -17243,7 +17252,7 @@
         <v>425</v>
       </c>
       <c r="D142" s="38" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E142" s="38" t="s">
         <v>345</v>
@@ -17318,7 +17327,7 @@
         <v>362</v>
       </c>
       <c r="Z142" s="43" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="AA142" s="42" t="str">
         <f t="shared" si="258"/>
@@ -18062,7 +18071,7 @@
         <v>363</v>
       </c>
       <c r="Z150" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA150" s="42" t="str">
         <f t="shared" si="258"/>
@@ -18155,7 +18164,7 @@
         <v>364</v>
       </c>
       <c r="Z151" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA151" s="42" t="str">
         <f t="shared" si="258"/>
@@ -18248,7 +18257,7 @@
         <v>365</v>
       </c>
       <c r="Z152" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA152" s="42" t="str">
         <f t="shared" si="258"/>
@@ -18341,7 +18350,7 @@
         <v>366</v>
       </c>
       <c r="Z153" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA153" s="42" t="str">
         <f t="shared" si="258"/>
@@ -18434,7 +18443,7 @@
         <v>367</v>
       </c>
       <c r="Z154" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA154" s="42" t="str">
         <f t="shared" si="258"/>
@@ -18527,7 +18536,7 @@
         <v>368</v>
       </c>
       <c r="Z155" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA155" s="42" t="str">
         <f t="shared" si="258"/>
@@ -18620,7 +18629,7 @@
         <v>369</v>
       </c>
       <c r="Z156" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA156" s="42" t="str">
         <f t="shared" si="258"/>
@@ -18713,7 +18722,7 @@
         <v>370</v>
       </c>
       <c r="Z157" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA157" s="42" t="str">
         <f t="shared" si="258"/>
@@ -18806,7 +18815,7 @@
         <v>371</v>
       </c>
       <c r="Z158" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA158" s="42" t="str">
         <f t="shared" si="258"/>
@@ -18899,7 +18908,7 @@
         <v>373</v>
       </c>
       <c r="Z159" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA159" s="42" t="str">
         <f t="shared" ref="AA159" si="324">_xlfn.TRANSLATE(P159,"pt","en")</f>
@@ -18992,7 +19001,7 @@
         <v>372</v>
       </c>
       <c r="Z160" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA160" s="42" t="str">
         <f t="shared" si="258"/>
@@ -19016,7 +19025,7 @@
         <v>270</v>
       </c>
       <c r="F161" s="39" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G161" s="40" t="s">
         <v>10</v>
@@ -19031,7 +19040,7 @@
         <v>10</v>
       </c>
       <c r="K161" s="45" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="L161" s="41" t="str">
         <f t="shared" si="218"/>
@@ -19050,7 +19059,7 @@
         <v>Zona de Biossegurança</v>
       </c>
       <c r="P161" s="42" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="Q161" s="42" t="str">
         <f t="shared" ref="Q161:Q173" si="325">_xlfn.TRANSLATE(P161,"pt","es")</f>
@@ -19085,7 +19094,7 @@
         <v>371</v>
       </c>
       <c r="Z161" s="43" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AA161" s="42" t="str">
         <f t="shared" si="258"/>
@@ -19103,7 +19112,7 @@
         <v>425</v>
       </c>
       <c r="D162" s="38" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E162" s="38" t="s">
         <v>408</v>
@@ -19143,7 +19152,7 @@
         <v>Sol</v>
       </c>
       <c r="P162" s="42" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="Q162" s="42" t="str">
         <f t="shared" si="325"/>
@@ -19196,7 +19205,7 @@
         <v>425</v>
       </c>
       <c r="D163" s="38" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E163" s="38" t="s">
         <v>408</v>
@@ -19236,7 +19245,7 @@
         <v>Sol Percurso 1</v>
       </c>
       <c r="P163" s="42" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="Q163" s="42" t="str">
         <f t="shared" si="325"/>
@@ -19289,7 +19298,7 @@
         <v>425</v>
       </c>
       <c r="D164" s="38" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E164" s="38" t="s">
         <v>408</v>
@@ -19329,7 +19338,7 @@
         <v>Sol Percurso 2</v>
       </c>
       <c r="P164" s="42" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="Q164" s="42" t="str">
         <f t="shared" si="325"/>
@@ -19382,7 +19391,7 @@
         <v>425</v>
       </c>
       <c r="D165" s="38" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E165" s="38" t="s">
         <v>408</v>
@@ -19422,7 +19431,7 @@
         <v>Sol Texto Amanhecer</v>
       </c>
       <c r="P165" s="42" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="Q165" s="42" t="str">
         <f t="shared" si="325"/>
@@ -19475,7 +19484,7 @@
         <v>425</v>
       </c>
       <c r="D166" s="38" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E166" s="38" t="s">
         <v>408</v>
@@ -19515,7 +19524,7 @@
         <v>Sol Texto Anoitecer</v>
       </c>
       <c r="P166" s="42" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="Q166" s="42" t="str">
         <f t="shared" si="325"/>
@@ -19568,7 +19577,7 @@
         <v>425</v>
       </c>
       <c r="D167" s="38" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E167" s="38" t="s">
         <v>408</v>
@@ -19608,7 +19617,7 @@
         <v>Sol Estudo</v>
       </c>
       <c r="P167" s="42" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="Q167" s="42" t="str">
         <f t="shared" si="325"/>
@@ -19661,7 +19670,7 @@
         <v>425</v>
       </c>
       <c r="D168" s="38" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E168" s="38" t="s">
         <v>408</v>
@@ -19701,7 +19710,7 @@
         <v>Sol Superfície</v>
       </c>
       <c r="P168" s="42" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="Q168" s="42" t="str">
         <f t="shared" si="325"/>
@@ -19754,7 +19763,7 @@
         <v>425</v>
       </c>
       <c r="D169" s="38" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E169" s="38" t="s">
         <v>340</v>
@@ -19794,7 +19803,7 @@
         <v>Orientação Norte</v>
       </c>
       <c r="P169" s="42" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="Q169" s="42" t="str">
         <f t="shared" si="325"/>
@@ -19847,7 +19856,7 @@
         <v>425</v>
       </c>
       <c r="D170" s="38" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E170" s="38" t="s">
         <v>340</v>
@@ -19887,7 +19896,7 @@
         <v>Orientação Sul</v>
       </c>
       <c r="P170" s="42" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="Q170" s="42" t="str">
         <f t="shared" si="325"/>
@@ -19940,7 +19949,7 @@
         <v>425</v>
       </c>
       <c r="D171" s="38" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E171" s="38" t="s">
         <v>340</v>
@@ -19980,7 +19989,7 @@
         <v>Orientação Leste</v>
       </c>
       <c r="P171" s="42" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="Q171" s="42" t="str">
         <f t="shared" si="325"/>
@@ -20033,7 +20042,7 @@
         <v>425</v>
       </c>
       <c r="D172" s="38" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E172" s="38" t="s">
         <v>340</v>
@@ -20073,7 +20082,7 @@
         <v>Orientação Oeste</v>
       </c>
       <c r="P172" s="42" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="Q172" s="42" t="str">
         <f t="shared" si="325"/>
@@ -20126,7 +20135,7 @@
         <v>425</v>
       </c>
       <c r="D173" s="38" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E173" s="38" t="s">
         <v>340</v>
@@ -20224,16 +20233,16 @@
     <cfRule type="duplicateValues" dxfId="51" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="50" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="49"/>
     <cfRule type="duplicateValues" dxfId="49" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F17">
     <cfRule type="duplicateValues" dxfId="47" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="61"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F121 F138:F161">
     <cfRule type="duplicateValues" dxfId="42" priority="602"/>
@@ -20242,36 +20251,36 @@
     <cfRule type="duplicateValues" dxfId="41" priority="605"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18:F121">
-    <cfRule type="duplicateValues" dxfId="40" priority="585"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="586"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="587"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="588"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="588"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="587"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="586"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="585"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F122:F137">
-    <cfRule type="duplicateValues" dxfId="36" priority="441"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="442"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="445"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="444"/>
     <cfRule type="duplicateValues" dxfId="34" priority="443"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="444"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="445"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="442"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="441"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F162:F168">
-    <cfRule type="duplicateValues" dxfId="31" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="44"/>
-    <cfRule type="containsText" dxfId="26" priority="45" operator="containsText" text="null">
+    <cfRule type="duplicateValues" dxfId="31" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="44"/>
+    <cfRule type="containsText" dxfId="29" priority="45" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",F162)))</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="25" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F169:F173">
-    <cfRule type="duplicateValues" dxfId="24" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="14"/>
     <cfRule type="duplicateValues" dxfId="21" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L138:P160">
     <cfRule type="cellIs" dxfId="18" priority="5" operator="equal">
@@ -20284,22 +20293,22 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P132:P137">
-    <cfRule type="duplicateValues" dxfId="16" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="25"/>
     <cfRule type="duplicateValues" dxfId="14" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="X162:X168">
-    <cfRule type="duplicateValues" dxfId="11" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="35"/>
-    <cfRule type="containsText" dxfId="6" priority="36" operator="containsText" text="null">
+    <cfRule type="duplicateValues" dxfId="11" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="37"/>
+    <cfRule type="containsText" dxfId="9" priority="36" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",X162)))</formula>
     </cfRule>
-    <cfRule type="duplicateValues" dxfId="5" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="X169:Y173 AA169:XFD173">
     <cfRule type="cellIs" dxfId="4" priority="9" operator="equal">
@@ -20633,14 +20642,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F4F343-F8A9-4565-8E75-460BD2B52D7E}">
   <sheetPr codeName="Planilha5"/>
-  <dimension ref="A1:AA45"/>
+  <dimension ref="A1:AE46"/>
   <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.765625" style="64" customWidth="1"/>
     <col min="2" max="2" width="9.3046875" style="52" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.3828125" style="50" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.84375" style="50" customWidth="1"/>
-    <col min="5" max="5" width="6" style="50" customWidth="1"/>
+    <col min="5" max="5" width="7.921875" style="50" customWidth="1"/>
     <col min="6" max="6" width="5.84375" style="50" customWidth="1"/>
     <col min="7" max="7" width="5.07421875" style="50" customWidth="1"/>
     <col min="8" max="8" width="7.53515625" style="50" bestFit="1" customWidth="1"/>
@@ -20659,14 +20668,18 @@
     <col min="21" max="21" width="25.3828125" style="50" customWidth="1"/>
     <col min="22" max="22" width="5.69140625" style="50" customWidth="1"/>
     <col min="23" max="23" width="11" style="50" customWidth="1"/>
-    <col min="24" max="24" width="5.69140625" style="50" customWidth="1"/>
+    <col min="24" max="24" width="9.07421875" style="50" customWidth="1"/>
     <col min="25" max="25" width="12.69140625" style="50" customWidth="1"/>
     <col min="26" max="26" width="2.3828125" style="50" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="12.765625" style="50" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.3046875" style="50"/>
+    <col min="28" max="28" width="4.07421875" style="50" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.53515625" style="50" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.53515625" style="50" customWidth="1"/>
+    <col min="31" max="31" width="7.53515625" style="50" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.3046875" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="20.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:31" ht="20.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="62" t="s">
         <v>11</v>
       </c>
@@ -20748,8 +20761,20 @@
       <c r="AA1" s="24" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="2" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB1" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC1" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD1" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE1" s="24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="63">
         <v>1</v>
       </c>
@@ -20757,7 +20782,7 @@
         <v>101</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D2" s="48" t="s">
         <v>82</v>
@@ -20799,7 +20824,7 @@
         <v>77</v>
       </c>
       <c r="Q2" s="25" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="R2" s="33" t="s">
         <v>10</v>
@@ -20820,33 +20845,45 @@
         <v>10</v>
       </c>
       <c r="X2" s="33" t="s">
-        <v>495</v>
+        <v>732</v>
       </c>
       <c r="Y2" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z2" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA2" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA2" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB2" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC2" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD2" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE2" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="63">
         <v>2</v>
       </c>
       <c r="B3" s="51" t="s">
-        <v>275</v>
-      </c>
-      <c r="C3" s="47" t="s">
-        <v>381</v>
+        <v>99</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>382</v>
       </c>
       <c r="D3" s="48" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="E3" s="49" t="s">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="F3" s="48" t="s">
         <v>10</v>
@@ -20858,7 +20895,7 @@
         <v>78</v>
       </c>
       <c r="I3" s="26" t="s">
-        <v>286</v>
+        <v>109</v>
       </c>
       <c r="J3" s="33" t="s">
         <v>96</v>
@@ -20867,22 +20904,22 @@
         <v>97</v>
       </c>
       <c r="L3" s="33" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="M3" s="26" t="s">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="N3" s="33" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="O3" s="26" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="P3" s="33" t="s">
         <v>77</v>
       </c>
       <c r="Q3" s="26" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="R3" s="33" t="s">
         <v>10</v>
@@ -20903,27 +20940,39 @@
         <v>10</v>
       </c>
       <c r="X3" s="33" t="s">
-        <v>495</v>
+        <v>732</v>
       </c>
       <c r="Y3" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z3" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA3" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA3" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB3" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC3" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD3" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE3" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="63">
         <v>3</v>
       </c>
       <c r="B4" s="51" t="s">
-        <v>440</v>
-      </c>
-      <c r="C4" s="38" t="s">
-        <v>192</v>
+        <v>275</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>381</v>
       </c>
       <c r="D4" s="48" t="s">
         <v>82</v>
@@ -20932,16 +20981,16 @@
         <v>101</v>
       </c>
       <c r="F4" s="48" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="G4" s="49" t="s">
-        <v>119</v>
+        <v>10</v>
       </c>
       <c r="H4" s="33" t="s">
         <v>78</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>444</v>
+        <v>286</v>
       </c>
       <c r="J4" s="33" t="s">
         <v>96</v>
@@ -20965,45 +21014,57 @@
         <v>77</v>
       </c>
       <c r="Q4" s="26" t="s">
-        <v>448</v>
+        <v>286</v>
       </c>
       <c r="R4" s="33" t="s">
-        <v>287</v>
+        <v>10</v>
       </c>
       <c r="S4" s="26" t="s">
-        <v>727</v>
+        <v>10</v>
       </c>
       <c r="T4" s="33" t="s">
-        <v>494</v>
+        <v>10</v>
       </c>
       <c r="U4" s="26" t="s">
-        <v>452</v>
+        <v>10</v>
       </c>
       <c r="V4" s="33" t="s">
-        <v>288</v>
+        <v>10</v>
       </c>
       <c r="W4" s="26" t="s">
-        <v>728</v>
+        <v>10</v>
       </c>
       <c r="X4" s="33" t="s">
-        <v>495</v>
+        <v>732</v>
       </c>
       <c r="Y4" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z4" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA4" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA4" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB4" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC4" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD4" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE4" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="63">
         <v>4</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C5" s="38" t="s">
         <v>192</v>
@@ -21024,7 +21085,7 @@
         <v>78</v>
       </c>
       <c r="I5" s="26" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="J5" s="33" t="s">
         <v>96</v>
@@ -21048,13 +21109,13 @@
         <v>77</v>
       </c>
       <c r="Q5" s="26" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="R5" s="33" t="s">
         <v>287</v>
       </c>
       <c r="S5" s="26" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="T5" s="33" t="s">
         <v>494</v>
@@ -21066,27 +21127,39 @@
         <v>288</v>
       </c>
       <c r="W5" s="26" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="X5" s="33" t="s">
-        <v>495</v>
+        <v>732</v>
       </c>
       <c r="Y5" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z5" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA5" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA5" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB5" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC5" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD5" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE5" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="63">
         <v>5</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>192</v>
@@ -21107,7 +21180,7 @@
         <v>78</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="J6" s="33" t="s">
         <v>96</v>
@@ -21131,13 +21204,13 @@
         <v>77</v>
       </c>
       <c r="Q6" s="26" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="R6" s="33" t="s">
         <v>287</v>
       </c>
       <c r="S6" s="26" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="T6" s="33" t="s">
         <v>494</v>
@@ -21149,27 +21222,39 @@
         <v>288</v>
       </c>
       <c r="W6" s="26" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="X6" s="33" t="s">
-        <v>495</v>
+        <v>732</v>
       </c>
       <c r="Y6" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z6" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA6" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA6" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB6" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC6" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD6" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE6" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="63">
         <v>6</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C7" s="38" t="s">
         <v>192</v>
@@ -21190,7 +21275,7 @@
         <v>78</v>
       </c>
       <c r="I7" s="26" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="J7" s="33" t="s">
         <v>96</v>
@@ -21214,13 +21299,13 @@
         <v>77</v>
       </c>
       <c r="Q7" s="26" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="R7" s="33" t="s">
         <v>287</v>
       </c>
       <c r="S7" s="26" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="T7" s="33" t="s">
         <v>494</v>
@@ -21232,48 +21317,60 @@
         <v>288</v>
       </c>
       <c r="W7" s="26" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="X7" s="33" t="s">
-        <v>495</v>
+        <v>732</v>
       </c>
       <c r="Y7" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z7" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA7" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA7" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB7" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC7" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD7" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE7" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="63">
         <v>7</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="C8" s="39" t="s">
-        <v>382</v>
+        <v>443</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>192</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="E8" s="49" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="F8" s="48" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="G8" s="49" t="s">
-        <v>10</v>
+        <v>119</v>
       </c>
       <c r="H8" s="33" t="s">
         <v>78</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>109</v>
+        <v>447</v>
       </c>
       <c r="J8" s="33" t="s">
         <v>96</v>
@@ -21282,55 +21379,67 @@
         <v>97</v>
       </c>
       <c r="L8" s="33" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="M8" s="26" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="N8" s="33" t="s">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="O8" s="26" t="s">
-        <v>109</v>
+        <v>10</v>
       </c>
       <c r="P8" s="33" t="s">
         <v>77</v>
       </c>
       <c r="Q8" s="26" t="s">
-        <v>290</v>
+        <v>451</v>
       </c>
       <c r="R8" s="33" t="s">
-        <v>10</v>
+        <v>287</v>
       </c>
       <c r="S8" s="26" t="s">
-        <v>10</v>
+        <v>726</v>
       </c>
       <c r="T8" s="33" t="s">
-        <v>10</v>
+        <v>494</v>
       </c>
       <c r="U8" s="26" t="s">
-        <v>10</v>
+        <v>452</v>
       </c>
       <c r="V8" s="33" t="s">
-        <v>10</v>
+        <v>288</v>
       </c>
       <c r="W8" s="26" t="s">
-        <v>10</v>
+        <v>727</v>
       </c>
       <c r="X8" s="33" t="s">
-        <v>495</v>
+        <v>732</v>
       </c>
       <c r="Y8" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z8" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA8" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA8" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB8" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC8" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD8" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE8" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="63">
         <v>8</v>
       </c>
@@ -21341,10 +21450,10 @@
         <v>381</v>
       </c>
       <c r="D9" s="48" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="E9" s="49" t="s">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="F9" s="48" t="s">
         <v>10</v>
@@ -21401,19 +21510,31 @@
         <v>10</v>
       </c>
       <c r="X9" s="33" t="s">
-        <v>495</v>
+        <v>732</v>
       </c>
       <c r="Y9" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z9" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA9" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA9" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB9" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC9" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD9" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE9" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="63">
         <v>9</v>
       </c>
@@ -21424,10 +21545,10 @@
         <v>381</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="E10" s="49" t="s">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="F10" s="48" t="s">
         <v>10</v>
@@ -21484,19 +21605,31 @@
         <v>10</v>
       </c>
       <c r="X10" s="33" t="s">
-        <v>495</v>
+        <v>732</v>
       </c>
       <c r="Y10" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z10" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA10" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA10" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB10" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC10" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD10" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE10" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="63">
         <v>10</v>
       </c>
@@ -21507,10 +21640,10 @@
         <v>381</v>
       </c>
       <c r="D11" s="48" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="E11" s="49" t="s">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="F11" s="48" t="s">
         <v>10</v>
@@ -21567,19 +21700,31 @@
         <v>10</v>
       </c>
       <c r="X11" s="33" t="s">
-        <v>495</v>
+        <v>732</v>
       </c>
       <c r="Y11" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z11" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA11" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA11" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB11" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC11" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD11" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE11" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="63">
         <v>11</v>
       </c>
@@ -21590,10 +21735,10 @@
         <v>381</v>
       </c>
       <c r="D12" s="48" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="E12" s="49" t="s">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="F12" s="48" t="s">
         <v>10</v>
@@ -21650,19 +21795,31 @@
         <v>10</v>
       </c>
       <c r="X12" s="33" t="s">
-        <v>495</v>
+        <v>732</v>
       </c>
       <c r="Y12" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z12" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA12" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA12" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB12" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC12" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD12" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE12" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="63">
         <v>12</v>
       </c>
@@ -21673,10 +21830,10 @@
         <v>381</v>
       </c>
       <c r="D13" s="48" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="E13" s="49" t="s">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="F13" s="48" t="s">
         <v>10</v>
@@ -21733,19 +21890,31 @@
         <v>10</v>
       </c>
       <c r="X13" s="33" t="s">
-        <v>495</v>
+        <v>732</v>
       </c>
       <c r="Y13" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z13" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA13" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA13" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB13" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC13" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD13" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE13" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="63">
         <v>13</v>
       </c>
@@ -21756,10 +21925,10 @@
         <v>381</v>
       </c>
       <c r="D14" s="48" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="E14" s="49" t="s">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="F14" s="48" t="s">
         <v>10</v>
@@ -21816,19 +21985,31 @@
         <v>10</v>
       </c>
       <c r="X14" s="33" t="s">
-        <v>495</v>
+        <v>732</v>
       </c>
       <c r="Y14" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z14" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA14" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA14" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB14" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC14" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD14" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE14" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="63">
         <v>14</v>
       </c>
@@ -21884,34 +22065,46 @@
         <v>287</v>
       </c>
       <c r="S15" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T15" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U15" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V15" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W15" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X15" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y15" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V15" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W15" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X15" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y15" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z15" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA15" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA15" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB15" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC15" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD15" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE15" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="63">
         <v>15</v>
       </c>
@@ -21967,34 +22160,46 @@
         <v>287</v>
       </c>
       <c r="S16" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T16" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U16" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V16" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W16" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X16" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y16" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V16" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W16" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X16" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y16" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z16" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA16" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA16" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB16" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC16" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD16" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE16" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="63">
         <v>16</v>
       </c>
@@ -22050,34 +22255,46 @@
         <v>287</v>
       </c>
       <c r="S17" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T17" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U17" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V17" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W17" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X17" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y17" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V17" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W17" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X17" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y17" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z17" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA17" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA17" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB17" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC17" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD17" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE17" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="63">
         <v>17</v>
       </c>
@@ -22133,34 +22350,46 @@
         <v>287</v>
       </c>
       <c r="S18" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T18" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U18" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V18" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W18" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X18" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y18" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V18" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W18" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X18" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y18" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z18" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA18" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA18" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB18" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC18" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD18" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE18" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="63">
         <v>18</v>
       </c>
@@ -22216,34 +22445,46 @@
         <v>287</v>
       </c>
       <c r="S19" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T19" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U19" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V19" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W19" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X19" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y19" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V19" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W19" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X19" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y19" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z19" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA19" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA19" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB19" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC19" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD19" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE19" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="63">
         <v>19</v>
       </c>
@@ -22299,34 +22540,46 @@
         <v>287</v>
       </c>
       <c r="S20" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T20" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U20" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V20" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W20" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X20" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y20" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V20" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W20" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X20" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y20" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z20" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA20" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA20" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB20" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC20" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD20" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE20" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="63">
         <v>20</v>
       </c>
@@ -22382,34 +22635,46 @@
         <v>287</v>
       </c>
       <c r="S21" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T21" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U21" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V21" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W21" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X21" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y21" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V21" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W21" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X21" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y21" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z21" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA21" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA21" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB21" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC21" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD21" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE21" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="63">
         <v>21</v>
       </c>
@@ -22465,34 +22730,46 @@
         <v>287</v>
       </c>
       <c r="S22" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T22" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U22" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V22" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W22" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X22" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y22" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V22" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W22" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X22" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y22" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z22" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA22" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA22" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB22" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC22" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD22" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE22" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="63">
         <v>22</v>
       </c>
@@ -22548,34 +22825,46 @@
         <v>287</v>
       </c>
       <c r="S23" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T23" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U23" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V23" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W23" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X23" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y23" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V23" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W23" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X23" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y23" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z23" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA23" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA23" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB23" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC23" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD23" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE23" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="63">
         <v>23</v>
       </c>
@@ -22631,34 +22920,46 @@
         <v>287</v>
       </c>
       <c r="S24" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T24" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U24" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V24" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W24" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X24" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y24" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V24" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W24" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X24" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y24" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z24" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA24" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA24" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB24" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC24" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD24" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE24" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="63">
         <v>24</v>
       </c>
@@ -22714,34 +23015,46 @@
         <v>287</v>
       </c>
       <c r="S25" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T25" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U25" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V25" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W25" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X25" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y25" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V25" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W25" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X25" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y25" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z25" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA25" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA25" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB25" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC25" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD25" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE25" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="63">
         <v>25</v>
       </c>
@@ -22797,34 +23110,46 @@
         <v>287</v>
       </c>
       <c r="S26" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T26" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U26" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V26" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X26" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y26" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V26" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W26" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X26" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y26" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z26" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA26" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA26" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB26" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD26" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE26" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="63">
         <v>26</v>
       </c>
@@ -22880,34 +23205,46 @@
         <v>287</v>
       </c>
       <c r="S27" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T27" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U27" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V27" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W27" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X27" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y27" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V27" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W27" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X27" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y27" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z27" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA27" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA27" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB27" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC27" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD27" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE27" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="63">
         <v>27</v>
       </c>
@@ -22963,34 +23300,46 @@
         <v>287</v>
       </c>
       <c r="S28" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T28" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U28" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V28" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W28" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X28" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y28" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V28" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W28" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X28" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y28" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z28" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA28" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA28" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB28" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC28" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD28" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE28" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="63">
         <v>28</v>
       </c>
@@ -23046,34 +23395,46 @@
         <v>287</v>
       </c>
       <c r="S29" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T29" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U29" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V29" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W29" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X29" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y29" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V29" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W29" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X29" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y29" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z29" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA29" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA29" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB29" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC29" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD29" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE29" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="63">
         <v>29</v>
       </c>
@@ -23129,34 +23490,46 @@
         <v>287</v>
       </c>
       <c r="S30" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T30" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U30" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V30" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W30" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X30" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y30" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V30" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W30" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X30" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y30" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z30" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA30" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA30" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB30" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC30" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD30" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE30" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="63">
         <v>30</v>
       </c>
@@ -23212,34 +23585,46 @@
         <v>287</v>
       </c>
       <c r="S31" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T31" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U31" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V31" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W31" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X31" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y31" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V31" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W31" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X31" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y31" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z31" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA31" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA31" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB31" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC31" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD31" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE31" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="63">
         <v>31</v>
       </c>
@@ -23295,34 +23680,46 @@
         <v>287</v>
       </c>
       <c r="S32" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T32" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U32" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V32" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W32" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X32" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y32" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V32" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W32" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X32" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y32" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z32" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA32" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA32" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB32" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC32" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD32" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE32" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="63">
         <v>32</v>
       </c>
@@ -23378,34 +23775,46 @@
         <v>287</v>
       </c>
       <c r="S33" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T33" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U33" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V33" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W33" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X33" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y33" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V33" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W33" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X33" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y33" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z33" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA33" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA33" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB33" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC33" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD33" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE33" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="63">
         <v>33</v>
       </c>
@@ -23461,34 +23870,46 @@
         <v>287</v>
       </c>
       <c r="S34" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T34" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U34" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V34" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W34" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X34" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y34" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V34" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W34" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X34" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y34" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z34" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA34" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA34" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB34" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC34" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD34" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE34" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="63">
         <v>34</v>
       </c>
@@ -23544,34 +23965,46 @@
         <v>287</v>
       </c>
       <c r="S35" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T35" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U35" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V35" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W35" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X35" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y35" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V35" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W35" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X35" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y35" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z35" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA35" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA35" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB35" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC35" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD35" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE35" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="63">
         <v>35</v>
       </c>
@@ -23627,34 +24060,46 @@
         <v>287</v>
       </c>
       <c r="S36" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T36" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U36" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V36" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W36" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X36" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y36" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V36" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W36" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X36" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y36" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z36" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA36" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA36" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB36" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC36" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD36" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE36" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="63">
         <v>36</v>
       </c>
@@ -23710,34 +24155,46 @@
         <v>287</v>
       </c>
       <c r="S37" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T37" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U37" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V37" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W37" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X37" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y37" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V37" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W37" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X37" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y37" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z37" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA37" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA37" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB37" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC37" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD37" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE37" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="63">
         <v>37</v>
       </c>
@@ -23793,34 +24250,46 @@
         <v>287</v>
       </c>
       <c r="S38" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T38" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U38" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V38" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W38" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X38" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y38" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V38" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W38" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X38" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y38" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z38" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA38" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA38" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB38" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC38" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD38" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE38" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="63">
         <v>38</v>
       </c>
@@ -23876,34 +24345,46 @@
         <v>287</v>
       </c>
       <c r="S39" s="26" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="T39" s="33" t="s">
         <v>494</v>
       </c>
       <c r="U39" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="V39" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="W39" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="X39" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y39" s="26" t="s">
         <v>497</v>
       </c>
-      <c r="V39" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="W39" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="X39" s="33" t="s">
-        <v>495</v>
-      </c>
-      <c r="Y39" s="26" t="s">
-        <v>498</v>
-      </c>
       <c r="Z39" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA39" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA39" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="40" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB39" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC39" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD39" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE39" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="63">
         <v>39</v>
       </c>
@@ -23965,28 +24446,40 @@
         <v>494</v>
       </c>
       <c r="U40" s="26" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="V40" s="33" t="s">
         <v>288</v>
       </c>
       <c r="W40" s="26" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="X40" s="33" t="s">
-        <v>495</v>
+        <v>732</v>
       </c>
       <c r="Y40" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z40" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA40" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA40" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="41" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB40" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC40" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD40" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE40" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="63">
         <v>40</v>
       </c>
@@ -23994,7 +24487,7 @@
         <v>319</v>
       </c>
       <c r="C41" s="39" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D41" s="48" t="s">
         <v>82</v>
@@ -24048,28 +24541,40 @@
         <v>494</v>
       </c>
       <c r="U41" s="26" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="V41" s="33" t="s">
         <v>288</v>
       </c>
       <c r="W41" s="26" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="X41" s="33" t="s">
-        <v>495</v>
+        <v>732</v>
       </c>
       <c r="Y41" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z41" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA41" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA41" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="42" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB41" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC41" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD41" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE41" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="63">
         <v>41</v>
       </c>
@@ -24077,7 +24582,7 @@
         <v>386</v>
       </c>
       <c r="C42" s="39" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D42" s="48" t="s">
         <v>82</v>
@@ -24131,28 +24636,40 @@
         <v>494</v>
       </c>
       <c r="U42" s="26" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="V42" s="33" t="s">
         <v>288</v>
       </c>
       <c r="W42" s="26" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="X42" s="33" t="s">
-        <v>495</v>
+        <v>732</v>
       </c>
       <c r="Y42" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z42" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA42" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA42" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="43" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB42" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC42" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD42" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE42" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="63">
         <v>42</v>
       </c>
@@ -24160,7 +24677,7 @@
         <v>387</v>
       </c>
       <c r="C43" s="39" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D43" s="48" t="s">
         <v>82</v>
@@ -24214,28 +24731,40 @@
         <v>494</v>
       </c>
       <c r="U43" s="26" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="V43" s="33" t="s">
         <v>288</v>
       </c>
       <c r="W43" s="26" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="X43" s="33" t="s">
-        <v>495</v>
+        <v>732</v>
       </c>
       <c r="Y43" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z43" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA43" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA43" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="44" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB43" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC43" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD43" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE43" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="63">
         <v>43</v>
       </c>
@@ -24243,7 +24772,7 @@
         <v>388</v>
       </c>
       <c r="C44" s="39" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D44" s="48" t="s">
         <v>82</v>
@@ -24297,28 +24826,40 @@
         <v>494</v>
       </c>
       <c r="U44" s="26" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="V44" s="33" t="s">
         <v>288</v>
       </c>
       <c r="W44" s="26" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="X44" s="33" t="s">
-        <v>495</v>
+        <v>732</v>
       </c>
       <c r="Y44" s="26" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Z44" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA44" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA44" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="45" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB44" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC44" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD44" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE44" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="63">
         <v>44</v>
       </c>
@@ -24326,7 +24867,7 @@
         <v>389</v>
       </c>
       <c r="C45" s="39" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D45" s="48" t="s">
         <v>82</v>
@@ -24380,25 +24921,132 @@
         <v>494</v>
       </c>
       <c r="U45" s="26" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="V45" s="33" t="s">
         <v>288</v>
       </c>
       <c r="W45" s="26" t="s">
+        <v>728</v>
+      </c>
+      <c r="X45" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y45" s="26" t="s">
+        <v>497</v>
+      </c>
+      <c r="Z45" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA45" s="26" t="s">
+        <v>724</v>
+      </c>
+      <c r="AB45" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC45" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD45" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE45" s="26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="63">
+        <v>45</v>
+      </c>
+      <c r="B46" s="51" t="s">
         <v>729</v>
       </c>
-      <c r="X45" s="33" t="s">
+      <c r="C46" s="39" t="s">
+        <v>687</v>
+      </c>
+      <c r="D46" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="E46" s="49" t="s">
+        <v>130</v>
+      </c>
+      <c r="F46" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="H46" s="33" t="s">
+        <v>320</v>
+      </c>
+      <c r="I46" s="26" t="s">
+        <v>393</v>
+      </c>
+      <c r="J46" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="K46" s="26" t="s">
+        <v>397</v>
+      </c>
+      <c r="L46" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="M46" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="N46" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="O46" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="P46" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q46" s="26" t="s">
+        <v>399</v>
+      </c>
+      <c r="R46" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="S46" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="T46" s="33" t="s">
+        <v>494</v>
+      </c>
+      <c r="U46" s="26" t="s">
         <v>495</v>
       </c>
-      <c r="Y45" s="26" t="s">
-        <v>498</v>
-      </c>
-      <c r="Z45" s="33" t="s">
+      <c r="V46" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="W46" s="26" t="s">
+        <v>728</v>
+      </c>
+      <c r="X46" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="Y46" s="26" t="s">
+        <v>497</v>
+      </c>
+      <c r="Z46" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AA46" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="AA45" s="26" t="s">
-        <v>725</v>
+      <c r="AB46" s="33" t="s">
+        <v>730</v>
+      </c>
+      <c r="AC46" s="26" t="s">
+        <v>731</v>
+      </c>
+      <c r="AD46" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="AE46" s="26">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Versão5/AMBI/Ontologia_AMBIENTES.xlsx
+++ b/Versão5/AMBI/Ontologia_AMBIENTES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="EstaPastaDeTrabalho"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\AMBI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15491EAA-8657-460C-8A5A-27B51FF17C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71822CEE-330C-40DD-87A7-3741F5E27FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -37,28 +37,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3424,64 +3402,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>9</v>
-    <v>1</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="subType" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
@@ -3801,14 +3721,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.3046875" customWidth="1"/>
-    <col min="2" max="2" width="51.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="56" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" customWidth="1"/>
+    <col min="2" max="2" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="56" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>47</v>
       </c>
@@ -3819,7 +3739,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>49</v>
       </c>
@@ -3830,7 +3750,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>51</v>
       </c>
@@ -3841,7 +3761,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
         <v>52</v>
       </c>
@@ -3852,7 +3772,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
         <v>53</v>
       </c>
@@ -3864,7 +3784,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
         <v>54</v>
       </c>
@@ -3876,7 +3796,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
         <v>55</v>
       </c>
@@ -3887,7 +3807,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
         <v>57</v>
       </c>
@@ -3898,7 +3818,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
         <v>58</v>
       </c>
@@ -3909,7 +3829,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
         <v>60</v>
       </c>
@@ -3920,7 +3840,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
         <v>62</v>
       </c>
@@ -3931,7 +3851,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>63</v>
       </c>
@@ -3942,7 +3862,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>64</v>
       </c>
@@ -3953,7 +3873,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
         <v>65</v>
       </c>
@@ -3964,7 +3884,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
         <v>66</v>
       </c>
@@ -3975,7 +3895,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
         <v>67</v>
       </c>
@@ -3986,7 +3906,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
         <v>68</v>
       </c>
@@ -3997,19 +3917,19 @@
         <v>283</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
         <v>69</v>
       </c>
       <c r="B18" s="22">
         <f ca="1">NOW()</f>
-        <v>46152.487211111111</v>
+        <v>46156.54499884259</v>
       </c>
       <c r="C18" s="55" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
         <v>315</v>
       </c>
@@ -4020,7 +3940,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
         <v>316</v>
       </c>
@@ -4032,7 +3952,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
         <v>317</v>
       </c>
@@ -4044,7 +3964,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>70</v>
       </c>
@@ -4055,7 +3975,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
         <v>71</v>
       </c>
@@ -4066,7 +3986,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
         <v>72</v>
       </c>
@@ -4077,7 +3997,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
         <v>73</v>
       </c>
@@ -4088,7 +4008,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
         <v>281</v>
       </c>
@@ -4109,36 +4029,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA173"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.23046875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="4.53515625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="7.3828125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.921875" style="14" customWidth="1"/>
-    <col min="5" max="5" width="10.3046875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.69140625" style="14" customWidth="1"/>
-    <col min="7" max="10" width="6.69140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="49.4609375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.84375" style="14" customWidth="1"/>
-    <col min="13" max="13" width="11.07421875" style="13" customWidth="1"/>
-    <col min="14" max="14" width="9.53515625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="12.3046875" style="2" customWidth="1"/>
-    <col min="16" max="16" width="82.4609375" style="14" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="83.84375" style="14" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.15234375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="6.84375" style="2" customWidth="1"/>
-    <col min="20" max="20" width="11.07421875" style="14" customWidth="1"/>
-    <col min="21" max="21" width="12.84375" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.3828125" style="14" customWidth="1"/>
-    <col min="23" max="23" width="7.23046875" style="67" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="4.5703125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="14" customWidth="1"/>
+    <col min="7" max="10" width="6.7109375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="49.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.85546875" style="14" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" style="13" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="12.28515625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="82.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="83.85546875" style="14" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.140625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="6.85546875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="11.140625" style="14" customWidth="1"/>
+    <col min="21" max="21" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.42578125" style="14" customWidth="1"/>
+    <col min="23" max="23" width="7.28515625" style="67" customWidth="1"/>
     <col min="24" max="24" width="26" style="36" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="19.765625" style="36" customWidth="1"/>
-    <col min="26" max="26" width="14.53515625" style="35" customWidth="1"/>
-    <col min="27" max="27" width="70.84375" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.15234375" style="2"/>
+    <col min="25" max="25" width="19.7109375" style="36" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="35" customWidth="1"/>
+    <col min="27" max="27" width="70.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="32" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" s="32" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29">
         <v>0</v>
       </c>
@@ -4221,7 +4141,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="2" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="37">
         <v>2</v>
       </c>
@@ -4314,7 +4234,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="37">
         <v>3</v>
       </c>
@@ -4407,7 +4327,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37">
         <v>4</v>
       </c>
@@ -4500,7 +4420,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>5</v>
       </c>
@@ -4593,7 +4513,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="37">
         <v>6</v>
       </c>
@@ -4686,7 +4606,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="37">
         <v>7</v>
       </c>
@@ -4779,7 +4699,7 @@
         <v>Floor of the building.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="37">
         <v>8</v>
       </c>
@@ -4872,7 +4792,7 @@
         <v>Floor building type.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="37">
         <v>9</v>
       </c>
@@ -4965,7 +4885,7 @@
         <v>Single floor of the building. Floors that are not typical and are custom designed.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="37">
         <v>10</v>
       </c>
@@ -5058,7 +4978,7 @@
         <v>Single floor of the building. Floors that are not typical.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>11</v>
       </c>
@@ -5151,7 +5071,7 @@
         <v>Single floor of the building. In buildings that have concert halls, it is the floor that contains the stage or projection screen.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="37">
         <v>12</v>
       </c>
@@ -5244,7 +5164,7 @@
         <v>Single floor of the building. Identifies the floor that stands out for its double height or some characteristic that makes it unique.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="37">
         <v>13</v>
       </c>
@@ -5337,7 +5257,7 @@
         <v>Technical floor of the building.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="37">
         <v>14</v>
       </c>
@@ -5430,7 +5350,7 @@
         <v>Lower partial floor introduced at the ceiling height of one floor, with access only from the interior of the enclosure.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>15</v>
       </c>
@@ -5523,7 +5443,7 @@
         <v>Access floor to the building.</v>
       </c>
     </row>
-    <row r="16" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="37">
         <v>16</v>
       </c>
@@ -5616,7 +5536,7 @@
         <v>Basement floor of the building.</v>
       </c>
     </row>
-    <row r="17" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>17</v>
       </c>
@@ -5709,7 +5629,7 @@
         <v>Symbolic reference element of the position of each Floor of the project: the floor marker can be declared with a specific type in the category OST_LevelHeads.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="37">
         <v>18</v>
       </c>
@@ -5802,7 +5722,7 @@
         <v>Horizontal plane of the building's foundation blocks.</v>
       </c>
     </row>
-    <row r="19" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>19</v>
       </c>
@@ -5895,7 +5815,7 @@
         <v>Horizontal plane of the foundation piles of the building.</v>
       </c>
     </row>
-    <row r="20" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="37">
         <v>20</v>
       </c>
@@ -5988,7 +5908,7 @@
         <v>Template that defines the upper level of the saturated zone of groundwater or water table.</v>
       </c>
     </row>
-    <row r="21" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="37">
         <v>21</v>
       </c>
@@ -6081,7 +6001,7 @@
         <v>Depth gauge. Can be used to define the upper elevation of an underground project, such as a subway line or urban special installations. Used as a depth penetration reference limit for new projects.</v>
       </c>
     </row>
-    <row r="22" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="37">
         <v>22</v>
       </c>
@@ -6174,7 +6094,7 @@
         <v>Height gauge allowed to perform safe flights with UAS (drones). Established by ANAC (National Civil Aviation Agency). Especially in regions close to airports.</v>
       </c>
     </row>
-    <row r="23" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>23</v>
       </c>
@@ -6267,7 +6187,7 @@
         <v>Gauge that defines the variable levels of a natural body of water, such as the sea or maximum and minimum increases of rivers and lagoons. Reference for projects in coastal or floodable areas.</v>
       </c>
     </row>
-    <row r="24" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>24</v>
       </c>
@@ -6360,7 +6280,7 @@
         <v>Maximum height gauge allowed for buildings in each urban area. Established by municipal laws for land use and occupation. It cannot be exceeded by the project.</v>
       </c>
     </row>
-    <row r="25" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>25</v>
       </c>
@@ -6453,7 +6373,7 @@
         <v>Main Facade Elevation Symbol. Relative to the North of the Revit project. The view marker can be declared with a specific type.</v>
       </c>
     </row>
-    <row r="26" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <v>26</v>
       </c>
@@ -6546,7 +6466,7 @@
         <v>Back Facade Elevation Symbol. Relative to the Main or North Facade of Revit Project. The view marker can be declared with a specific type.</v>
       </c>
     </row>
-    <row r="27" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>27</v>
       </c>
@@ -6639,7 +6559,7 @@
         <v>Right Side Façade Elevation Symbol. Relative to the Main or North Façade of Revit Project. The view marker can be declared with a specific type.</v>
       </c>
     </row>
-    <row r="28" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="37">
         <v>28</v>
       </c>
@@ -6732,7 +6652,7 @@
         <v>Left Side Façade Elevation Symbol. Relative to the Main or North Façade of Revit Project. The view marker can be declared with a specific type.</v>
       </c>
     </row>
-    <row r="29" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>29</v>
       </c>
@@ -6825,7 +6745,7 @@
         <v>Elevation Symbol of a Secondary Facade. Relative to the Main or North Facade of a Revit Project. The view marker can be declared with a specific type.</v>
       </c>
     </row>
-    <row r="30" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="37">
         <v>30</v>
       </c>
@@ -6918,7 +6838,7 @@
         <v>Elevation Symbol of an Interior View defined in the project, for pagination of bathrooms and kitchens, for example: the view marker can be declared with a specific type.</v>
       </c>
     </row>
-    <row r="31" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="37">
         <v>31</v>
       </c>
@@ -7011,7 +6931,7 @@
         <v>Design axes used for column location, symmetries, bodies, etc.</v>
       </c>
     </row>
-    <row r="32" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="37">
         <v>32</v>
       </c>
@@ -7104,7 +7024,7 @@
         <v>Irregularly arranged design axes used for the location of columns, symmetries, bodies, etc.</v>
       </c>
     </row>
-    <row r="33" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>33</v>
       </c>
@@ -7197,7 +7117,7 @@
         <v>Radially arranged design axes used for location of columns, symmetries, bodies, etc.</v>
       </c>
     </row>
-    <row r="34" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="37">
         <v>34</v>
       </c>
@@ -7290,7 +7210,7 @@
         <v>Regularly arranged design axes used for column location, symmetries, bodies, etc.</v>
       </c>
     </row>
-    <row r="35" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>35</v>
       </c>
@@ -7378,12 +7298,12 @@
       <c r="Z35" s="43" t="s">
         <v>407</v>
       </c>
-      <c r="AA35" s="42" t="e" vm="1">
-        <f t="shared" ref="AA35:AA39" si="46">_xlfn.TRANSLATE(P35,"pt","en")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AA35" s="42" t="str">
+        <f t="shared" si="17"/>
+        <v>Design axes arranged in an inclined or triangular manner used to locate columns, symmetries, bodies, etc.</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="37">
         <v>36</v>
       </c>
@@ -7437,22 +7357,22 @@
         <v>344</v>
       </c>
       <c r="Q36" s="42" t="str">
-        <f t="shared" ref="Q36" si="47">_xlfn.TRANSLATE(P36,"pt","es")</f>
+        <f t="shared" ref="Q36" si="46">_xlfn.TRANSLATE(P36,"pt","es")</f>
         <v>Elemento simbólico de referencia de la posición del eje estructural: marcador del eje.</v>
       </c>
       <c r="R36" s="43" t="s">
         <v>10</v>
       </c>
       <c r="S36" s="44" t="str">
-        <f t="shared" ref="S36" si="48">SUBSTITUTE(C36, ".", " ")</f>
+        <f t="shared" ref="S36" si="47">SUBSTITUTE(C36, ".", " ")</f>
         <v>Espacialidade</v>
       </c>
       <c r="T36" s="44" t="str">
-        <f t="shared" ref="T36" si="49">SUBSTITUTE(D36, ".", " ")</f>
+        <f t="shared" ref="T36" si="48">SUBSTITUTE(D36, ".", " ")</f>
         <v>Elementos Estruturantes</v>
       </c>
       <c r="U36" s="44" t="str">
-        <f t="shared" ref="U36" si="50">SUBSTITUTE(E36, ".", " ")</f>
+        <f t="shared" ref="U36" si="49">SUBSTITUTE(E36, ".", " ")</f>
         <v>Eixos Estruturais</v>
       </c>
       <c r="V36" s="42" t="s">
@@ -7472,11 +7392,11 @@
         <v>407</v>
       </c>
       <c r="AA36" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" ref="AA35:AA39" si="50">_xlfn.TRANSLATE(P36,"pt","en")</f>
         <v>Symbolic reference element of the position of the Structural Axis: Axis marker.</v>
       </c>
     </row>
-    <row r="37" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>37</v>
       </c>
@@ -7569,7 +7489,7 @@
         <v>Symbolic reference element of the position of a Main Axial Symmetry Axis of the Building.</v>
       </c>
     </row>
-    <row r="38" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="37">
         <v>38</v>
       </c>
@@ -7658,11 +7578,11 @@
         <v>407</v>
       </c>
       <c r="AA38" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>Symbolic reference element of the position of a Secondary or Local Axial Symmetry Axis of a Part of the Building.</v>
       </c>
     </row>
-    <row r="39" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
         <v>39</v>
       </c>
@@ -7751,11 +7671,11 @@
         <v>571</v>
       </c>
       <c r="AA39" s="42" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>Refers to the Campus-type implantation location where the project is located. Used for urban projects implanted in large Campus-type lots.</v>
       </c>
     </row>
-    <row r="40" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>40</v>
       </c>
@@ -7848,7 +7768,7 @@
         <v>Refers to the location of the Urban Lot type where the project is located. Used for urban projects implemented in normal lots.</v>
       </c>
     </row>
-    <row r="41" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
         <v>41</v>
       </c>
@@ -7941,7 +7861,7 @@
         <v>Delimitation of the Gross Area of the Project implemented.</v>
       </c>
     </row>
-    <row r="42" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="37">
         <v>42</v>
       </c>
@@ -8034,7 +7954,7 @@
         <v>Delimitation of buildable space to implement the project.</v>
       </c>
     </row>
-    <row r="43" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
         <v>43</v>
       </c>
@@ -8127,7 +8047,7 @@
         <v>Delimitation of the Frontal Setback of the Lot.</v>
       </c>
     </row>
-    <row r="44" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="37">
         <v>44</v>
       </c>
@@ -8220,7 +8140,7 @@
         <v>Delimitation of the space of Lot Clearances.</v>
       </c>
     </row>
-    <row r="45" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="37">
         <v>45</v>
       </c>
@@ -8313,7 +8233,7 @@
         <v>Space occupied by buildings neighboring the site of implantation.</v>
       </c>
     </row>
-    <row r="46" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="37">
         <v>46</v>
       </c>
@@ -8406,7 +8326,7 @@
         <v>Outdoor space of an implanted project.</v>
       </c>
     </row>
-    <row r="47" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="37">
         <v>47</v>
       </c>
@@ -8499,7 +8419,7 @@
         <v>Outdoor space covered with water around the implanted building.</v>
       </c>
     </row>
-    <row r="48" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="37">
         <v>48</v>
       </c>
@@ -8592,7 +8512,7 @@
         <v>Outdoor space tree of an implanted project.</v>
       </c>
     </row>
-    <row r="49" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>49</v>
       </c>
@@ -8685,7 +8605,7 @@
         <v>Outdoor space protected by some kind of environmental preservation provision.</v>
       </c>
     </row>
-    <row r="50" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="37">
         <v>50</v>
       </c>
@@ -8778,7 +8698,7 @@
         <v>Dedicated outdoor architectural spaces for Dock-type Loading and Unloading.</v>
       </c>
     </row>
-    <row r="51" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="37">
         <v>51</v>
       </c>
@@ -8871,7 +8791,7 @@
         <v>Dedicated outdoor architectural spaces for temporary storage of patio-type products.</v>
       </c>
     </row>
-    <row r="52" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="37">
         <v>52</v>
       </c>
@@ -8964,7 +8884,7 @@
         <v>Dedicated exterior architectural spaces to use as vehicle parking space, including access.</v>
       </c>
     </row>
-    <row r="53" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="37">
         <v>53</v>
       </c>
@@ -9057,7 +8977,7 @@
         <v>Architectural spaces that have not yet been specified with a defined functionality or that do not yet have a defined class in this Ontology.</v>
       </c>
     </row>
-    <row r="54" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="37">
         <v>54</v>
       </c>
@@ -9150,7 +9070,7 @@
         <v>Architectural spaces that have the function of articulating other environments and areas of a project: They can be Circulations, Halls, Stairs, Elevators, Foyers, Emergency Exits, etc...</v>
       </c>
     </row>
-    <row r="55" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="37">
         <v>55</v>
       </c>
@@ -9243,7 +9163,7 @@
         <v>Architectural spaces that have a vertical passage function for building systems of pipes and ducts.</v>
       </c>
     </row>
-    <row r="56" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="37">
         <v>56</v>
       </c>
@@ -9336,7 +9256,7 @@
         <v>Architectural spaces with specialized acoustic treatment such as recording studios, radio and TV, etc.</v>
       </c>
     </row>
-    <row r="57" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="37">
         <v>57</v>
       </c>
@@ -9429,7 +9349,7 @@
         <v>Architectural spaces with specialized acoustic treatment to eliminate sound reflections (echo).</v>
       </c>
     </row>
-    <row r="58" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="37">
         <v>58</v>
       </c>
@@ -9522,7 +9442,7 @@
         <v>Architectural spaces with specialized acoustic treatment to increase sound reflection time.</v>
       </c>
     </row>
-    <row r="59" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="37">
         <v>59</v>
       </c>
@@ -9615,7 +9535,7 @@
         <v>Architectural spaces sized as large structuring environments of a project, such as cinema audiences, theater, etc.</v>
       </c>
     </row>
-    <row r="60" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="37">
         <v>60</v>
       </c>
@@ -9708,7 +9628,7 @@
         <v>Architectural spaces sized and equipped to exhibit works of art or products, for museums, exhibitions, etc.</v>
       </c>
     </row>
-    <row r="61" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="37">
         <v>61</v>
       </c>
@@ -9801,7 +9721,7 @@
         <v>Architectural spaces sized and equipped to store cultural products such as libraries, newspaper libraries, map libraries, discotheques, media libraries, etc.</v>
       </c>
     </row>
-    <row r="62" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="37">
         <v>62</v>
       </c>
@@ -9894,7 +9814,7 @@
         <v>Architectural spaces sized and equipped to store products at low temperatures, such as Frezzers Architectural Spaces, Refrigerated Architectural Spaces, etc.</v>
       </c>
     </row>
-    <row r="63" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="37">
         <v>63</v>
       </c>
@@ -9987,7 +9907,7 @@
         <v>Architectural spaces sized and equipped for computer servers for virtual telematic activities.</v>
       </c>
     </row>
-    <row r="64" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="37">
         <v>64</v>
       </c>
@@ -10080,7 +10000,7 @@
         <v>Architectural spaces sized and equipped for public service food activities such as restaurants, bars, kiosks, etc.</v>
       </c>
     </row>
-    <row r="65" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="37">
         <v>65</v>
       </c>
@@ -10173,7 +10093,7 @@
         <v>Architectural spaces sized and equipped for Cleaning and Building Maintenance activities, etc.</v>
       </c>
     </row>
-    <row r="66" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="37">
         <v>66</v>
       </c>
@@ -10266,7 +10186,7 @@
         <v>Architectural spaces designed and equipped for the reception, storage and distribution of logistic warehouse-type elements.</v>
       </c>
     </row>
-    <row r="67" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="37">
         <v>67</v>
       </c>
@@ -10359,7 +10279,7 @@
         <v>Architectural spaces sized and equipped for activities that must remain shielded by the use of explosives or radiation emitters.</v>
       </c>
     </row>
-    <row r="68" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="37">
         <v>68</v>
       </c>
@@ -10452,7 +10372,7 @@
         <v>Architectural spaces sized and equipped for activities related to animal manipulation such as vivariums or burial spaces such as cemetery or morgues.</v>
       </c>
     </row>
-    <row r="69" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="37">
         <v>69</v>
       </c>
@@ -10545,7 +10465,7 @@
         <v>Architectural spaces sized and equipped for activities that require quarantine spaces or temporary controls.</v>
       </c>
     </row>
-    <row r="70" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="37">
         <v>70</v>
       </c>
@@ -10638,7 +10558,7 @@
         <v>Architectural spaces sized and equipped for activities or processes related to judicial acts.</v>
       </c>
     </row>
-    <row r="71" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="37">
         <v>71</v>
       </c>
@@ -10731,7 +10651,7 @@
         <v>Architectural spaces sized and equipped for vehicle entry, stay and exit activities.</v>
       </c>
     </row>
-    <row r="72" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="37">
         <v>72</v>
       </c>
@@ -10824,7 +10744,7 @@
         <v>Architectural spaces sized and equipped for sports activities, etc.</v>
       </c>
     </row>
-    <row r="73" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="37">
         <v>73</v>
       </c>
@@ -10912,12 +10832,12 @@
       <c r="Z73" s="43" t="s">
         <v>707</v>
       </c>
-      <c r="AA73" s="42" t="e" vm="1">
+      <c r="AA73" s="42" t="str">
         <f t="shared" si="140"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="74" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <v>Architectural spaces designed and equipped for outdoor or indoor sports activities such as sports courts.</v>
+      </c>
+    </row>
+    <row r="74" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="37">
         <v>74</v>
       </c>
@@ -11010,7 +10930,7 @@
         <v>Architectural spaces designed and equipped for outdoor or indoor water sports activities such as sports pools.</v>
       </c>
     </row>
-    <row r="75" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="37">
         <v>75</v>
       </c>
@@ -11103,7 +11023,7 @@
         <v>Architectural spaces sized and equipped for sports activities of racing on sports tracks.</v>
       </c>
     </row>
-    <row r="76" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="37">
         <v>76</v>
       </c>
@@ -11196,7 +11116,7 @@
         <v>Architectural spaces sized and equipped for the public to see a sporting event like Grandstand.</v>
       </c>
     </row>
-    <row r="77" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="37">
         <v>77</v>
       </c>
@@ -11289,7 +11209,7 @@
         <v>Architectural spaces sized and equipped for sports locker room.</v>
       </c>
     </row>
-    <row r="78" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="37">
         <v>78</v>
       </c>
@@ -11382,7 +11302,7 @@
         <v>Architectural spaces sized and equipped with sanitary parts for male use.</v>
       </c>
     </row>
-    <row r="79" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="37">
         <v>79</v>
       </c>
@@ -11475,7 +11395,7 @@
         <v>Architectural spaces sized and equipped with sanitary parts for male use.</v>
       </c>
     </row>
-    <row r="80" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="37">
         <v>80</v>
       </c>
@@ -11568,7 +11488,7 @@
         <v>Architectural spaces sized and equipped with sanitary parts for common use by women and men.</v>
       </c>
     </row>
-    <row r="81" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="37">
         <v>81</v>
       </c>
@@ -11661,7 +11581,7 @@
         <v>Architectural spaces sized and equipped with sanitary parts for use by people with special needs (PNE).</v>
       </c>
     </row>
-    <row r="82" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="37">
         <v>82</v>
       </c>
@@ -11754,7 +11674,7 @@
         <v>Architectural spaces sized and equipped with sanitary parts of a small bathroom.</v>
       </c>
     </row>
-    <row r="83" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="37">
         <v>83</v>
       </c>
@@ -11847,7 +11767,7 @@
         <v>Architectural spaces sized and equipped for administrative commercial work.</v>
       </c>
     </row>
-    <row r="84" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="37">
         <v>84</v>
       </c>
@@ -11940,7 +11860,7 @@
         <v>Architectural spaces sized and equipped for commercial activities such as buying, selling or exchanging products with public participation. They can be ticket offices or service spaces.</v>
       </c>
     </row>
-    <row r="85" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="37">
         <v>85</v>
       </c>
@@ -12033,7 +11953,7 @@
         <v>Architectural spaces sized and equipped for residential function of Living - Architectural spaces, Balconies, etc.</v>
       </c>
     </row>
-    <row r="86" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="37">
         <v>86</v>
       </c>
@@ -12126,7 +12046,7 @@
         <v>Architectural spaces sized and equipped for intimate residential function - Bedrooms, Dressing rooms, etc.</v>
       </c>
     </row>
-    <row r="87" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="37">
         <v>87</v>
       </c>
@@ -12219,7 +12139,7 @@
         <v>Architectural spaces sized and equipped for residential hygiene function - Bathrooms, toilets, etc.</v>
       </c>
     </row>
-    <row r="88" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="37">
         <v>88</v>
       </c>
@@ -12312,7 +12232,7 @@
         <v>Architectural spaces sized and equipped for residential service function - Areas, Kitchens, etc.</v>
       </c>
     </row>
-    <row r="89" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="37">
         <v>89</v>
       </c>
@@ -12405,7 +12325,7 @@
         <v>Architectural spaces sized and equipped for residential leisure function such as architectural spaces for TV, games, etc.</v>
       </c>
     </row>
-    <row r="90" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="37">
         <v>90</v>
       </c>
@@ -12498,7 +12418,7 @@
         <v>Architectural spaces sized and equipped for residential function of professional activities.</v>
       </c>
     </row>
-    <row r="91" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="37">
         <v>91</v>
       </c>
@@ -12591,7 +12511,7 @@
         <v>Architectural spaces sized and equipped for hospital activity of general health care activities.</v>
       </c>
     </row>
-    <row r="92" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="37">
         <v>92</v>
       </c>
@@ -12684,7 +12604,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out Clinical Analysis activity.</v>
       </c>
     </row>
-    <row r="93" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="37">
         <v>93</v>
       </c>
@@ -12777,7 +12697,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out surgical activity.</v>
       </c>
     </row>
-    <row r="94" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="37">
         <v>94</v>
       </c>
@@ -12870,7 +12790,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out the Inpatient process.</v>
       </c>
     </row>
-    <row r="95" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="37">
         <v>95</v>
       </c>
@@ -12963,7 +12883,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out the Intensive Care Hospitalization process.</v>
       </c>
     </row>
-    <row r="96" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="37">
         <v>96</v>
       </c>
@@ -13056,7 +12976,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to perform Diagnostic Imaging (CT scans, MRIs, Ultrasounds, etc.)</v>
       </c>
     </row>
-    <row r="97" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="37">
         <v>97</v>
       </c>
@@ -13149,7 +13069,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out therapies with patients (physiotherapy, respiratory, etc.).</v>
       </c>
     </row>
-    <row r="98" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="37">
         <v>98</v>
       </c>
@@ -13242,7 +13162,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out Therapeutic activities in Swimming Pool, etc.</v>
       </c>
     </row>
-    <row r="99" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="37">
         <v>99</v>
       </c>
@@ -13335,7 +13255,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to perform Emergency Care.</v>
       </c>
     </row>
-    <row r="100" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="37">
         <v>100</v>
       </c>
@@ -13428,7 +13348,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to perform Patient or Material Screening.</v>
       </c>
     </row>
-    <row r="101" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="37">
         <v>101</v>
       </c>
@@ -13521,7 +13441,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out vehicular movement.</v>
       </c>
     </row>
-    <row r="102" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="37">
         <v>102</v>
       </c>
@@ -13614,7 +13534,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out Waiting activities.</v>
       </c>
     </row>
-    <row r="103" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="37">
         <v>103</v>
       </c>
@@ -13707,7 +13627,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out Medical Consultation activities.</v>
       </c>
     </row>
-    <row r="104" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="37">
         <v>104</v>
       </c>
@@ -13800,7 +13720,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out Nursing activities.</v>
       </c>
     </row>
-    <row r="105" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="37">
         <v>105</v>
       </c>
@@ -13893,7 +13813,7 @@
         <v>Architectural spaces sized and equipped for Low Biohazard Laboratory activity. Basic microbiology practices. No special barriers.</v>
       </c>
     </row>
-    <row r="106" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="37">
         <v>106</v>
       </c>
@@ -13986,7 +13906,7 @@
         <v>Architectural spaces sized and equipped for Moderate Biohazard Laboratory activity. With primary barriers (PPE, sink, decontamination). Restricted access.</v>
       </c>
     </row>
-    <row r="107" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="37">
         <v>107</v>
       </c>
@@ -14079,7 +13999,7 @@
         <v>Architectural spaces sized and equipped for High Biological Risk Laboratory activity. With advanced containment (security cabins, controlled ventilation, water showers). Strict access.</v>
       </c>
     </row>
-    <row r="108" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="37">
         <v>108</v>
       </c>
@@ -14172,7 +14092,7 @@
         <v>Architectural spaces sized and equipped for Very High Biological Risk Laboratory activity. With maximum containment (overalls with filtered air, chemical shower, isolated areas).</v>
       </c>
     </row>
-    <row r="109" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="37">
         <v>109</v>
       </c>
@@ -14265,7 +14185,7 @@
         <v>Architectural spaces sized and equipped for the activity of Vestment of professionals who work in a Biosafety containment environment.</v>
       </c>
     </row>
-    <row r="110" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="37">
         <v>110</v>
       </c>
@@ -14358,7 +14278,7 @@
         <v>Architectural spaces sized and equipped for children's activities.</v>
       </c>
     </row>
-    <row r="111" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="37">
         <v>111</v>
       </c>
@@ -14451,7 +14371,7 @@
         <v>Architectural spaces sized and equipped for Teaching and General Research activities</v>
       </c>
     </row>
-    <row r="112" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="37">
         <v>112</v>
       </c>
@@ -14544,7 +14464,7 @@
         <v>Architectural spaces sized and equipped for Teaching and Artistic Research activities related to plastics, such as painting, sculpture, etc.</v>
       </c>
     </row>
-    <row r="113" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="37">
         <v>113</v>
       </c>
@@ -14637,7 +14557,7 @@
         <v>Architectural spaces sized and equipped for Science Teaching and Research activities.</v>
       </c>
     </row>
-    <row r="114" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="37">
         <v>114</v>
       </c>
@@ -14730,7 +14650,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in technical, graphic, electronic skills, etc.</v>
       </c>
     </row>
-    <row r="115" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="37">
         <v>115</v>
       </c>
@@ -14823,7 +14743,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in Informatics.</v>
       </c>
     </row>
-    <row r="116" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="37">
         <v>116</v>
       </c>
@@ -14916,7 +14836,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in Chemistry.</v>
       </c>
     </row>
-    <row r="117" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="37">
         <v>117</v>
       </c>
@@ -15009,7 +14929,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in Physics.</v>
       </c>
     </row>
-    <row r="118" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="37">
         <v>118</v>
       </c>
@@ -15102,7 +15022,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in Biology.</v>
       </c>
     </row>
-    <row r="119" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="37">
         <v>119</v>
       </c>
@@ -15195,7 +15115,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in Music or Performing Arts.</v>
       </c>
     </row>
-    <row r="120" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="37">
         <v>120</v>
       </c>
@@ -15288,7 +15208,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in robotic fabrication, 3D printing, laser cutting and other fabrication technologies.</v>
       </c>
     </row>
-    <row r="121" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="37">
         <v>121</v>
       </c>
@@ -15381,7 +15301,7 @@
         <v>Architectural spaces sized and equipped for recreational school activities.</v>
       </c>
     </row>
-    <row r="122" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="37">
         <v>122</v>
       </c>
@@ -15474,7 +15394,7 @@
         <v>Architectural spaces sized and equipped for the preparation of artists.</v>
       </c>
     </row>
-    <row r="123" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="37">
         <v>123</v>
       </c>
@@ -15567,7 +15487,7 @@
         <v>Front space of the stage, close to the audience. It integrates architecturally to the scene, fulfilling aesthetic and acoustic functions, also called the stage mouth.</v>
       </c>
     </row>
-    <row r="124" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="37">
         <v>124</v>
       </c>
@@ -15660,7 +15580,7 @@
         <v>Space exposed to spectators, where the actors perform. It can be elevated, flat, rotating, Italian, arena, among other formats.</v>
       </c>
     </row>
-    <row r="125" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="37">
         <v>125</v>
       </c>
@@ -15753,7 +15673,7 @@
         <v>Hidden space and back to the stage, behind the artists' performance area. It can house various scenographic, technical and functional elements to the play.</v>
       </c>
     </row>
-    <row r="126" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="37">
         <v>126</v>
       </c>
@@ -15846,7 +15766,7 @@
         <v>Space lateral to the stage, used for the entry and exit of the artists.</v>
       </c>
     </row>
-    <row r="127" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="37">
         <v>127</v>
       </c>
@@ -15939,7 +15859,7 @@
         <v>Space between the audience and the stage, usually below the stage, to accommodate the orchestra during a musical or dance performance.</v>
       </c>
     </row>
-    <row r="128" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="37">
         <v>128</v>
       </c>
@@ -16032,7 +15952,7 @@
         <v>Space at stage level, where the audience sits with a view of the front of the stage.</v>
       </c>
     </row>
-    <row r="129" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="37">
         <v>129</v>
       </c>
@@ -16125,7 +16045,7 @@
         <v>Space integrated to the audience, but at an upper level where the audience is accommodated with a frontal view of the stage.</v>
       </c>
     </row>
-    <row r="130" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="37">
         <v>130</v>
       </c>
@@ -16218,7 +16138,7 @@
         <v>Space integrated into the concert hall, usually reserved and with better visibility and comfort.</v>
       </c>
     </row>
-    <row r="131" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="37">
         <v>131</v>
       </c>
@@ -16311,7 +16231,7 @@
         <v>Superior space to accommodate the public with more affordable prices.</v>
       </c>
     </row>
-    <row r="132" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="37">
         <v>132</v>
       </c>
@@ -16404,7 +16324,7 @@
         <v>Industrial Space type Large Industrial Building.</v>
       </c>
     </row>
-    <row r="133" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="37">
         <v>133</v>
       </c>
@@ -16497,7 +16417,7 @@
         <v>Industrial Space type Shed.</v>
       </c>
     </row>
-    <row r="134" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="37">
         <v>134</v>
       </c>
@@ -16590,7 +16510,7 @@
         <v>Industrial space sized and equipped with furnaces or heavy equipment for processing metals and alloys.</v>
       </c>
     </row>
-    <row r="135" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="37">
         <v>135</v>
       </c>
@@ -16683,7 +16603,7 @@
         <v>Industrial space sized and equipped as a Production Line of large-scale goods (automobiles, electronics, textiles and food, etc.). It is an assembly line of automated machines</v>
       </c>
     </row>
-    <row r="136" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="37">
         <v>136</v>
       </c>
@@ -16776,7 +16696,7 @@
         <v>Industrial space sized and equipped as a Production Workshop for medium or low scale goods (furniture, equipment, small vehicles, etc.). It is prepared for assembly.</v>
       </c>
     </row>
-    <row r="137" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="37">
         <v>137</v>
       </c>
@@ -16869,7 +16789,7 @@
         <v>Industrial space sized and equipped as a Painting Workshop of medium or low scale goods (furniture, equipment, small vehicles, etc.). It is prepared for assembly.</v>
       </c>
     </row>
-    <row r="138" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="37">
         <v>138</v>
       </c>
@@ -16962,7 +16882,7 @@
         <v>It represents a Housing Unit of Social Interest.</v>
       </c>
     </row>
-    <row r="139" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="37">
         <v>139</v>
       </c>
@@ -17055,7 +16975,7 @@
         <v>Represents an Apartment of residential building.</v>
       </c>
     </row>
-    <row r="140" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="37">
         <v>140</v>
       </c>
@@ -17148,7 +17068,7 @@
         <v>Represents an administrative functional department of an institutional building.</v>
       </c>
     </row>
-    <row r="141" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="37">
         <v>141</v>
       </c>
@@ -17241,7 +17161,7 @@
         <v>It represents an administrative functional division of an institutional building.</v>
       </c>
     </row>
-    <row r="142" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="37">
         <v>142</v>
       </c>
@@ -17334,7 +17254,7 @@
         <v>It represents an administrative functional sector of an institutional building.</v>
       </c>
     </row>
-    <row r="143" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="37">
         <v>143</v>
       </c>
@@ -17427,7 +17347,7 @@
         <v>It represents a Built Block that contains other autonomous units without a specific function.</v>
       </c>
     </row>
-    <row r="144" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="37">
         <v>144</v>
       </c>
@@ -17520,7 +17440,7 @@
         <v>It represents a Built Block that is a House or Individual Residential Unit.</v>
       </c>
     </row>
-    <row r="145" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="37">
         <v>145</v>
       </c>
@@ -17613,7 +17533,7 @@
         <v>It represents a Built Block that contains other autonomous units with a residential function.</v>
       </c>
     </row>
-    <row r="146" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="37">
         <v>146</v>
       </c>
@@ -17706,7 +17626,7 @@
         <v>It represents a Built Block of an Educational Unit.</v>
       </c>
     </row>
-    <row r="147" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="37">
         <v>147</v>
       </c>
@@ -17799,7 +17719,7 @@
         <v>It represents a Built Block of a SUS Health Unit.</v>
       </c>
     </row>
-    <row r="148" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="37">
         <v>148</v>
       </c>
@@ -17892,7 +17812,7 @@
         <v>It represents a Built Block of a Health Unit of the Private Network.</v>
       </c>
     </row>
-    <row r="149" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="37">
         <v>149</v>
       </c>
@@ -17985,7 +17905,7 @@
         <v>It represents a Built Block of a Health Unit of the Private Network contracted with the SUS.</v>
       </c>
     </row>
-    <row r="150" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="37">
         <v>150</v>
       </c>
@@ -18078,7 +17998,7 @@
         <v>Spatial zone is a non-hierarchical and potentially overlapping decomposition of the project under some condition.</v>
       </c>
     </row>
-    <row r="151" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="37">
         <v>151</v>
       </c>
@@ -18171,7 +18091,7 @@
         <v>Space zone is used to represent a construction zone for the manufacturing process.</v>
       </c>
     </row>
-    <row r="152" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="37">
         <v>152</v>
       </c>
@@ -18264,7 +18184,7 @@
         <v>Spatial zone is used to define an interference between occurrences of Ifcspatialelement.</v>
       </c>
     </row>
-    <row r="153" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="37">
         <v>153</v>
       </c>
@@ -18357,7 +18277,7 @@
         <v>Spatial zone is used to represent a particular zone of occupation.</v>
       </c>
     </row>
-    <row r="154" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="37">
         <v>154</v>
       </c>
@@ -18450,7 +18370,7 @@
         <v>A spatial zone that represents some type of reserve within the project for future use.</v>
       </c>
     </row>
-    <row r="155" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="37">
         <v>155</v>
       </c>
@@ -18543,7 +18463,7 @@
         <v>Spatial zone is used to represent an area primarily dedicated to the circulation of people or vehicles.</v>
       </c>
     </row>
-    <row r="156" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="37">
         <v>156</v>
       </c>
@@ -18636,7 +18556,7 @@
         <v>Space zone is used to represent a thermal zone with homogeneous characteristics.</v>
       </c>
     </row>
-    <row r="157" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="37">
         <v>157</v>
       </c>
@@ -18729,7 +18649,7 @@
         <v>Spatial zone is used to represent a lighting zone; a zone of natural light.</v>
       </c>
     </row>
-    <row r="158" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="37">
         <v>158</v>
       </c>
@@ -18822,7 +18742,7 @@
         <v>Spatial zone is used to represent a ventilation zone.</v>
       </c>
     </row>
-    <row r="159" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="37">
         <v>159</v>
       </c>
@@ -18915,7 +18835,7 @@
         <v>Spatial zone is used to represent a zone for planning safety and work, accesses, etc.</v>
       </c>
     </row>
-    <row r="160" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="37">
         <v>160</v>
       </c>
@@ -19008,7 +18928,7 @@
         <v>Space zone is used to represent a fire safety zone, or compartment.</v>
       </c>
     </row>
-    <row r="161" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="37">
         <v>161</v>
       </c>
@@ -19101,7 +19021,7 @@
         <v>Space zone is used to represent a biosecurity zone, typically where ventilation is critical.</v>
       </c>
     </row>
-    <row r="162" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="37">
         <v>162</v>
       </c>
@@ -19194,7 +19114,7 @@
         <v>Solar Heliodom or Analema: sun.</v>
       </c>
     </row>
-    <row r="163" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="37">
         <v>163</v>
       </c>
@@ -19287,7 +19207,7 @@
         <v>Heliodom Solar Analemma: Solar Path 1.</v>
       </c>
     </row>
-    <row r="164" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="37">
         <v>164</v>
       </c>
@@ -19380,7 +19300,7 @@
         <v>Heliodom Solar Analemma: Solar Path 1.</v>
       </c>
     </row>
-    <row r="165" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="37">
         <v>165</v>
       </c>
@@ -19473,7 +19393,7 @@
         <v>Heliodom Dawn: Text from the exit of the sun.</v>
       </c>
     </row>
-    <row r="166" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="37">
         <v>166</v>
       </c>
@@ -19566,7 +19486,7 @@
         <v>Heliodom Nightfall: text from posta do sol.</v>
       </c>
     </row>
-    <row r="167" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="37">
         <v>167</v>
       </c>
@@ -19659,7 +19579,7 @@
         <v>Solar Study Heliodom.</v>
       </c>
     </row>
-    <row r="168" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="37">
         <v>168</v>
       </c>
@@ -19752,7 +19672,7 @@
         <v>Heliodom Surface of the sun.</v>
       </c>
     </row>
-    <row r="169" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="37">
         <v>169</v>
       </c>
@@ -19845,7 +19765,7 @@
         <v>Envelope orientation analysis. North-oriented elements, relative to True or Solar North.</v>
       </c>
     </row>
-    <row r="170" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="37">
         <v>170</v>
       </c>
@@ -19938,7 +19858,7 @@
         <v>Orientation analysis of the Envelope. South-oriented elements, relative to True or Solar North.</v>
       </c>
     </row>
-    <row r="171" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="37">
         <v>171</v>
       </c>
@@ -20031,7 +19951,7 @@
         <v>Envelope orientation analysis. East-facing elements, relative to True North or Solar.</v>
       </c>
     </row>
-    <row r="172" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="37">
         <v>172</v>
       </c>
@@ -20124,7 +20044,7 @@
         <v>Orientation analysis of the Envelope. Elements oriented to the West, relative to True or Solar North.</v>
       </c>
     </row>
-    <row r="173" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="37">
         <v>173</v>
       </c>
@@ -20219,12 +20139,12 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="E18:F24 D25:F121 D138:F161 AA1:AA30 Z7:Z24 AB18:XFD30 L18:P121 X39:XFD110 AA111:XFD121 K161:P161">
+  <conditionalFormatting sqref="E18:F24 D25:F121 D138:F161 AA1:AA30 Z7:Z24 AB18:XFD30 L18:P121 AA111:XFD121 K161:P161 X39:XFD110">
     <cfRule type="cellIs" dxfId="53" priority="65" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E169:F173 A2:A173 B18:B121 X25:Y38 AA31:XFD38 X111:Z137 D122:D137 AA122:AA137 B138:B161 L162:O168 B169:B173 L169:P173">
+  <conditionalFormatting sqref="E169:F173 A2:A173 B18:B121 X25:Y38 X111:Z137 D122:D137 AA122:AA137 B138:B161 L162:O168 B169:B173 L169:P173 AA31:XFD38">
     <cfRule type="cellIs" dxfId="52" priority="29" operator="equal">
       <formula>"null"</formula>
     </cfRule>
@@ -20339,15 +20259,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="10" width="6" style="12" bestFit="1" customWidth="1"/>
     <col min="11" max="21" width="6" style="10" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="10"/>
+    <col min="22" max="16384" width="11.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
@@ -20412,7 +20332,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -20477,7 +20397,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="7">
         <v>3</v>
       </c>
@@ -20552,16 +20472,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B299E44-CC41-4C47-93B0-FF411236635D}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="8.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.15234375" customWidth="1"/>
-    <col min="3" max="3" width="10.69140625" customWidth="1"/>
-    <col min="4" max="4" width="8.3046875" customWidth="1"/>
-    <col min="5" max="5" width="9.84375" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15">
         <v>1</v>
       </c>
@@ -20578,7 +20498,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28">
         <v>2</v>
       </c>
@@ -20595,7 +20515,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="28">
         <v>3</v>
       </c>
@@ -20612,7 +20532,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="28">
         <v>4</v>
       </c>
@@ -20643,43 +20563,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F4F343-F8A9-4565-8E75-460BD2B52D7E}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AE46"/>
-  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.765625" style="64" customWidth="1"/>
-    <col min="2" max="2" width="9.3046875" style="52" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3828125" style="50" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.84375" style="50" customWidth="1"/>
-    <col min="5" max="5" width="7.921875" style="50" customWidth="1"/>
-    <col min="6" max="6" width="5.84375" style="50" customWidth="1"/>
-    <col min="7" max="7" width="5.07421875" style="50" customWidth="1"/>
-    <col min="8" max="8" width="7.53515625" style="50" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.07421875" style="50" customWidth="1"/>
-    <col min="10" max="10" width="8.4609375" style="50" customWidth="1"/>
-    <col min="11" max="11" width="4.69140625" style="50" customWidth="1"/>
-    <col min="12" max="12" width="3.3046875" style="50" customWidth="1"/>
-    <col min="13" max="13" width="5.84375" style="50" customWidth="1"/>
-    <col min="14" max="14" width="8.69140625" style="50" customWidth="1"/>
-    <col min="15" max="15" width="19.84375" style="50" customWidth="1"/>
-    <col min="16" max="16" width="4.53515625" style="50" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" style="64" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="52" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="50" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.85546875" style="50" customWidth="1"/>
+    <col min="5" max="5" width="7.85546875" style="50" customWidth="1"/>
+    <col min="6" max="6" width="5.85546875" style="50" customWidth="1"/>
+    <col min="7" max="7" width="5.140625" style="50" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="50" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.140625" style="50" customWidth="1"/>
+    <col min="10" max="10" width="8.42578125" style="50" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" style="50" customWidth="1"/>
+    <col min="12" max="12" width="3.28515625" style="50" customWidth="1"/>
+    <col min="13" max="13" width="5.85546875" style="50" customWidth="1"/>
+    <col min="14" max="14" width="8.7109375" style="50" customWidth="1"/>
+    <col min="15" max="15" width="19.85546875" style="50" customWidth="1"/>
+    <col min="16" max="16" width="4.5703125" style="50" customWidth="1"/>
     <col min="17" max="17" width="28" style="50" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.69140625" style="50" customWidth="1"/>
-    <col min="19" max="19" width="15.69140625" style="50" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="50" customWidth="1"/>
+    <col min="19" max="19" width="15.7109375" style="50" customWidth="1"/>
     <col min="20" max="20" width="5" style="50" customWidth="1"/>
-    <col min="21" max="21" width="25.3828125" style="50" customWidth="1"/>
-    <col min="22" max="22" width="5.69140625" style="50" customWidth="1"/>
+    <col min="21" max="21" width="25.42578125" style="50" customWidth="1"/>
+    <col min="22" max="22" width="5.7109375" style="50" customWidth="1"/>
     <col min="23" max="23" width="11" style="50" customWidth="1"/>
-    <col min="24" max="24" width="9.07421875" style="50" customWidth="1"/>
-    <col min="25" max="25" width="12.69140625" style="50" customWidth="1"/>
-    <col min="26" max="26" width="2.3828125" style="50" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.765625" style="50" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.07421875" style="50" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.53515625" style="50" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.53515625" style="50" customWidth="1"/>
-    <col min="31" max="31" width="7.53515625" style="50" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.3046875" style="50"/>
+    <col min="24" max="24" width="9.140625" style="50" customWidth="1"/>
+    <col min="25" max="25" width="12.7109375" style="50" customWidth="1"/>
+    <col min="26" max="26" width="2.42578125" style="50" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.7109375" style="50" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.140625" style="50" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.5703125" style="50" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.5703125" style="50" customWidth="1"/>
+    <col min="31" max="31" width="7.5703125" style="50" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.28515625" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="20.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:31" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="62" t="s">
         <v>11</v>
       </c>
@@ -20774,7 +20694,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="63">
         <v>1</v>
       </c>
@@ -20869,7 +20789,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="63">
         <v>2</v>
       </c>
@@ -20964,7 +20884,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="63">
         <v>3</v>
       </c>
@@ -21059,7 +20979,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="63">
         <v>4</v>
       </c>
@@ -21154,7 +21074,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="63">
         <v>5</v>
       </c>
@@ -21249,7 +21169,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="63">
         <v>6</v>
       </c>
@@ -21344,7 +21264,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="63">
         <v>7</v>
       </c>
@@ -21439,7 +21359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="63">
         <v>8</v>
       </c>
@@ -21534,7 +21454,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="63">
         <v>9</v>
       </c>
@@ -21629,7 +21549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="63">
         <v>10</v>
       </c>
@@ -21724,7 +21644,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="63">
         <v>11</v>
       </c>
@@ -21819,7 +21739,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="63">
         <v>12</v>
       </c>
@@ -21914,7 +21834,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="63">
         <v>13</v>
       </c>
@@ -22009,7 +21929,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="63">
         <v>14</v>
       </c>
@@ -22104,7 +22024,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="63">
         <v>15</v>
       </c>
@@ -22199,7 +22119,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="63">
         <v>16</v>
       </c>
@@ -22294,7 +22214,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="63">
         <v>17</v>
       </c>
@@ -22389,7 +22309,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="63">
         <v>18</v>
       </c>
@@ -22484,7 +22404,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="63">
         <v>19</v>
       </c>
@@ -22579,7 +22499,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="63">
         <v>20</v>
       </c>
@@ -22674,7 +22594,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="63">
         <v>21</v>
       </c>
@@ -22769,7 +22689,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="63">
         <v>22</v>
       </c>
@@ -22864,7 +22784,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="63">
         <v>23</v>
       </c>
@@ -22959,7 +22879,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="63">
         <v>24</v>
       </c>
@@ -23054,7 +22974,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="63">
         <v>25</v>
       </c>
@@ -23149,7 +23069,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="63">
         <v>26</v>
       </c>
@@ -23244,7 +23164,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="63">
         <v>27</v>
       </c>
@@ -23339,7 +23259,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="63">
         <v>28</v>
       </c>
@@ -23434,7 +23354,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="63">
         <v>29</v>
       </c>
@@ -23529,7 +23449,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="63">
         <v>30</v>
       </c>
@@ -23624,7 +23544,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="63">
         <v>31</v>
       </c>
@@ -23719,7 +23639,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="63">
         <v>32</v>
       </c>
@@ -23814,7 +23734,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="63">
         <v>33</v>
       </c>
@@ -23909,7 +23829,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="63">
         <v>34</v>
       </c>
@@ -24004,7 +23924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="63">
         <v>35</v>
       </c>
@@ -24099,7 +24019,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="63">
         <v>36</v>
       </c>
@@ -24194,7 +24114,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="63">
         <v>37</v>
       </c>
@@ -24289,7 +24209,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="63">
         <v>38</v>
       </c>
@@ -24384,7 +24304,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="63">
         <v>39</v>
       </c>
@@ -24479,7 +24399,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="63">
         <v>40</v>
       </c>
@@ -24574,7 +24494,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="63">
         <v>41</v>
       </c>
@@ -24669,7 +24589,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="63">
         <v>42</v>
       </c>
@@ -24764,7 +24684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="63">
         <v>43</v>
       </c>
@@ -24859,7 +24779,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="63">
         <v>44</v>
       </c>
@@ -24954,7 +24874,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="63">
         <v>45</v>
       </c>

--- a/Versão5/AMBI/Ontologia_AMBIENTES.xlsx
+++ b/Versão5/AMBI/Ontologia_AMBIENTES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\AMBI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D7417BE-B78D-417B-9E54-5AA6EC36BE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4122CE48-F487-4E27-B384-7B8A408D9E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -3721,14 +3721,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.3046875" customWidth="1"/>
-    <col min="2" max="2" width="51.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="56" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" customWidth="1"/>
+    <col min="2" max="2" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="56" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>47</v>
       </c>
@@ -3739,7 +3739,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>49</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>51</v>
       </c>
@@ -3761,7 +3761,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
         <v>52</v>
       </c>
@@ -3772,7 +3772,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
         <v>53</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
         <v>54</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
         <v>55</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
         <v>57</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
         <v>58</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
         <v>60</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
         <v>62</v>
       </c>
@@ -3851,7 +3851,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>63</v>
       </c>
@@ -3862,7 +3862,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
         <v>64</v>
       </c>
@@ -3873,7 +3873,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
         <v>65</v>
       </c>
@@ -3884,7 +3884,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
         <v>66</v>
       </c>
@@ -3895,7 +3895,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
         <v>67</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
         <v>68</v>
       </c>
@@ -3917,19 +3917,19 @@
         <v>283</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
         <v>69</v>
       </c>
       <c r="B18" s="22">
         <f ca="1">NOW()</f>
-        <v>46192.506090162038</v>
+        <v>46195.504604282411</v>
       </c>
       <c r="C18" s="55" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
         <v>315</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
         <v>316</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
         <v>317</v>
       </c>
@@ -3964,7 +3964,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
         <v>70</v>
       </c>
@@ -3975,7 +3975,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="20" t="s">
         <v>71</v>
       </c>
@@ -3986,7 +3986,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
         <v>72</v>
       </c>
@@ -3997,7 +3997,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
         <v>73</v>
       </c>
@@ -4008,7 +4008,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
         <v>281</v>
       </c>
@@ -4029,36 +4029,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA173"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.3046875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="4.53515625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="7.3828125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.84375" style="14" customWidth="1"/>
-    <col min="5" max="5" width="10.3046875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.69140625" style="14" customWidth="1"/>
-    <col min="7" max="10" width="6.69140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="52" style="2" customWidth="1"/>
-    <col min="12" max="12" width="6.84375" style="14" customWidth="1"/>
-    <col min="13" max="13" width="11.15234375" style="13" customWidth="1"/>
-    <col min="14" max="14" width="9.53515625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="12.3046875" style="2" customWidth="1"/>
-    <col min="16" max="16" width="82.3828125" style="14" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="83.84375" style="14" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.15234375" style="2" customWidth="1"/>
-    <col min="19" max="19" width="6.84375" style="2" customWidth="1"/>
-    <col min="20" max="20" width="11.15234375" style="14" customWidth="1"/>
-    <col min="21" max="21" width="12.84375" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.3828125" style="14" customWidth="1"/>
-    <col min="23" max="23" width="7.3046875" style="67" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="4.5703125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="14" customWidth="1"/>
+    <col min="7" max="10" width="6.7109375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="49.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.85546875" style="14" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" style="13" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="12.28515625" style="2" customWidth="1"/>
+    <col min="16" max="16" width="82.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="83.85546875" style="14" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.140625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="6.85546875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="11.140625" style="14" customWidth="1"/>
+    <col min="21" max="21" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.42578125" style="14" customWidth="1"/>
+    <col min="23" max="23" width="7.28515625" style="67" customWidth="1"/>
     <col min="24" max="24" width="26" style="36" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="19.69140625" style="36" customWidth="1"/>
-    <col min="26" max="26" width="14.53515625" style="35" customWidth="1"/>
-    <col min="27" max="27" width="70.84375" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.15234375" style="2"/>
+    <col min="25" max="25" width="19.7109375" style="36" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="35" customWidth="1"/>
+    <col min="27" max="27" width="70.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="32" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" s="32" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="29">
         <v>0</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="2" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="37">
         <v>2</v>
       </c>
@@ -4234,7 +4234,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="37">
         <v>3</v>
       </c>
@@ -4327,7 +4327,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37">
         <v>4</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>5</v>
       </c>
@@ -4513,7 +4513,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="37">
         <v>6</v>
       </c>
@@ -4606,7 +4606,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="37">
         <v>7</v>
       </c>
@@ -4699,7 +4699,7 @@
         <v>Floor of the building.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="37">
         <v>8</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>Floor building type.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="37">
         <v>9</v>
       </c>
@@ -4885,7 +4885,7 @@
         <v>Single floor of the building. Floors that are not typical and are custom designed.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="37">
         <v>10</v>
       </c>
@@ -4978,7 +4978,7 @@
         <v>Single floor of the building. Floors that are not typical.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>11</v>
       </c>
@@ -5071,7 +5071,7 @@
         <v>Single floor of the building. In buildings that have concert halls, it is the floor that contains the stage or projection screen.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="37">
         <v>12</v>
       </c>
@@ -5164,7 +5164,7 @@
         <v>Single floor of the building. Identifies the floor that stands out for its double height or some characteristic that makes it unique.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="37">
         <v>13</v>
       </c>
@@ -5257,7 +5257,7 @@
         <v>Technical floor of the building.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="37">
         <v>14</v>
       </c>
@@ -5350,7 +5350,7 @@
         <v>Lower partial floor introduced at the ceiling height of one floor, with access only from the interior of the enclosure.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>15</v>
       </c>
@@ -5443,7 +5443,7 @@
         <v>Access floor to the building.</v>
       </c>
     </row>
-    <row r="16" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="37">
         <v>16</v>
       </c>
@@ -5536,7 +5536,7 @@
         <v>Basement floor of the building.</v>
       </c>
     </row>
-    <row r="17" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>17</v>
       </c>
@@ -5629,7 +5629,7 @@
         <v>Symbolic reference element of the position of each Floor of the project: the floor marker can be declared with a specific type in the category OST_LevelHeads.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="37">
         <v>18</v>
       </c>
@@ -5722,7 +5722,7 @@
         <v>Horizontal plane of the building's foundation blocks.</v>
       </c>
     </row>
-    <row r="19" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>19</v>
       </c>
@@ -5815,7 +5815,7 @@
         <v>Horizontal plane of the foundation piles of the building.</v>
       </c>
     </row>
-    <row r="20" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="37">
         <v>20</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>Template that defines the upper level of the saturated zone of groundwater or water table.</v>
       </c>
     </row>
-    <row r="21" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="37">
         <v>21</v>
       </c>
@@ -6001,7 +6001,7 @@
         <v>Depth gauge. Can be used to define the upper elevation of an underground project, such as a subway line or urban special installations. Used as a depth penetration reference limit for new projects.</v>
       </c>
     </row>
-    <row r="22" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="37">
         <v>22</v>
       </c>
@@ -6094,7 +6094,7 @@
         <v>Height gauge allowed to perform safe flights with UAS (drones). Established by ANAC (National Civil Aviation Agency). Especially in regions close to airports.</v>
       </c>
     </row>
-    <row r="23" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>23</v>
       </c>
@@ -6187,7 +6187,7 @@
         <v>Gauge that defines the variable levels of a natural body of water, such as the sea or maximum and minimum increases of rivers and lagoons. Reference for projects in coastal or floodable areas.</v>
       </c>
     </row>
-    <row r="24" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>24</v>
       </c>
@@ -6280,7 +6280,7 @@
         <v>Maximum height gauge allowed for buildings in each urban area. Established by municipal laws for land use and occupation. It cannot be exceeded by the project.</v>
       </c>
     </row>
-    <row r="25" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>25</v>
       </c>
@@ -6373,7 +6373,7 @@
         <v>Main Facade Elevation Symbol. Relative to the North of the Revit project. The view marker can be declared with a specific type.</v>
       </c>
     </row>
-    <row r="26" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <v>26</v>
       </c>
@@ -6466,7 +6466,7 @@
         <v>Back Facade Elevation Symbol. Relative to the Main or North Facade of Revit Project. The view marker can be declared with a specific type.</v>
       </c>
     </row>
-    <row r="27" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>27</v>
       </c>
@@ -6559,7 +6559,7 @@
         <v>Right Side Façade Elevation Symbol. Relative to the Main or North Façade of Revit Project. The view marker can be declared with a specific type.</v>
       </c>
     </row>
-    <row r="28" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="37">
         <v>28</v>
       </c>
@@ -6652,7 +6652,7 @@
         <v>Left Side Façade Elevation Symbol. Relative to the Main or North Façade of Revit Project. The view marker can be declared with a specific type.</v>
       </c>
     </row>
-    <row r="29" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>29</v>
       </c>
@@ -6745,7 +6745,7 @@
         <v>Elevation Symbol of a Secondary Facade. Relative to the Main or North Facade of a Revit Project. The view marker can be declared with a specific type.</v>
       </c>
     </row>
-    <row r="30" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="37">
         <v>30</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>Elevation Symbol of an Interior View defined in the project, for pagination of bathrooms and kitchens, for example: the view marker can be declared with a specific type.</v>
       </c>
     </row>
-    <row r="31" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="37">
         <v>31</v>
       </c>
@@ -6931,7 +6931,7 @@
         <v>Design axes used for column location, symmetries, bodies, etc.</v>
       </c>
     </row>
-    <row r="32" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="37">
         <v>32</v>
       </c>
@@ -7024,7 +7024,7 @@
         <v>Irregularly arranged design axes used for the location of columns, symmetries, bodies, etc.</v>
       </c>
     </row>
-    <row r="33" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>33</v>
       </c>
@@ -7117,7 +7117,7 @@
         <v>Radially arranged design axes used for location of columns, symmetries, bodies, etc.</v>
       </c>
     </row>
-    <row r="34" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="37">
         <v>34</v>
       </c>
@@ -7210,7 +7210,7 @@
         <v>Regularly arranged design axes used for column location, symmetries, bodies, etc.</v>
       </c>
     </row>
-    <row r="35" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>35</v>
       </c>
@@ -7303,7 +7303,7 @@
         <v>Design axes arranged in an inclined or triangular manner used to locate columns, symmetries, bodies, etc.</v>
       </c>
     </row>
-    <row r="36" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="37">
         <v>36</v>
       </c>
@@ -7396,7 +7396,7 @@
         <v>Symbolic reference element of the position of the Structural Axis: Axis marker.</v>
       </c>
     </row>
-    <row r="37" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>37</v>
       </c>
@@ -7489,7 +7489,7 @@
         <v>Symbolic reference element of the position of a Main Axial Symmetry Axis of the Building.</v>
       </c>
     </row>
-    <row r="38" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="37">
         <v>38</v>
       </c>
@@ -7582,7 +7582,7 @@
         <v>Symbolic reference element of the position of a Secondary or Local Axial Symmetry Axis of a Part of the Building.</v>
       </c>
     </row>
-    <row r="39" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
         <v>39</v>
       </c>
@@ -7675,7 +7675,7 @@
         <v>Refers to the Campus-type implantation location where the project is located. Used for urban projects implanted in large Campus-type lots.</v>
       </c>
     </row>
-    <row r="40" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>40</v>
       </c>
@@ -7768,7 +7768,7 @@
         <v>Refers to the location of the Urban Lot type where the project is located. Used for urban projects implemented in normal lots.</v>
       </c>
     </row>
-    <row r="41" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
         <v>41</v>
       </c>
@@ -7861,7 +7861,7 @@
         <v>Delimitation of the Gross Area of the Project implemented.</v>
       </c>
     </row>
-    <row r="42" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="37">
         <v>42</v>
       </c>
@@ -7954,7 +7954,7 @@
         <v>Delimitation of buildable space to implement the project.</v>
       </c>
     </row>
-    <row r="43" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
         <v>43</v>
       </c>
@@ -8047,7 +8047,7 @@
         <v>Delimitation of the Frontal Setback of the Lot.</v>
       </c>
     </row>
-    <row r="44" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="37">
         <v>44</v>
       </c>
@@ -8140,7 +8140,7 @@
         <v>Delimitation of the space of Lot Clearances.</v>
       </c>
     </row>
-    <row r="45" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="37">
         <v>45</v>
       </c>
@@ -8233,7 +8233,7 @@
         <v>Space occupied by buildings neighboring the site of implantation.</v>
       </c>
     </row>
-    <row r="46" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="37">
         <v>46</v>
       </c>
@@ -8326,7 +8326,7 @@
         <v>Outdoor space of an implanted project.</v>
       </c>
     </row>
-    <row r="47" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="37">
         <v>47</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>Outdoor space covered with water around the implanted building.</v>
       </c>
     </row>
-    <row r="48" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="37">
         <v>48</v>
       </c>
@@ -8512,7 +8512,7 @@
         <v>Outdoor space tree of an implanted project.</v>
       </c>
     </row>
-    <row r="49" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>49</v>
       </c>
@@ -8605,7 +8605,7 @@
         <v>Outdoor space protected by some kind of environmental preservation provision.</v>
       </c>
     </row>
-    <row r="50" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="37">
         <v>50</v>
       </c>
@@ -8698,7 +8698,7 @@
         <v>Dedicated outdoor architectural spaces for Dock-type Loading and Unloading.</v>
       </c>
     </row>
-    <row r="51" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="37">
         <v>51</v>
       </c>
@@ -8791,7 +8791,7 @@
         <v>Dedicated outdoor architectural spaces for temporary storage of patio-type products.</v>
       </c>
     </row>
-    <row r="52" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="37">
         <v>52</v>
       </c>
@@ -8884,7 +8884,7 @@
         <v>Dedicated exterior architectural spaces to use as vehicle parking space, including access.</v>
       </c>
     </row>
-    <row r="53" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="37">
         <v>53</v>
       </c>
@@ -8977,7 +8977,7 @@
         <v>Architectural spaces that have not yet been specified with a defined functionality or that do not yet have a defined class in this Ontology.</v>
       </c>
     </row>
-    <row r="54" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="37">
         <v>54</v>
       </c>
@@ -9070,7 +9070,7 @@
         <v>Architectural spaces that have the function of articulating other environments and areas of a project: They can be Circulations, Halls, Stairs, Elevators, Foyers, Emergency Exits, etc...</v>
       </c>
     </row>
-    <row r="55" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="37">
         <v>55</v>
       </c>
@@ -9163,7 +9163,7 @@
         <v>Architectural spaces that have a vertical passage function for building systems of pipes and ducts.</v>
       </c>
     </row>
-    <row r="56" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="37">
         <v>56</v>
       </c>
@@ -9256,7 +9256,7 @@
         <v>Architectural spaces with specialized acoustic treatment such as recording studios, radio and TV, etc.</v>
       </c>
     </row>
-    <row r="57" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="37">
         <v>57</v>
       </c>
@@ -9349,7 +9349,7 @@
         <v>Architectural spaces with specialized acoustic treatment to eliminate sound reflections (echo).</v>
       </c>
     </row>
-    <row r="58" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="37">
         <v>58</v>
       </c>
@@ -9442,7 +9442,7 @@
         <v>Architectural spaces with specialized acoustic treatment to increase sound reflection time.</v>
       </c>
     </row>
-    <row r="59" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="37">
         <v>59</v>
       </c>
@@ -9535,7 +9535,7 @@
         <v>Architectural spaces sized as large structuring environments of a project, such as cinema audiences, theater, etc.</v>
       </c>
     </row>
-    <row r="60" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="37">
         <v>60</v>
       </c>
@@ -9628,7 +9628,7 @@
         <v>Architectural spaces sized and equipped to exhibit works of art or products, for museums, exhibitions, etc.</v>
       </c>
     </row>
-    <row r="61" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="37">
         <v>61</v>
       </c>
@@ -9721,7 +9721,7 @@
         <v>Architectural spaces sized and equipped to store cultural products such as libraries, newspaper libraries, map libraries, discotheques, media libraries, etc.</v>
       </c>
     </row>
-    <row r="62" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="37">
         <v>62</v>
       </c>
@@ -9814,7 +9814,7 @@
         <v>Architectural spaces sized and equipped to store products at low temperatures, such as Frezzers Architectural Spaces, Refrigerated Architectural Spaces, etc.</v>
       </c>
     </row>
-    <row r="63" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="37">
         <v>63</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>Architectural spaces sized and equipped for computer servers for virtual telematic activities.</v>
       </c>
     </row>
-    <row r="64" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="37">
         <v>64</v>
       </c>
@@ -10000,7 +10000,7 @@
         <v>Architectural spaces sized and equipped for public service food activities such as restaurants, bars, kiosks, etc.</v>
       </c>
     </row>
-    <row r="65" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="37">
         <v>65</v>
       </c>
@@ -10093,7 +10093,7 @@
         <v>Architectural spaces sized and equipped for Cleaning and Building Maintenance activities, etc.</v>
       </c>
     </row>
-    <row r="66" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="37">
         <v>66</v>
       </c>
@@ -10186,7 +10186,7 @@
         <v>Architectural spaces designed and equipped for the reception, storage and distribution of logistic warehouse-type elements.</v>
       </c>
     </row>
-    <row r="67" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="37">
         <v>67</v>
       </c>
@@ -10279,7 +10279,7 @@
         <v>Architectural spaces sized and equipped for activities that must remain shielded by the use of explosives or radiation emitters.</v>
       </c>
     </row>
-    <row r="68" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="37">
         <v>68</v>
       </c>
@@ -10372,7 +10372,7 @@
         <v>Architectural spaces sized and equipped for activities related to animal manipulation such as vivariums or burial spaces such as cemetery or morgues.</v>
       </c>
     </row>
-    <row r="69" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="37">
         <v>69</v>
       </c>
@@ -10465,7 +10465,7 @@
         <v>Architectural spaces sized and equipped for activities that require quarantine spaces or temporary controls.</v>
       </c>
     </row>
-    <row r="70" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="37">
         <v>70</v>
       </c>
@@ -10558,7 +10558,7 @@
         <v>Architectural spaces sized and equipped for activities or processes related to judicial acts.</v>
       </c>
     </row>
-    <row r="71" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="37">
         <v>71</v>
       </c>
@@ -10651,7 +10651,7 @@
         <v>Architectural spaces sized and equipped for vehicle entry, stay and exit activities.</v>
       </c>
     </row>
-    <row r="72" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="37">
         <v>72</v>
       </c>
@@ -10744,7 +10744,7 @@
         <v>Architectural spaces sized and equipped for sports activities, etc.</v>
       </c>
     </row>
-    <row r="73" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="37">
         <v>73</v>
       </c>
@@ -10837,7 +10837,7 @@
         <v>Architectural spaces designed and equipped for outdoor or indoor sports activities such as sports courts.</v>
       </c>
     </row>
-    <row r="74" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="37">
         <v>74</v>
       </c>
@@ -10930,7 +10930,7 @@
         <v>Architectural spaces designed and equipped for outdoor or indoor water sports activities such as sports pools.</v>
       </c>
     </row>
-    <row r="75" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="37">
         <v>75</v>
       </c>
@@ -11023,7 +11023,7 @@
         <v>Architectural spaces sized and equipped for sports activities of racing on sports tracks.</v>
       </c>
     </row>
-    <row r="76" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="37">
         <v>76</v>
       </c>
@@ -11116,7 +11116,7 @@
         <v>Architectural spaces sized and equipped for the public to see a sporting event like Grandstand.</v>
       </c>
     </row>
-    <row r="77" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="37">
         <v>77</v>
       </c>
@@ -11209,7 +11209,7 @@
         <v>Architectural spaces sized and equipped for sports locker room.</v>
       </c>
     </row>
-    <row r="78" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="37">
         <v>78</v>
       </c>
@@ -11302,7 +11302,7 @@
         <v>Architectural spaces sized and equipped with sanitary parts for male use.</v>
       </c>
     </row>
-    <row r="79" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="37">
         <v>79</v>
       </c>
@@ -11395,7 +11395,7 @@
         <v>Architectural spaces sized and equipped with sanitary parts for male use.</v>
       </c>
     </row>
-    <row r="80" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="37">
         <v>80</v>
       </c>
@@ -11488,7 +11488,7 @@
         <v>Architectural spaces sized and equipped with sanitary parts for common use by women and men.</v>
       </c>
     </row>
-    <row r="81" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="37">
         <v>81</v>
       </c>
@@ -11581,7 +11581,7 @@
         <v>Architectural spaces sized and equipped with sanitary parts for use by people with special needs (PNE).</v>
       </c>
     </row>
-    <row r="82" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="37">
         <v>82</v>
       </c>
@@ -11674,7 +11674,7 @@
         <v>Architectural spaces sized and equipped with sanitary parts of a small bathroom.</v>
       </c>
     </row>
-    <row r="83" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="37">
         <v>83</v>
       </c>
@@ -11767,7 +11767,7 @@
         <v>Architectural spaces sized and equipped for administrative commercial work.</v>
       </c>
     </row>
-    <row r="84" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="37">
         <v>84</v>
       </c>
@@ -11860,7 +11860,7 @@
         <v>Architectural spaces sized and equipped for commercial activities such as buying, selling or exchanging products with public participation. They can be ticket offices or service spaces.</v>
       </c>
     </row>
-    <row r="85" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="37">
         <v>85</v>
       </c>
@@ -11953,7 +11953,7 @@
         <v>Architectural spaces sized and equipped for residential function of Living - Architectural spaces, Balconies, etc.</v>
       </c>
     </row>
-    <row r="86" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="37">
         <v>86</v>
       </c>
@@ -12046,7 +12046,7 @@
         <v>Architectural spaces sized and equipped for intimate residential function - Bedrooms, Dressing rooms, etc.</v>
       </c>
     </row>
-    <row r="87" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="37">
         <v>87</v>
       </c>
@@ -12139,7 +12139,7 @@
         <v>Architectural spaces sized and equipped for residential hygiene function - Bathrooms, toilets, etc.</v>
       </c>
     </row>
-    <row r="88" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="37">
         <v>88</v>
       </c>
@@ -12232,7 +12232,7 @@
         <v>Architectural spaces sized and equipped for residential service function - Areas, Kitchens, etc.</v>
       </c>
     </row>
-    <row r="89" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="37">
         <v>89</v>
       </c>
@@ -12325,7 +12325,7 @@
         <v>Architectural spaces sized and equipped for residential leisure function such as architectural spaces for TV, games, etc.</v>
       </c>
     </row>
-    <row r="90" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="37">
         <v>90</v>
       </c>
@@ -12418,7 +12418,7 @@
         <v>Architectural spaces sized and equipped for residential function of professional activities.</v>
       </c>
     </row>
-    <row r="91" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="37">
         <v>91</v>
       </c>
@@ -12511,7 +12511,7 @@
         <v>Architectural spaces sized and equipped for hospital activity of general health care activities.</v>
       </c>
     </row>
-    <row r="92" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="37">
         <v>92</v>
       </c>
@@ -12604,7 +12604,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out Clinical Analysis activity.</v>
       </c>
     </row>
-    <row r="93" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="37">
         <v>93</v>
       </c>
@@ -12697,7 +12697,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out surgical activity.</v>
       </c>
     </row>
-    <row r="94" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="37">
         <v>94</v>
       </c>
@@ -12790,7 +12790,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out the Inpatient process.</v>
       </c>
     </row>
-    <row r="95" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="37">
         <v>95</v>
       </c>
@@ -12883,7 +12883,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out the Intensive Care Hospitalization process.</v>
       </c>
     </row>
-    <row r="96" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="37">
         <v>96</v>
       </c>
@@ -12976,7 +12976,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to perform Diagnostic Imaging (CT scans, MRIs, Ultrasounds, etc.)</v>
       </c>
     </row>
-    <row r="97" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="37">
         <v>97</v>
       </c>
@@ -13069,7 +13069,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out therapies with patients (physiotherapy, respiratory, etc.).</v>
       </c>
     </row>
-    <row r="98" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="37">
         <v>98</v>
       </c>
@@ -13162,7 +13162,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out Therapeutic activities in Swimming Pool, etc.</v>
       </c>
     </row>
-    <row r="99" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="37">
         <v>99</v>
       </c>
@@ -13255,7 +13255,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to perform Emergency Care.</v>
       </c>
     </row>
-    <row r="100" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="37">
         <v>100</v>
       </c>
@@ -13348,7 +13348,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to perform Patient or Material Screening.</v>
       </c>
     </row>
-    <row r="101" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="37">
         <v>101</v>
       </c>
@@ -13441,7 +13441,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out vehicular movement.</v>
       </c>
     </row>
-    <row r="102" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="37">
         <v>102</v>
       </c>
@@ -13534,7 +13534,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out Waiting activities.</v>
       </c>
     </row>
-    <row r="103" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="37">
         <v>103</v>
       </c>
@@ -13627,7 +13627,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out Medical Consultation activities.</v>
       </c>
     </row>
-    <row r="104" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="37">
         <v>104</v>
       </c>
@@ -13720,7 +13720,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out Nursing activities.</v>
       </c>
     </row>
-    <row r="105" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="37">
         <v>105</v>
       </c>
@@ -13813,7 +13813,7 @@
         <v>Architectural spaces sized and equipped for Low Biohazard Laboratory activity. Basic microbiology practices. No special barriers.</v>
       </c>
     </row>
-    <row r="106" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="37">
         <v>106</v>
       </c>
@@ -13906,7 +13906,7 @@
         <v>Architectural spaces sized and equipped for Moderate Biohazard Laboratory activity. With primary barriers (PPE, sink, decontamination). Restricted access.</v>
       </c>
     </row>
-    <row r="107" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="37">
         <v>107</v>
       </c>
@@ -13999,7 +13999,7 @@
         <v>Architectural spaces sized and equipped for High Biological Risk Laboratory activity. With advanced containment (security cabins, controlled ventilation, water showers). Strict access.</v>
       </c>
     </row>
-    <row r="108" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="37">
         <v>108</v>
       </c>
@@ -14092,7 +14092,7 @@
         <v>Architectural spaces sized and equipped for Very High Biological Risk Laboratory activity. With maximum containment (overalls with filtered air, chemical shower, isolated areas).</v>
       </c>
     </row>
-    <row r="109" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="37">
         <v>109</v>
       </c>
@@ -14185,7 +14185,7 @@
         <v>Architectural spaces sized and equipped for the activity of Vestment of professionals who work in a Biosafety containment environment.</v>
       </c>
     </row>
-    <row r="110" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="37">
         <v>110</v>
       </c>
@@ -14278,7 +14278,7 @@
         <v>Architectural spaces sized and equipped for children's activities.</v>
       </c>
     </row>
-    <row r="111" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="37">
         <v>111</v>
       </c>
@@ -14371,7 +14371,7 @@
         <v>Architectural spaces sized and equipped for Teaching and General Research activities</v>
       </c>
     </row>
-    <row r="112" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="37">
         <v>112</v>
       </c>
@@ -14464,7 +14464,7 @@
         <v>Architectural spaces sized and equipped for Teaching and Artistic Research activities related to plastics, such as painting, sculpture, etc.</v>
       </c>
     </row>
-    <row r="113" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="37">
         <v>113</v>
       </c>
@@ -14557,7 +14557,7 @@
         <v>Architectural spaces sized and equipped for Science Teaching and Research activities.</v>
       </c>
     </row>
-    <row r="114" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="37">
         <v>114</v>
       </c>
@@ -14650,7 +14650,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in technical, graphic, electronic skills, etc.</v>
       </c>
     </row>
-    <row r="115" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="37">
         <v>115</v>
       </c>
@@ -14743,7 +14743,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in Informatics.</v>
       </c>
     </row>
-    <row r="116" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="37">
         <v>116</v>
       </c>
@@ -14836,7 +14836,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in Chemistry.</v>
       </c>
     </row>
-    <row r="117" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="37">
         <v>117</v>
       </c>
@@ -14929,7 +14929,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in Physics.</v>
       </c>
     </row>
-    <row r="118" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="37">
         <v>118</v>
       </c>
@@ -15022,7 +15022,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in Biology.</v>
       </c>
     </row>
-    <row r="119" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="37">
         <v>119</v>
       </c>
@@ -15115,7 +15115,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in Music or Performing Arts.</v>
       </c>
     </row>
-    <row r="120" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="37">
         <v>120</v>
       </c>
@@ -15208,7 +15208,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in robotic fabrication, 3D printing, laser cutting and other fabrication technologies.</v>
       </c>
     </row>
-    <row r="121" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="37">
         <v>121</v>
       </c>
@@ -15301,7 +15301,7 @@
         <v>Architectural spaces sized and equipped for recreational school activities.</v>
       </c>
     </row>
-    <row r="122" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="37">
         <v>122</v>
       </c>
@@ -15394,7 +15394,7 @@
         <v>Architectural spaces sized and equipped for the preparation of artists.</v>
       </c>
     </row>
-    <row r="123" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="37">
         <v>123</v>
       </c>
@@ -15487,7 +15487,7 @@
         <v>Front space of the stage, close to the audience. It integrates architecturally to the scene, fulfilling aesthetic and acoustic functions, also called the stage mouth.</v>
       </c>
     </row>
-    <row r="124" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="37">
         <v>124</v>
       </c>
@@ -15580,7 +15580,7 @@
         <v>Space exposed to spectators, where the actors perform. It can be elevated, flat, rotating, Italian, arena, among other formats.</v>
       </c>
     </row>
-    <row r="125" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="37">
         <v>125</v>
       </c>
@@ -15673,7 +15673,7 @@
         <v>Hidden space and back to the stage, behind the artists' performance area. It can house various scenographic, technical and functional elements to the play.</v>
       </c>
     </row>
-    <row r="126" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="37">
         <v>126</v>
       </c>
@@ -15766,7 +15766,7 @@
         <v>Space lateral to the stage, used for the entry and exit of the artists.</v>
       </c>
     </row>
-    <row r="127" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="37">
         <v>127</v>
       </c>
@@ -15859,7 +15859,7 @@
         <v>Space between the audience and the stage, usually below the stage, to accommodate the orchestra during a musical or dance performance.</v>
       </c>
     </row>
-    <row r="128" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="37">
         <v>128</v>
       </c>
@@ -15952,7 +15952,7 @@
         <v>Space at stage level, where the audience sits with a view of the front of the stage.</v>
       </c>
     </row>
-    <row r="129" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="37">
         <v>129</v>
       </c>
@@ -16045,7 +16045,7 @@
         <v>Space integrated to the audience, but at an upper level where the audience is accommodated with a frontal view of the stage.</v>
       </c>
     </row>
-    <row r="130" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="37">
         <v>130</v>
       </c>
@@ -16138,7 +16138,7 @@
         <v>Space integrated into the concert hall, usually reserved and with better visibility and comfort.</v>
       </c>
     </row>
-    <row r="131" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="37">
         <v>131</v>
       </c>
@@ -16231,7 +16231,7 @@
         <v>Superior space to accommodate the public with more affordable prices.</v>
       </c>
     </row>
-    <row r="132" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="37">
         <v>132</v>
       </c>
@@ -16324,7 +16324,7 @@
         <v>Industrial Space type Large Industrial Building.</v>
       </c>
     </row>
-    <row r="133" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="37">
         <v>133</v>
       </c>
@@ -16417,7 +16417,7 @@
         <v>Industrial Space type Shed.</v>
       </c>
     </row>
-    <row r="134" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="37">
         <v>134</v>
       </c>
@@ -16510,7 +16510,7 @@
         <v>Industrial space sized and equipped with furnaces or heavy equipment for processing metals and alloys.</v>
       </c>
     </row>
-    <row r="135" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="37">
         <v>135</v>
       </c>
@@ -16603,7 +16603,7 @@
         <v>Industrial space sized and equipped as a Production Line of large-scale goods (automobiles, electronics, textiles and food, etc.). It is an assembly line of automated machines</v>
       </c>
     </row>
-    <row r="136" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="37">
         <v>136</v>
       </c>
@@ -16696,7 +16696,7 @@
         <v>Industrial space sized and equipped as a Production Workshop for medium or low scale goods (furniture, equipment, small vehicles, etc.). It is prepared for assembly.</v>
       </c>
     </row>
-    <row r="137" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="37">
         <v>137</v>
       </c>
@@ -16789,7 +16789,7 @@
         <v>Industrial space sized and equipped as a Painting Workshop of medium or low scale goods (furniture, equipment, small vehicles, etc.). It is prepared for assembly.</v>
       </c>
     </row>
-    <row r="138" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="37">
         <v>138</v>
       </c>
@@ -16882,7 +16882,7 @@
         <v>It represents a Housing Unit of Social Interest.</v>
       </c>
     </row>
-    <row r="139" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="37">
         <v>139</v>
       </c>
@@ -16975,7 +16975,7 @@
         <v>Represents an Apartment of residential building.</v>
       </c>
     </row>
-    <row r="140" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="37">
         <v>140</v>
       </c>
@@ -17068,7 +17068,7 @@
         <v>Represents an administrative functional department of an institutional building.</v>
       </c>
     </row>
-    <row r="141" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="37">
         <v>141</v>
       </c>
@@ -17161,7 +17161,7 @@
         <v>It represents an administrative functional division of an institutional building.</v>
       </c>
     </row>
-    <row r="142" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="37">
         <v>142</v>
       </c>
@@ -17254,7 +17254,7 @@
         <v>It represents an administrative functional sector of an institutional building.</v>
       </c>
     </row>
-    <row r="143" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="37">
         <v>143</v>
       </c>
@@ -17347,7 +17347,7 @@
         <v>It represents a Built Block that contains other autonomous units without a specific function.</v>
       </c>
     </row>
-    <row r="144" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="37">
         <v>144</v>
       </c>
@@ -17440,7 +17440,7 @@
         <v>It represents a Built Block that is a House or Individual Residential Unit.</v>
       </c>
     </row>
-    <row r="145" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="37">
         <v>145</v>
       </c>
@@ -17533,7 +17533,7 @@
         <v>It represents a Built Block that contains other autonomous units with a residential function.</v>
       </c>
     </row>
-    <row r="146" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="37">
         <v>146</v>
       </c>
@@ -17626,7 +17626,7 @@
         <v>It represents a Built Block of an Educational Unit.</v>
       </c>
     </row>
-    <row r="147" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="37">
         <v>147</v>
       </c>
@@ -17719,7 +17719,7 @@
         <v>It represents a Built Block of a SUS Health Unit.</v>
       </c>
     </row>
-    <row r="148" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="37">
         <v>148</v>
       </c>
@@ -17812,7 +17812,7 @@
         <v>It represents a Built Block of a Health Unit of the Private Network.</v>
       </c>
     </row>
-    <row r="149" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="37">
         <v>149</v>
       </c>
@@ -17905,7 +17905,7 @@
         <v>It represents a Built Block of a Health Unit of the Private Network contracted with the SUS.</v>
       </c>
     </row>
-    <row r="150" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="37">
         <v>150</v>
       </c>
@@ -17998,7 +17998,7 @@
         <v>Spatial zone is a non-hierarchical and potentially overlapping decomposition of the project under some condition.</v>
       </c>
     </row>
-    <row r="151" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="37">
         <v>151</v>
       </c>
@@ -18091,7 +18091,7 @@
         <v>Space zone is used to represent a construction zone for the manufacturing process.</v>
       </c>
     </row>
-    <row r="152" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="37">
         <v>152</v>
       </c>
@@ -18184,7 +18184,7 @@
         <v>Spatial zone is used to define an interference between occurrences of Ifcspatialelement.</v>
       </c>
     </row>
-    <row r="153" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="37">
         <v>153</v>
       </c>
@@ -18277,7 +18277,7 @@
         <v>Spatial zone is used to represent a particular zone of occupation.</v>
       </c>
     </row>
-    <row r="154" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="37">
         <v>154</v>
       </c>
@@ -18370,7 +18370,7 @@
         <v>A spatial zone that represents some type of reserve within the project for future use.</v>
       </c>
     </row>
-    <row r="155" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="37">
         <v>155</v>
       </c>
@@ -18463,7 +18463,7 @@
         <v>Spatial zone is used to represent an area primarily dedicated to the circulation of people or vehicles.</v>
       </c>
     </row>
-    <row r="156" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="37">
         <v>156</v>
       </c>
@@ -18556,7 +18556,7 @@
         <v>Space zone is used to represent a thermal zone with homogeneous characteristics.</v>
       </c>
     </row>
-    <row r="157" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="37">
         <v>157</v>
       </c>
@@ -18649,7 +18649,7 @@
         <v>Spatial zone is used to represent a lighting zone; a zone of natural light.</v>
       </c>
     </row>
-    <row r="158" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="37">
         <v>158</v>
       </c>
@@ -18742,7 +18742,7 @@
         <v>Spatial zone is used to represent a ventilation zone.</v>
       </c>
     </row>
-    <row r="159" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="37">
         <v>159</v>
       </c>
@@ -18835,7 +18835,7 @@
         <v>Spatial zone is used to represent a zone for planning safety and work, accesses, etc.</v>
       </c>
     </row>
-    <row r="160" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="37">
         <v>160</v>
       </c>
@@ -18928,7 +18928,7 @@
         <v>Space zone is used to represent a fire safety zone, or compartment.</v>
       </c>
     </row>
-    <row r="161" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="37">
         <v>161</v>
       </c>
@@ -19021,7 +19021,7 @@
         <v>Space zone is used to represent a biosecurity zone, typically where ventilation is critical.</v>
       </c>
     </row>
-    <row r="162" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="37">
         <v>162</v>
       </c>
@@ -19114,7 +19114,7 @@
         <v>Solar Heliodom or Analema: sun.</v>
       </c>
     </row>
-    <row r="163" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="37">
         <v>163</v>
       </c>
@@ -19207,7 +19207,7 @@
         <v>Heliodom Solar Analemma: Solar Path 1.</v>
       </c>
     </row>
-    <row r="164" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="37">
         <v>164</v>
       </c>
@@ -19300,7 +19300,7 @@
         <v>Heliodom Solar Analemma: Solar Path 1.</v>
       </c>
     </row>
-    <row r="165" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="37">
         <v>165</v>
       </c>
@@ -19393,7 +19393,7 @@
         <v>Heliodom Dawn: Text from the exit of the sun.</v>
       </c>
     </row>
-    <row r="166" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="37">
         <v>166</v>
       </c>
@@ -19486,7 +19486,7 @@
         <v>Heliodom Nightfall: text from posta do sol.</v>
       </c>
     </row>
-    <row r="167" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="37">
         <v>167</v>
       </c>
@@ -19579,7 +19579,7 @@
         <v>Solar Study Heliodom.</v>
       </c>
     </row>
-    <row r="168" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="37">
         <v>168</v>
       </c>
@@ -19672,7 +19672,7 @@
         <v>Heliodom Surface of the sun.</v>
       </c>
     </row>
-    <row r="169" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="37">
         <v>169</v>
       </c>
@@ -19765,7 +19765,7 @@
         <v>Envelope orientation analysis. North-oriented elements, relative to True or Solar North.</v>
       </c>
     </row>
-    <row r="170" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="37">
         <v>170</v>
       </c>
@@ -19858,7 +19858,7 @@
         <v>Orientation analysis of the Envelope. South-oriented elements, relative to True or Solar North.</v>
       </c>
     </row>
-    <row r="171" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="37">
         <v>171</v>
       </c>
@@ -19951,7 +19951,7 @@
         <v>Envelope orientation analysis. East-facing elements, relative to True North or Solar.</v>
       </c>
     </row>
-    <row r="172" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="37">
         <v>172</v>
       </c>
@@ -20044,7 +20044,7 @@
         <v>Orientation analysis of the Envelope. Elements oriented to the West, relative to True or Solar North.</v>
       </c>
     </row>
-    <row r="173" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="37">
         <v>173</v>
       </c>
@@ -20259,15 +20259,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="10" width="6" style="12" bestFit="1" customWidth="1"/>
     <col min="11" max="21" width="6" style="10" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="10"/>
+    <col min="22" max="16384" width="11.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
@@ -20332,7 +20332,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -20397,7 +20397,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="7">
         <v>3</v>
       </c>
@@ -20472,16 +20472,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B299E44-CC41-4C47-93B0-FF411236635D}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="8.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.15234375" customWidth="1"/>
-    <col min="3" max="3" width="10.69140625" customWidth="1"/>
-    <col min="4" max="4" width="8.3046875" customWidth="1"/>
-    <col min="5" max="5" width="9.84375" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="15">
         <v>1</v>
       </c>
@@ -20498,7 +20498,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28">
         <v>2</v>
       </c>
@@ -20515,7 +20515,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="28">
         <v>3</v>
       </c>
@@ -20532,7 +20532,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="28">
         <v>4</v>
       </c>
@@ -20563,43 +20563,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F4F343-F8A9-4565-8E75-460BD2B52D7E}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AE46"/>
-  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="64" customWidth="1"/>
-    <col min="2" max="2" width="9.3046875" style="52" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3828125" style="50" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.84375" style="50" customWidth="1"/>
-    <col min="5" max="5" width="7.84375" style="50" customWidth="1"/>
-    <col min="6" max="6" width="5.84375" style="50" customWidth="1"/>
-    <col min="7" max="7" width="5.15234375" style="50" customWidth="1"/>
-    <col min="8" max="8" width="7.53515625" style="50" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.15234375" style="50" customWidth="1"/>
-    <col min="10" max="10" width="8.3828125" style="50" customWidth="1"/>
-    <col min="11" max="11" width="4.69140625" style="50" customWidth="1"/>
-    <col min="12" max="12" width="3.3046875" style="50" customWidth="1"/>
-    <col min="13" max="13" width="5.84375" style="50" customWidth="1"/>
-    <col min="14" max="14" width="8.69140625" style="50" customWidth="1"/>
-    <col min="15" max="15" width="19.84375" style="50" customWidth="1"/>
-    <col min="16" max="16" width="4.53515625" style="50" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" style="64" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="52" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="50" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.85546875" style="50" customWidth="1"/>
+    <col min="5" max="5" width="7.85546875" style="50" customWidth="1"/>
+    <col min="6" max="6" width="5.85546875" style="50" customWidth="1"/>
+    <col min="7" max="7" width="5.140625" style="50" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" style="50" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.140625" style="50" customWidth="1"/>
+    <col min="10" max="10" width="8.42578125" style="50" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" style="50" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" style="50" customWidth="1"/>
+    <col min="13" max="13" width="5.85546875" style="50" customWidth="1"/>
+    <col min="14" max="14" width="8.7109375" style="50" customWidth="1"/>
+    <col min="15" max="15" width="19.85546875" style="50" customWidth="1"/>
+    <col min="16" max="16" width="4.5703125" style="50" customWidth="1"/>
     <col min="17" max="17" width="28" style="50" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.69140625" style="50" customWidth="1"/>
-    <col min="19" max="19" width="15.69140625" style="50" customWidth="1"/>
-    <col min="20" max="20" width="5" style="50" customWidth="1"/>
-    <col min="21" max="21" width="25.3828125" style="50" customWidth="1"/>
-    <col min="22" max="22" width="5.69140625" style="50" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" style="50" customWidth="1"/>
+    <col min="19" max="19" width="15.7109375" style="50" customWidth="1"/>
+    <col min="20" max="20" width="4.28515625" style="50" customWidth="1"/>
+    <col min="21" max="21" width="25.42578125" style="50" customWidth="1"/>
+    <col min="22" max="22" width="4.5703125" style="50" customWidth="1"/>
     <col min="23" max="23" width="11" style="50" customWidth="1"/>
-    <col min="24" max="24" width="9.15234375" style="50" customWidth="1"/>
-    <col min="25" max="25" width="12.69140625" style="50" customWidth="1"/>
-    <col min="26" max="26" width="2.3828125" style="50" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.69140625" style="50" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.15234375" style="50" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.53515625" style="50" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.53515625" style="50" customWidth="1"/>
-    <col min="31" max="31" width="7.53515625" style="50" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.3046875" style="50"/>
+    <col min="24" max="24" width="9.140625" style="50" customWidth="1"/>
+    <col min="25" max="25" width="12.7109375" style="50" customWidth="1"/>
+    <col min="26" max="26" width="2.42578125" style="50" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14" style="50" customWidth="1"/>
+    <col min="28" max="28" width="5" style="50" customWidth="1"/>
+    <col min="29" max="29" width="9.28515625" style="50" customWidth="1"/>
+    <col min="30" max="30" width="10.5703125" style="50" customWidth="1"/>
+    <col min="31" max="31" width="7.5703125" style="50" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.28515625" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="20.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:31" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="62" t="s">
         <v>11</v>
       </c>
@@ -20694,7 +20694,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="63">
         <v>1</v>
       </c>
@@ -20789,7 +20789,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="63">
         <v>2</v>
       </c>
@@ -20884,7 +20884,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="63">
         <v>3</v>
       </c>
@@ -20979,7 +20979,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="63">
         <v>4</v>
       </c>
@@ -21074,7 +21074,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="63">
         <v>5</v>
       </c>
@@ -21169,7 +21169,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="63">
         <v>6</v>
       </c>
@@ -21264,7 +21264,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="63">
         <v>7</v>
       </c>
@@ -21359,7 +21359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="63">
         <v>8</v>
       </c>
@@ -21454,7 +21454,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="63">
         <v>9</v>
       </c>
@@ -21549,7 +21549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="63">
         <v>10</v>
       </c>
@@ -21644,7 +21644,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="63">
         <v>11</v>
       </c>
@@ -21739,7 +21739,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="63">
         <v>12</v>
       </c>
@@ -21834,7 +21834,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="63">
         <v>13</v>
       </c>
@@ -21929,7 +21929,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="63">
         <v>14</v>
       </c>
@@ -22024,7 +22024,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="63">
         <v>15</v>
       </c>
@@ -22119,7 +22119,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="63">
         <v>16</v>
       </c>
@@ -22214,7 +22214,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="63">
         <v>17</v>
       </c>
@@ -22309,7 +22309,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="63">
         <v>18</v>
       </c>
@@ -22404,7 +22404,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="63">
         <v>19</v>
       </c>
@@ -22499,7 +22499,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="63">
         <v>20</v>
       </c>
@@ -22594,7 +22594,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="63">
         <v>21</v>
       </c>
@@ -22689,7 +22689,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="63">
         <v>22</v>
       </c>
@@ -22784,7 +22784,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="63">
         <v>23</v>
       </c>
@@ -22879,7 +22879,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="63">
         <v>24</v>
       </c>
@@ -22974,7 +22974,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="63">
         <v>25</v>
       </c>
@@ -23069,7 +23069,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="63">
         <v>26</v>
       </c>
@@ -23164,7 +23164,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="63">
         <v>27</v>
       </c>
@@ -23259,7 +23259,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="63">
         <v>28</v>
       </c>
@@ -23354,7 +23354,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="63">
         <v>29</v>
       </c>
@@ -23449,7 +23449,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="63">
         <v>30</v>
       </c>
@@ -23544,7 +23544,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="63">
         <v>31</v>
       </c>
@@ -23639,7 +23639,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="63">
         <v>32</v>
       </c>
@@ -23734,7 +23734,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="63">
         <v>33</v>
       </c>
@@ -23829,7 +23829,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="63">
         <v>34</v>
       </c>
@@ -23924,7 +23924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="63">
         <v>35</v>
       </c>
@@ -24019,7 +24019,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="63">
         <v>36</v>
       </c>
@@ -24114,7 +24114,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="63">
         <v>37</v>
       </c>
@@ -24209,7 +24209,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="63">
         <v>38</v>
       </c>
@@ -24304,7 +24304,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="63">
         <v>39</v>
       </c>
@@ -24399,7 +24399,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="63">
         <v>40</v>
       </c>
@@ -24494,7 +24494,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="63">
         <v>41</v>
       </c>
@@ -24589,7 +24589,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="63">
         <v>42</v>
       </c>
@@ -24684,7 +24684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="63">
         <v>43</v>
       </c>
@@ -24779,7 +24779,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="63">
         <v>44</v>
       </c>
@@ -24874,7 +24874,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="63">
         <v>45</v>
       </c>

--- a/Versão5/AMBI/Ontologia_AMBIENTES.xlsx
+++ b/Versão5/AMBI/Ontologia_AMBIENTES.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4122CE48-F487-4E27-B384-7B8A408D9E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -3721,14 +3721,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
-    <col min="2" max="2" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="56" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.3046875" customWidth="1"/>
+    <col min="2" max="2" width="51.69140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="56" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
         <v>47</v>
       </c>
@@ -3739,7 +3739,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19" t="s">
         <v>49</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="19" t="s">
         <v>51</v>
       </c>
@@ -3761,7 +3761,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="20" t="s">
         <v>52</v>
       </c>
@@ -3772,7 +3772,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20" t="s">
         <v>53</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="20" t="s">
         <v>54</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="20" t="s">
         <v>55</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="20" t="s">
         <v>57</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="20" t="s">
         <v>58</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="20" t="s">
         <v>60</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="20" t="s">
         <v>62</v>
       </c>
@@ -3851,7 +3851,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="20" t="s">
         <v>63</v>
       </c>
@@ -3862,7 +3862,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="20" t="s">
         <v>64</v>
       </c>
@@ -3873,7 +3873,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="20" t="s">
         <v>65</v>
       </c>
@@ -3884,7 +3884,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="20" t="s">
         <v>66</v>
       </c>
@@ -3895,7 +3895,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="20" t="s">
         <v>67</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="20" t="s">
         <v>68</v>
       </c>
@@ -3917,19 +3917,19 @@
         <v>283</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="20" t="s">
         <v>69</v>
       </c>
       <c r="B18" s="22">
         <f ca="1">NOW()</f>
-        <v>46195.504604282411</v>
+        <v>46214.349723032406</v>
       </c>
       <c r="C18" s="55" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="20" t="s">
         <v>315</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="20" t="s">
         <v>316</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="20" t="s">
         <v>317</v>
       </c>
@@ -3964,7 +3964,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="20" t="s">
         <v>70</v>
       </c>
@@ -3975,7 +3975,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="20" t="s">
         <v>71</v>
       </c>
@@ -3986,7 +3986,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="20" t="s">
         <v>72</v>
       </c>
@@ -3997,7 +3997,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="20" t="s">
         <v>73</v>
       </c>
@@ -4008,7 +4008,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
         <v>281</v>
       </c>
@@ -4029,36 +4029,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA173"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="4.5703125" style="14" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" style="14" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="14" customWidth="1"/>
-    <col min="7" max="10" width="6.7109375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="49.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.85546875" style="14" customWidth="1"/>
-    <col min="13" max="13" width="11.140625" style="13" customWidth="1"/>
-    <col min="14" max="14" width="9.5703125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="12.28515625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="82.42578125" style="14" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="83.85546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.140625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="6.85546875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="11.140625" style="14" customWidth="1"/>
-    <col min="21" max="21" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.42578125" style="14" customWidth="1"/>
-    <col min="23" max="23" width="7.28515625" style="67" customWidth="1"/>
+    <col min="1" max="1" width="3.3046875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="4.53515625" style="14" customWidth="1"/>
+    <col min="3" max="3" width="7.3828125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="10.84375" style="14" customWidth="1"/>
+    <col min="5" max="5" width="10.3046875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.69140625" style="14" customWidth="1"/>
+    <col min="7" max="10" width="6.69140625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="49.3828125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.84375" style="14" customWidth="1"/>
+    <col min="13" max="13" width="11.15234375" style="13" customWidth="1"/>
+    <col min="14" max="14" width="9.53515625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="12.3046875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="82.3828125" style="14" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="83.84375" style="14" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.15234375" style="2" customWidth="1"/>
+    <col min="19" max="19" width="6.84375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="11.15234375" style="14" customWidth="1"/>
+    <col min="21" max="21" width="12.84375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.3828125" style="14" customWidth="1"/>
+    <col min="23" max="23" width="7.3046875" style="67" customWidth="1"/>
     <col min="24" max="24" width="26" style="36" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="19.7109375" style="36" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="35" customWidth="1"/>
-    <col min="27" max="27" width="70.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="2"/>
+    <col min="25" max="25" width="19.69140625" style="36" customWidth="1"/>
+    <col min="26" max="26" width="14.53515625" style="35" customWidth="1"/>
+    <col min="27" max="27" width="70.84375" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.15234375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="32" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" s="32" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="29">
         <v>0</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="2" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="37">
         <v>2</v>
       </c>
@@ -4234,7 +4234,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="37">
         <v>3</v>
       </c>
@@ -4327,7 +4327,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="37">
         <v>4</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="37">
         <v>5</v>
       </c>
@@ -4513,7 +4513,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="37">
         <v>6</v>
       </c>
@@ -4606,7 +4606,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="37">
         <v>7</v>
       </c>
@@ -4699,7 +4699,7 @@
         <v>Floor of the building.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="37">
         <v>8</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>Floor building type.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="37">
         <v>9</v>
       </c>
@@ -4885,7 +4885,7 @@
         <v>Single floor of the building. Floors that are not typical and are custom designed.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="37">
         <v>10</v>
       </c>
@@ -4978,7 +4978,7 @@
         <v>Single floor of the building. Floors that are not typical.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="37">
         <v>11</v>
       </c>
@@ -5071,7 +5071,7 @@
         <v>Single floor of the building. In buildings that have concert halls, it is the floor that contains the stage or projection screen.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="37">
         <v>12</v>
       </c>
@@ -5164,7 +5164,7 @@
         <v>Single floor of the building. Identifies the floor that stands out for its double height or some characteristic that makes it unique.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="37">
         <v>13</v>
       </c>
@@ -5257,7 +5257,7 @@
         <v>Technical floor of the building.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="37">
         <v>14</v>
       </c>
@@ -5350,7 +5350,7 @@
         <v>Lower partial floor introduced at the ceiling height of one floor, with access only from the interior of the enclosure.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="37">
         <v>15</v>
       </c>
@@ -5443,7 +5443,7 @@
         <v>Access floor to the building.</v>
       </c>
     </row>
-    <row r="16" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="37">
         <v>16</v>
       </c>
@@ -5536,7 +5536,7 @@
         <v>Basement floor of the building.</v>
       </c>
     </row>
-    <row r="17" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="37">
         <v>17</v>
       </c>
@@ -5629,7 +5629,7 @@
         <v>Symbolic reference element of the position of each Floor of the project: the floor marker can be declared with a specific type in the category OST_LevelHeads.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="37">
         <v>18</v>
       </c>
@@ -5722,7 +5722,7 @@
         <v>Horizontal plane of the building's foundation blocks.</v>
       </c>
     </row>
-    <row r="19" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="37">
         <v>19</v>
       </c>
@@ -5815,7 +5815,7 @@
         <v>Horizontal plane of the foundation piles of the building.</v>
       </c>
     </row>
-    <row r="20" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="37">
         <v>20</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>Template that defines the upper level of the saturated zone of groundwater or water table.</v>
       </c>
     </row>
-    <row r="21" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="37">
         <v>21</v>
       </c>
@@ -6001,7 +6001,7 @@
         <v>Depth gauge. Can be used to define the upper elevation of an underground project, such as a subway line or urban special installations. Used as a depth penetration reference limit for new projects.</v>
       </c>
     </row>
-    <row r="22" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="37">
         <v>22</v>
       </c>
@@ -6094,7 +6094,7 @@
         <v>Height gauge allowed to perform safe flights with UAS (drones). Established by ANAC (National Civil Aviation Agency). Especially in regions close to airports.</v>
       </c>
     </row>
-    <row r="23" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="37">
         <v>23</v>
       </c>
@@ -6187,7 +6187,7 @@
         <v>Gauge that defines the variable levels of a natural body of water, such as the sea or maximum and minimum increases of rivers and lagoons. Reference for projects in coastal or floodable areas.</v>
       </c>
     </row>
-    <row r="24" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="37">
         <v>24</v>
       </c>
@@ -6280,7 +6280,7 @@
         <v>Maximum height gauge allowed for buildings in each urban area. Established by municipal laws for land use and occupation. It cannot be exceeded by the project.</v>
       </c>
     </row>
-    <row r="25" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="37">
         <v>25</v>
       </c>
@@ -6373,7 +6373,7 @@
         <v>Main Facade Elevation Symbol. Relative to the North of the Revit project. The view marker can be declared with a specific type.</v>
       </c>
     </row>
-    <row r="26" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="37">
         <v>26</v>
       </c>
@@ -6466,7 +6466,7 @@
         <v>Back Facade Elevation Symbol. Relative to the Main or North Facade of Revit Project. The view marker can be declared with a specific type.</v>
       </c>
     </row>
-    <row r="27" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="37">
         <v>27</v>
       </c>
@@ -6559,7 +6559,7 @@
         <v>Right Side Façade Elevation Symbol. Relative to the Main or North Façade of Revit Project. The view marker can be declared with a specific type.</v>
       </c>
     </row>
-    <row r="28" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="37">
         <v>28</v>
       </c>
@@ -6652,7 +6652,7 @@
         <v>Left Side Façade Elevation Symbol. Relative to the Main or North Façade of Revit Project. The view marker can be declared with a specific type.</v>
       </c>
     </row>
-    <row r="29" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="37">
         <v>29</v>
       </c>
@@ -6745,7 +6745,7 @@
         <v>Elevation Symbol of a Secondary Facade. Relative to the Main or North Facade of a Revit Project. The view marker can be declared with a specific type.</v>
       </c>
     </row>
-    <row r="30" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="37">
         <v>30</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>Elevation Symbol of an Interior View defined in the project, for pagination of bathrooms and kitchens, for example: the view marker can be declared with a specific type.</v>
       </c>
     </row>
-    <row r="31" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="37">
         <v>31</v>
       </c>
@@ -6931,7 +6931,7 @@
         <v>Design axes used for column location, symmetries, bodies, etc.</v>
       </c>
     </row>
-    <row r="32" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="37">
         <v>32</v>
       </c>
@@ -7024,7 +7024,7 @@
         <v>Irregularly arranged design axes used for the location of columns, symmetries, bodies, etc.</v>
       </c>
     </row>
-    <row r="33" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="37">
         <v>33</v>
       </c>
@@ -7117,7 +7117,7 @@
         <v>Radially arranged design axes used for location of columns, symmetries, bodies, etc.</v>
       </c>
     </row>
-    <row r="34" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="37">
         <v>34</v>
       </c>
@@ -7210,7 +7210,7 @@
         <v>Regularly arranged design axes used for column location, symmetries, bodies, etc.</v>
       </c>
     </row>
-    <row r="35" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="37">
         <v>35</v>
       </c>
@@ -7303,7 +7303,7 @@
         <v>Design axes arranged in an inclined or triangular manner used to locate columns, symmetries, bodies, etc.</v>
       </c>
     </row>
-    <row r="36" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="37">
         <v>36</v>
       </c>
@@ -7396,7 +7396,7 @@
         <v>Symbolic reference element of the position of the Structural Axis: Axis marker.</v>
       </c>
     </row>
-    <row r="37" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="37">
         <v>37</v>
       </c>
@@ -7489,7 +7489,7 @@
         <v>Symbolic reference element of the position of a Main Axial Symmetry Axis of the Building.</v>
       </c>
     </row>
-    <row r="38" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="37">
         <v>38</v>
       </c>
@@ -7582,7 +7582,7 @@
         <v>Symbolic reference element of the position of a Secondary or Local Axial Symmetry Axis of a Part of the Building.</v>
       </c>
     </row>
-    <row r="39" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="37">
         <v>39</v>
       </c>
@@ -7675,7 +7675,7 @@
         <v>Refers to the Campus-type implantation location where the project is located. Used for urban projects implanted in large Campus-type lots.</v>
       </c>
     </row>
-    <row r="40" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="37">
         <v>40</v>
       </c>
@@ -7768,7 +7768,7 @@
         <v>Refers to the location of the Urban Lot type where the project is located. Used for urban projects implemented in normal lots.</v>
       </c>
     </row>
-    <row r="41" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="37">
         <v>41</v>
       </c>
@@ -7861,7 +7861,7 @@
         <v>Delimitation of the Gross Area of the Project implemented.</v>
       </c>
     </row>
-    <row r="42" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="37">
         <v>42</v>
       </c>
@@ -7954,7 +7954,7 @@
         <v>Delimitation of buildable space to implement the project.</v>
       </c>
     </row>
-    <row r="43" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="37">
         <v>43</v>
       </c>
@@ -8047,7 +8047,7 @@
         <v>Delimitation of the Frontal Setback of the Lot.</v>
       </c>
     </row>
-    <row r="44" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="37">
         <v>44</v>
       </c>
@@ -8140,7 +8140,7 @@
         <v>Delimitation of the space of Lot Clearances.</v>
       </c>
     </row>
-    <row r="45" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="37">
         <v>45</v>
       </c>
@@ -8233,7 +8233,7 @@
         <v>Space occupied by buildings neighboring the site of implantation.</v>
       </c>
     </row>
-    <row r="46" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="37">
         <v>46</v>
       </c>
@@ -8326,7 +8326,7 @@
         <v>Outdoor space of an implanted project.</v>
       </c>
     </row>
-    <row r="47" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="37">
         <v>47</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>Outdoor space covered with water around the implanted building.</v>
       </c>
     </row>
-    <row r="48" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="37">
         <v>48</v>
       </c>
@@ -8512,7 +8512,7 @@
         <v>Outdoor space tree of an implanted project.</v>
       </c>
     </row>
-    <row r="49" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="37">
         <v>49</v>
       </c>
@@ -8605,7 +8605,7 @@
         <v>Outdoor space protected by some kind of environmental preservation provision.</v>
       </c>
     </row>
-    <row r="50" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="37">
         <v>50</v>
       </c>
@@ -8698,7 +8698,7 @@
         <v>Dedicated outdoor architectural spaces for Dock-type Loading and Unloading.</v>
       </c>
     </row>
-    <row r="51" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="37">
         <v>51</v>
       </c>
@@ -8791,7 +8791,7 @@
         <v>Dedicated outdoor architectural spaces for temporary storage of patio-type products.</v>
       </c>
     </row>
-    <row r="52" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="37">
         <v>52</v>
       </c>
@@ -8884,7 +8884,7 @@
         <v>Dedicated exterior architectural spaces to use as vehicle parking space, including access.</v>
       </c>
     </row>
-    <row r="53" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="37">
         <v>53</v>
       </c>
@@ -8977,7 +8977,7 @@
         <v>Architectural spaces that have not yet been specified with a defined functionality or that do not yet have a defined class in this Ontology.</v>
       </c>
     </row>
-    <row r="54" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="37">
         <v>54</v>
       </c>
@@ -9070,7 +9070,7 @@
         <v>Architectural spaces that have the function of articulating other environments and areas of a project: They can be Circulations, Halls, Stairs, Elevators, Foyers, Emergency Exits, etc...</v>
       </c>
     </row>
-    <row r="55" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="37">
         <v>55</v>
       </c>
@@ -9163,7 +9163,7 @@
         <v>Architectural spaces that have a vertical passage function for building systems of pipes and ducts.</v>
       </c>
     </row>
-    <row r="56" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="37">
         <v>56</v>
       </c>
@@ -9256,7 +9256,7 @@
         <v>Architectural spaces with specialized acoustic treatment such as recording studios, radio and TV, etc.</v>
       </c>
     </row>
-    <row r="57" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="37">
         <v>57</v>
       </c>
@@ -9349,7 +9349,7 @@
         <v>Architectural spaces with specialized acoustic treatment to eliminate sound reflections (echo).</v>
       </c>
     </row>
-    <row r="58" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="37">
         <v>58</v>
       </c>
@@ -9442,7 +9442,7 @@
         <v>Architectural spaces with specialized acoustic treatment to increase sound reflection time.</v>
       </c>
     </row>
-    <row r="59" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="37">
         <v>59</v>
       </c>
@@ -9535,7 +9535,7 @@
         <v>Architectural spaces sized as large structuring environments of a project, such as cinema audiences, theater, etc.</v>
       </c>
     </row>
-    <row r="60" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="37">
         <v>60</v>
       </c>
@@ -9628,7 +9628,7 @@
         <v>Architectural spaces sized and equipped to exhibit works of art or products, for museums, exhibitions, etc.</v>
       </c>
     </row>
-    <row r="61" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="37">
         <v>61</v>
       </c>
@@ -9721,7 +9721,7 @@
         <v>Architectural spaces sized and equipped to store cultural products such as libraries, newspaper libraries, map libraries, discotheques, media libraries, etc.</v>
       </c>
     </row>
-    <row r="62" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="37">
         <v>62</v>
       </c>
@@ -9814,7 +9814,7 @@
         <v>Architectural spaces sized and equipped to store products at low temperatures, such as Frezzers Architectural Spaces, Refrigerated Architectural Spaces, etc.</v>
       </c>
     </row>
-    <row r="63" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="37">
         <v>63</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>Architectural spaces sized and equipped for computer servers for virtual telematic activities.</v>
       </c>
     </row>
-    <row r="64" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="37">
         <v>64</v>
       </c>
@@ -10000,7 +10000,7 @@
         <v>Architectural spaces sized and equipped for public service food activities such as restaurants, bars, kiosks, etc.</v>
       </c>
     </row>
-    <row r="65" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="37">
         <v>65</v>
       </c>
@@ -10093,7 +10093,7 @@
         <v>Architectural spaces sized and equipped for Cleaning and Building Maintenance activities, etc.</v>
       </c>
     </row>
-    <row r="66" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="37">
         <v>66</v>
       </c>
@@ -10186,7 +10186,7 @@
         <v>Architectural spaces designed and equipped for the reception, storage and distribution of logistic warehouse-type elements.</v>
       </c>
     </row>
-    <row r="67" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="37">
         <v>67</v>
       </c>
@@ -10279,7 +10279,7 @@
         <v>Architectural spaces sized and equipped for activities that must remain shielded by the use of explosives or radiation emitters.</v>
       </c>
     </row>
-    <row r="68" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="37">
         <v>68</v>
       </c>
@@ -10372,7 +10372,7 @@
         <v>Architectural spaces sized and equipped for activities related to animal manipulation such as vivariums or burial spaces such as cemetery or morgues.</v>
       </c>
     </row>
-    <row r="69" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="37">
         <v>69</v>
       </c>
@@ -10465,7 +10465,7 @@
         <v>Architectural spaces sized and equipped for activities that require quarantine spaces or temporary controls.</v>
       </c>
     </row>
-    <row r="70" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="37">
         <v>70</v>
       </c>
@@ -10558,7 +10558,7 @@
         <v>Architectural spaces sized and equipped for activities or processes related to judicial acts.</v>
       </c>
     </row>
-    <row r="71" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="37">
         <v>71</v>
       </c>
@@ -10651,7 +10651,7 @@
         <v>Architectural spaces sized and equipped for vehicle entry, stay and exit activities.</v>
       </c>
     </row>
-    <row r="72" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="37">
         <v>72</v>
       </c>
@@ -10744,7 +10744,7 @@
         <v>Architectural spaces sized and equipped for sports activities, etc.</v>
       </c>
     </row>
-    <row r="73" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="37">
         <v>73</v>
       </c>
@@ -10837,7 +10837,7 @@
         <v>Architectural spaces designed and equipped for outdoor or indoor sports activities such as sports courts.</v>
       </c>
     </row>
-    <row r="74" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="37">
         <v>74</v>
       </c>
@@ -10930,7 +10930,7 @@
         <v>Architectural spaces designed and equipped for outdoor or indoor water sports activities such as sports pools.</v>
       </c>
     </row>
-    <row r="75" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="37">
         <v>75</v>
       </c>
@@ -11023,7 +11023,7 @@
         <v>Architectural spaces sized and equipped for sports activities of racing on sports tracks.</v>
       </c>
     </row>
-    <row r="76" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="37">
         <v>76</v>
       </c>
@@ -11116,7 +11116,7 @@
         <v>Architectural spaces sized and equipped for the public to see a sporting event like Grandstand.</v>
       </c>
     </row>
-    <row r="77" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="37">
         <v>77</v>
       </c>
@@ -11209,7 +11209,7 @@
         <v>Architectural spaces sized and equipped for sports locker room.</v>
       </c>
     </row>
-    <row r="78" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="37">
         <v>78</v>
       </c>
@@ -11302,7 +11302,7 @@
         <v>Architectural spaces sized and equipped with sanitary parts for male use.</v>
       </c>
     </row>
-    <row r="79" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="37">
         <v>79</v>
       </c>
@@ -11395,7 +11395,7 @@
         <v>Architectural spaces sized and equipped with sanitary parts for male use.</v>
       </c>
     </row>
-    <row r="80" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="37">
         <v>80</v>
       </c>
@@ -11488,7 +11488,7 @@
         <v>Architectural spaces sized and equipped with sanitary parts for common use by women and men.</v>
       </c>
     </row>
-    <row r="81" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="37">
         <v>81</v>
       </c>
@@ -11581,7 +11581,7 @@
         <v>Architectural spaces sized and equipped with sanitary parts for use by people with special needs (PNE).</v>
       </c>
     </row>
-    <row r="82" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="37">
         <v>82</v>
       </c>
@@ -11674,7 +11674,7 @@
         <v>Architectural spaces sized and equipped with sanitary parts of a small bathroom.</v>
       </c>
     </row>
-    <row r="83" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="37">
         <v>83</v>
       </c>
@@ -11767,7 +11767,7 @@
         <v>Architectural spaces sized and equipped for administrative commercial work.</v>
       </c>
     </row>
-    <row r="84" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="37">
         <v>84</v>
       </c>
@@ -11860,7 +11860,7 @@
         <v>Architectural spaces sized and equipped for commercial activities such as buying, selling or exchanging products with public participation. They can be ticket offices or service spaces.</v>
       </c>
     </row>
-    <row r="85" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="37">
         <v>85</v>
       </c>
@@ -11953,7 +11953,7 @@
         <v>Architectural spaces sized and equipped for residential function of Living - Architectural spaces, Balconies, etc.</v>
       </c>
     </row>
-    <row r="86" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="37">
         <v>86</v>
       </c>
@@ -12046,7 +12046,7 @@
         <v>Architectural spaces sized and equipped for intimate residential function - Bedrooms, Dressing rooms, etc.</v>
       </c>
     </row>
-    <row r="87" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="37">
         <v>87</v>
       </c>
@@ -12139,7 +12139,7 @@
         <v>Architectural spaces sized and equipped for residential hygiene function - Bathrooms, toilets, etc.</v>
       </c>
     </row>
-    <row r="88" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="37">
         <v>88</v>
       </c>
@@ -12232,7 +12232,7 @@
         <v>Architectural spaces sized and equipped for residential service function - Areas, Kitchens, etc.</v>
       </c>
     </row>
-    <row r="89" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="37">
         <v>89</v>
       </c>
@@ -12325,7 +12325,7 @@
         <v>Architectural spaces sized and equipped for residential leisure function such as architectural spaces for TV, games, etc.</v>
       </c>
     </row>
-    <row r="90" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="37">
         <v>90</v>
       </c>
@@ -12418,7 +12418,7 @@
         <v>Architectural spaces sized and equipped for residential function of professional activities.</v>
       </c>
     </row>
-    <row r="91" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="37">
         <v>91</v>
       </c>
@@ -12511,7 +12511,7 @@
         <v>Architectural spaces sized and equipped for hospital activity of general health care activities.</v>
       </c>
     </row>
-    <row r="92" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="37">
         <v>92</v>
       </c>
@@ -12604,7 +12604,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out Clinical Analysis activity.</v>
       </c>
     </row>
-    <row r="93" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="37">
         <v>93</v>
       </c>
@@ -12697,7 +12697,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out surgical activity.</v>
       </c>
     </row>
-    <row r="94" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="37">
         <v>94</v>
       </c>
@@ -12790,7 +12790,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out the Inpatient process.</v>
       </c>
     </row>
-    <row r="95" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="37">
         <v>95</v>
       </c>
@@ -12883,7 +12883,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out the Intensive Care Hospitalization process.</v>
       </c>
     </row>
-    <row r="96" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="37">
         <v>96</v>
       </c>
@@ -12976,7 +12976,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to perform Diagnostic Imaging (CT scans, MRIs, Ultrasounds, etc.)</v>
       </c>
     </row>
-    <row r="97" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="37">
         <v>97</v>
       </c>
@@ -13069,7 +13069,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out therapies with patients (physiotherapy, respiratory, etc.).</v>
       </c>
     </row>
-    <row r="98" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="37">
         <v>98</v>
       </c>
@@ -13162,7 +13162,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out Therapeutic activities in Swimming Pool, etc.</v>
       </c>
     </row>
-    <row r="99" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="37">
         <v>99</v>
       </c>
@@ -13255,7 +13255,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to perform Emergency Care.</v>
       </c>
     </row>
-    <row r="100" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="37">
         <v>100</v>
       </c>
@@ -13348,7 +13348,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to perform Patient or Material Screening.</v>
       </c>
     </row>
-    <row r="101" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="37">
         <v>101</v>
       </c>
@@ -13441,7 +13441,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out vehicular movement.</v>
       </c>
     </row>
-    <row r="102" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="37">
         <v>102</v>
       </c>
@@ -13534,7 +13534,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out Waiting activities.</v>
       </c>
     </row>
-    <row r="103" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="37">
         <v>103</v>
       </c>
@@ -13627,7 +13627,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out Medical Consultation activities.</v>
       </c>
     </row>
-    <row r="104" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="37">
         <v>104</v>
       </c>
@@ -13720,7 +13720,7 @@
         <v>Architectural spaces sized and equipped for hospital activity to carry out Nursing activities.</v>
       </c>
     </row>
-    <row r="105" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="37">
         <v>105</v>
       </c>
@@ -13813,7 +13813,7 @@
         <v>Architectural spaces sized and equipped for Low Biohazard Laboratory activity. Basic microbiology practices. No special barriers.</v>
       </c>
     </row>
-    <row r="106" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="37">
         <v>106</v>
       </c>
@@ -13906,7 +13906,7 @@
         <v>Architectural spaces sized and equipped for Moderate Biohazard Laboratory activity. With primary barriers (PPE, sink, decontamination). Restricted access.</v>
       </c>
     </row>
-    <row r="107" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="37">
         <v>107</v>
       </c>
@@ -13999,7 +13999,7 @@
         <v>Architectural spaces sized and equipped for High Biological Risk Laboratory activity. With advanced containment (security cabins, controlled ventilation, water showers). Strict access.</v>
       </c>
     </row>
-    <row r="108" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="37">
         <v>108</v>
       </c>
@@ -14092,7 +14092,7 @@
         <v>Architectural spaces sized and equipped for Very High Biological Risk Laboratory activity. With maximum containment (overalls with filtered air, chemical shower, isolated areas).</v>
       </c>
     </row>
-    <row r="109" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="37">
         <v>109</v>
       </c>
@@ -14185,7 +14185,7 @@
         <v>Architectural spaces sized and equipped for the activity of Vestment of professionals who work in a Biosafety containment environment.</v>
       </c>
     </row>
-    <row r="110" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="37">
         <v>110</v>
       </c>
@@ -14278,7 +14278,7 @@
         <v>Architectural spaces sized and equipped for children's activities.</v>
       </c>
     </row>
-    <row r="111" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="37">
         <v>111</v>
       </c>
@@ -14371,7 +14371,7 @@
         <v>Architectural spaces sized and equipped for Teaching and General Research activities</v>
       </c>
     </row>
-    <row r="112" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="37">
         <v>112</v>
       </c>
@@ -14464,7 +14464,7 @@
         <v>Architectural spaces sized and equipped for Teaching and Artistic Research activities related to plastics, such as painting, sculpture, etc.</v>
       </c>
     </row>
-    <row r="113" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="37">
         <v>113</v>
       </c>
@@ -14557,7 +14557,7 @@
         <v>Architectural spaces sized and equipped for Science Teaching and Research activities.</v>
       </c>
     </row>
-    <row r="114" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="37">
         <v>114</v>
       </c>
@@ -14650,7 +14650,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in technical, graphic, electronic skills, etc.</v>
       </c>
     </row>
-    <row r="115" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="37">
         <v>115</v>
       </c>
@@ -14743,7 +14743,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in Informatics.</v>
       </c>
     </row>
-    <row r="116" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="37">
         <v>116</v>
       </c>
@@ -14836,7 +14836,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in Chemistry.</v>
       </c>
     </row>
-    <row r="117" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="37">
         <v>117</v>
       </c>
@@ -14929,7 +14929,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in Physics.</v>
       </c>
     </row>
-    <row r="118" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="37">
         <v>118</v>
       </c>
@@ -15022,7 +15022,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in Biology.</v>
       </c>
     </row>
-    <row r="119" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="37">
         <v>119</v>
       </c>
@@ -15115,7 +15115,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in Music or Performing Arts.</v>
       </c>
     </row>
-    <row r="120" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="37">
         <v>120</v>
       </c>
@@ -15208,7 +15208,7 @@
         <v>Architectural spaces sized and equipped for Teaching or Research in robotic fabrication, 3D printing, laser cutting and other fabrication technologies.</v>
       </c>
     </row>
-    <row r="121" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="37">
         <v>121</v>
       </c>
@@ -15301,7 +15301,7 @@
         <v>Architectural spaces sized and equipped for recreational school activities.</v>
       </c>
     </row>
-    <row r="122" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="37">
         <v>122</v>
       </c>
@@ -15394,7 +15394,7 @@
         <v>Architectural spaces sized and equipped for the preparation of artists.</v>
       </c>
     </row>
-    <row r="123" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="37">
         <v>123</v>
       </c>
@@ -15487,7 +15487,7 @@
         <v>Front space of the stage, close to the audience. It integrates architecturally to the scene, fulfilling aesthetic and acoustic functions, also called the stage mouth.</v>
       </c>
     </row>
-    <row r="124" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="37">
         <v>124</v>
       </c>
@@ -15580,7 +15580,7 @@
         <v>Space exposed to spectators, where the actors perform. It can be elevated, flat, rotating, Italian, arena, among other formats.</v>
       </c>
     </row>
-    <row r="125" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="37">
         <v>125</v>
       </c>
@@ -15673,7 +15673,7 @@
         <v>Hidden space and back to the stage, behind the artists' performance area. It can house various scenographic, technical and functional elements to the play.</v>
       </c>
     </row>
-    <row r="126" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="37">
         <v>126</v>
       </c>
@@ -15766,7 +15766,7 @@
         <v>Space lateral to the stage, used for the entry and exit of the artists.</v>
       </c>
     </row>
-    <row r="127" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="37">
         <v>127</v>
       </c>
@@ -15859,7 +15859,7 @@
         <v>Space between the audience and the stage, usually below the stage, to accommodate the orchestra during a musical or dance performance.</v>
       </c>
     </row>
-    <row r="128" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="37">
         <v>128</v>
       </c>
@@ -15952,7 +15952,7 @@
         <v>Space at stage level, where the audience sits with a view of the front of the stage.</v>
       </c>
     </row>
-    <row r="129" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="37">
         <v>129</v>
       </c>
@@ -16045,7 +16045,7 @@
         <v>Space integrated to the audience, but at an upper level where the audience is accommodated with a frontal view of the stage.</v>
       </c>
     </row>
-    <row r="130" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="37">
         <v>130</v>
       </c>
@@ -16138,7 +16138,7 @@
         <v>Space integrated into the concert hall, usually reserved and with better visibility and comfort.</v>
       </c>
     </row>
-    <row r="131" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="37">
         <v>131</v>
       </c>
@@ -16231,7 +16231,7 @@
         <v>Superior space to accommodate the public with more affordable prices.</v>
       </c>
     </row>
-    <row r="132" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="37">
         <v>132</v>
       </c>
@@ -16324,7 +16324,7 @@
         <v>Industrial Space type Large Industrial Building.</v>
       </c>
     </row>
-    <row r="133" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A133" s="37">
         <v>133</v>
       </c>
@@ -16417,7 +16417,7 @@
         <v>Industrial Space type Shed.</v>
       </c>
     </row>
-    <row r="134" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A134" s="37">
         <v>134</v>
       </c>
@@ -16510,7 +16510,7 @@
         <v>Industrial space sized and equipped with furnaces or heavy equipment for processing metals and alloys.</v>
       </c>
     </row>
-    <row r="135" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A135" s="37">
         <v>135</v>
       </c>
@@ -16603,7 +16603,7 @@
         <v>Industrial space sized and equipped as a Production Line of large-scale goods (automobiles, electronics, textiles and food, etc.). It is an assembly line of automated machines</v>
       </c>
     </row>
-    <row r="136" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A136" s="37">
         <v>136</v>
       </c>
@@ -16696,7 +16696,7 @@
         <v>Industrial space sized and equipped as a Production Workshop for medium or low scale goods (furniture, equipment, small vehicles, etc.). It is prepared for assembly.</v>
       </c>
     </row>
-    <row r="137" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A137" s="37">
         <v>137</v>
       </c>
@@ -16789,7 +16789,7 @@
         <v>Industrial space sized and equipped as a Painting Workshop of medium or low scale goods (furniture, equipment, small vehicles, etc.). It is prepared for assembly.</v>
       </c>
     </row>
-    <row r="138" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A138" s="37">
         <v>138</v>
       </c>
@@ -16882,7 +16882,7 @@
         <v>It represents a Housing Unit of Social Interest.</v>
       </c>
     </row>
-    <row r="139" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A139" s="37">
         <v>139</v>
       </c>
@@ -16975,7 +16975,7 @@
         <v>Represents an Apartment of residential building.</v>
       </c>
     </row>
-    <row r="140" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A140" s="37">
         <v>140</v>
       </c>
@@ -17068,7 +17068,7 @@
         <v>Represents an administrative functional department of an institutional building.</v>
       </c>
     </row>
-    <row r="141" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A141" s="37">
         <v>141</v>
       </c>
@@ -17161,7 +17161,7 @@
         <v>It represents an administrative functional division of an institutional building.</v>
       </c>
     </row>
-    <row r="142" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A142" s="37">
         <v>142</v>
       </c>
@@ -17254,7 +17254,7 @@
         <v>It represents an administrative functional sector of an institutional building.</v>
       </c>
     </row>
-    <row r="143" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A143" s="37">
         <v>143</v>
       </c>
@@ -17347,7 +17347,7 @@
         <v>It represents a Built Block that contains other autonomous units without a specific function.</v>
       </c>
     </row>
-    <row r="144" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A144" s="37">
         <v>144</v>
       </c>
@@ -17440,7 +17440,7 @@
         <v>It represents a Built Block that is a House or Individual Residential Unit.</v>
       </c>
     </row>
-    <row r="145" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A145" s="37">
         <v>145</v>
       </c>
@@ -17533,7 +17533,7 @@
         <v>It represents a Built Block that contains other autonomous units with a residential function.</v>
       </c>
     </row>
-    <row r="146" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A146" s="37">
         <v>146</v>
       </c>
@@ -17626,7 +17626,7 @@
         <v>It represents a Built Block of an Educational Unit.</v>
       </c>
     </row>
-    <row r="147" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A147" s="37">
         <v>147</v>
       </c>
@@ -17719,7 +17719,7 @@
         <v>It represents a Built Block of a SUS Health Unit.</v>
       </c>
     </row>
-    <row r="148" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A148" s="37">
         <v>148</v>
       </c>
@@ -17812,7 +17812,7 @@
         <v>It represents a Built Block of a Health Unit of the Private Network.</v>
       </c>
     </row>
-    <row r="149" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A149" s="37">
         <v>149</v>
       </c>
@@ -17905,7 +17905,7 @@
         <v>It represents a Built Block of a Health Unit of the Private Network contracted with the SUS.</v>
       </c>
     </row>
-    <row r="150" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A150" s="37">
         <v>150</v>
       </c>
@@ -17998,7 +17998,7 @@
         <v>Spatial zone is a non-hierarchical and potentially overlapping decomposition of the project under some condition.</v>
       </c>
     </row>
-    <row r="151" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A151" s="37">
         <v>151</v>
       </c>
@@ -18091,7 +18091,7 @@
         <v>Space zone is used to represent a construction zone for the manufacturing process.</v>
       </c>
     </row>
-    <row r="152" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A152" s="37">
         <v>152</v>
       </c>
@@ -18184,7 +18184,7 @@
         <v>Spatial zone is used to define an interference between occurrences of Ifcspatialelement.</v>
       </c>
     </row>
-    <row r="153" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A153" s="37">
         <v>153</v>
       </c>
@@ -18277,7 +18277,7 @@
         <v>Spatial zone is used to represent a particular zone of occupation.</v>
       </c>
     </row>
-    <row r="154" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A154" s="37">
         <v>154</v>
       </c>
@@ -18370,7 +18370,7 @@
         <v>A spatial zone that represents some type of reserve within the project for future use.</v>
       </c>
     </row>
-    <row r="155" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A155" s="37">
         <v>155</v>
       </c>
@@ -18463,7 +18463,7 @@
         <v>Spatial zone is used to represent an area primarily dedicated to the circulation of people or vehicles.</v>
       </c>
     </row>
-    <row r="156" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A156" s="37">
         <v>156</v>
       </c>
@@ -18556,7 +18556,7 @@
         <v>Space zone is used to represent a thermal zone with homogeneous characteristics.</v>
       </c>
     </row>
-    <row r="157" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A157" s="37">
         <v>157</v>
       </c>
@@ -18649,7 +18649,7 @@
         <v>Spatial zone is used to represent a lighting zone; a zone of natural light.</v>
       </c>
     </row>
-    <row r="158" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A158" s="37">
         <v>158</v>
       </c>
@@ -18742,7 +18742,7 @@
         <v>Spatial zone is used to represent a ventilation zone.</v>
       </c>
     </row>
-    <row r="159" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A159" s="37">
         <v>159</v>
       </c>
@@ -18835,7 +18835,7 @@
         <v>Spatial zone is used to represent a zone for planning safety and work, accesses, etc.</v>
       </c>
     </row>
-    <row r="160" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A160" s="37">
         <v>160</v>
       </c>
@@ -18928,7 +18928,7 @@
         <v>Space zone is used to represent a fire safety zone, or compartment.</v>
       </c>
     </row>
-    <row r="161" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A161" s="37">
         <v>161</v>
       </c>
@@ -19021,7 +19021,7 @@
         <v>Space zone is used to represent a biosecurity zone, typically where ventilation is critical.</v>
       </c>
     </row>
-    <row r="162" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A162" s="37">
         <v>162</v>
       </c>
@@ -19114,7 +19114,7 @@
         <v>Solar Heliodom or Analema: sun.</v>
       </c>
     </row>
-    <row r="163" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A163" s="37">
         <v>163</v>
       </c>
@@ -19207,7 +19207,7 @@
         <v>Heliodom Solar Analemma: Solar Path 1.</v>
       </c>
     </row>
-    <row r="164" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A164" s="37">
         <v>164</v>
       </c>
@@ -19300,7 +19300,7 @@
         <v>Heliodom Solar Analemma: Solar Path 1.</v>
       </c>
     </row>
-    <row r="165" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A165" s="37">
         <v>165</v>
       </c>
@@ -19393,7 +19393,7 @@
         <v>Heliodom Dawn: Text from the exit of the sun.</v>
       </c>
     </row>
-    <row r="166" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A166" s="37">
         <v>166</v>
       </c>
@@ -19486,7 +19486,7 @@
         <v>Heliodom Nightfall: text from posta do sol.</v>
       </c>
     </row>
-    <row r="167" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A167" s="37">
         <v>167</v>
       </c>
@@ -19579,7 +19579,7 @@
         <v>Solar Study Heliodom.</v>
       </c>
     </row>
-    <row r="168" spans="1:27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:27" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="37">
         <v>168</v>
       </c>
@@ -19672,7 +19672,7 @@
         <v>Heliodom Surface of the sun.</v>
       </c>
     </row>
-    <row r="169" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A169" s="37">
         <v>169</v>
       </c>
@@ -19765,7 +19765,7 @@
         <v>Envelope orientation analysis. North-oriented elements, relative to True or Solar North.</v>
       </c>
     </row>
-    <row r="170" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A170" s="37">
         <v>170</v>
       </c>
@@ -19858,7 +19858,7 @@
         <v>Orientation analysis of the Envelope. South-oriented elements, relative to True or Solar North.</v>
       </c>
     </row>
-    <row r="171" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A171" s="37">
         <v>171</v>
       </c>
@@ -19951,7 +19951,7 @@
         <v>Envelope orientation analysis. East-facing elements, relative to True North or Solar.</v>
       </c>
     </row>
-    <row r="172" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A172" s="37">
         <v>172</v>
       </c>
@@ -20044,7 +20044,7 @@
         <v>Orientation analysis of the Envelope. Elements oriented to the West, relative to True or Solar North.</v>
       </c>
     </row>
-    <row r="173" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A173" s="37">
         <v>173</v>
       </c>
@@ -20259,15 +20259,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="10" width="6" style="12" bestFit="1" customWidth="1"/>
     <col min="11" max="21" width="6" style="10" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="10"/>
+    <col min="22" max="16384" width="11.15234375" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
@@ -20332,7 +20332,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -20397,7 +20397,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>3</v>
       </c>
@@ -20472,16 +20472,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B299E44-CC41-4C47-93B0-FF411236635D}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="8.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.15234375" customWidth="1"/>
+    <col min="3" max="3" width="10.69140625" customWidth="1"/>
+    <col min="4" max="4" width="8.3046875" customWidth="1"/>
+    <col min="5" max="5" width="9.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="15">
         <v>1</v>
       </c>
@@ -20498,7 +20498,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="28">
         <v>2</v>
       </c>
@@ -20515,7 +20515,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="28">
         <v>3</v>
       </c>
@@ -20532,7 +20532,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="28">
         <v>4</v>
       </c>
@@ -20563,43 +20563,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F4F343-F8A9-4565-8E75-460BD2B52D7E}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AE46"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="64" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" style="52" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="50" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.85546875" style="50" customWidth="1"/>
-    <col min="5" max="5" width="7.85546875" style="50" customWidth="1"/>
-    <col min="6" max="6" width="5.85546875" style="50" customWidth="1"/>
-    <col min="7" max="7" width="5.140625" style="50" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" style="50" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.140625" style="50" customWidth="1"/>
-    <col min="10" max="10" width="8.42578125" style="50" customWidth="1"/>
-    <col min="11" max="11" width="4.7109375" style="50" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" style="50" customWidth="1"/>
-    <col min="13" max="13" width="5.85546875" style="50" customWidth="1"/>
-    <col min="14" max="14" width="8.7109375" style="50" customWidth="1"/>
-    <col min="15" max="15" width="19.85546875" style="50" customWidth="1"/>
-    <col min="16" max="16" width="4.5703125" style="50" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="64" customWidth="1"/>
+    <col min="2" max="2" width="9.3046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3828125" style="50" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.84375" style="50" customWidth="1"/>
+    <col min="5" max="5" width="7.84375" style="50" customWidth="1"/>
+    <col min="6" max="6" width="5.84375" style="50" customWidth="1"/>
+    <col min="7" max="7" width="5.15234375" style="50" customWidth="1"/>
+    <col min="8" max="8" width="7.53515625" style="50" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.15234375" style="50" customWidth="1"/>
+    <col min="10" max="10" width="8.3828125" style="50" customWidth="1"/>
+    <col min="11" max="11" width="4.69140625" style="50" customWidth="1"/>
+    <col min="12" max="12" width="4.3046875" style="50" customWidth="1"/>
+    <col min="13" max="13" width="5.84375" style="50" customWidth="1"/>
+    <col min="14" max="14" width="8.69140625" style="50" customWidth="1"/>
+    <col min="15" max="15" width="19.84375" style="50" customWidth="1"/>
+    <col min="16" max="16" width="4.53515625" style="50" customWidth="1"/>
     <col min="17" max="17" width="28" style="50" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.7109375" style="50" customWidth="1"/>
-    <col min="19" max="19" width="15.7109375" style="50" customWidth="1"/>
-    <col min="20" max="20" width="4.28515625" style="50" customWidth="1"/>
-    <col min="21" max="21" width="25.42578125" style="50" customWidth="1"/>
-    <col min="22" max="22" width="4.5703125" style="50" customWidth="1"/>
+    <col min="18" max="18" width="6.69140625" style="50" customWidth="1"/>
+    <col min="19" max="19" width="15.69140625" style="50" customWidth="1"/>
+    <col min="20" max="20" width="4.3046875" style="50" customWidth="1"/>
+    <col min="21" max="21" width="25.3828125" style="50" customWidth="1"/>
+    <col min="22" max="22" width="4.53515625" style="50" customWidth="1"/>
     <col min="23" max="23" width="11" style="50" customWidth="1"/>
-    <col min="24" max="24" width="9.140625" style="50" customWidth="1"/>
-    <col min="25" max="25" width="12.7109375" style="50" customWidth="1"/>
-    <col min="26" max="26" width="2.42578125" style="50" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.15234375" style="50" customWidth="1"/>
+    <col min="25" max="25" width="12.69140625" style="50" customWidth="1"/>
+    <col min="26" max="26" width="2.3828125" style="50" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="14" style="50" customWidth="1"/>
     <col min="28" max="28" width="5" style="50" customWidth="1"/>
-    <col min="29" max="29" width="9.28515625" style="50" customWidth="1"/>
-    <col min="30" max="30" width="10.5703125" style="50" customWidth="1"/>
-    <col min="31" max="31" width="7.5703125" style="50" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.28515625" style="50"/>
+    <col min="29" max="29" width="9.3046875" style="50" customWidth="1"/>
+    <col min="30" max="30" width="10.53515625" style="50" customWidth="1"/>
+    <col min="31" max="31" width="7.53515625" style="50" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.3046875" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="20.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="62" t="s">
         <v>11</v>
       </c>
@@ -20694,7 +20694,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="63">
         <v>1</v>
       </c>
@@ -20789,7 +20789,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="63">
         <v>2</v>
       </c>
@@ -20884,7 +20884,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="63">
         <v>3</v>
       </c>
@@ -20979,7 +20979,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="63">
         <v>4</v>
       </c>
@@ -21074,7 +21074,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="63">
         <v>5</v>
       </c>
@@ -21169,7 +21169,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="63">
         <v>6</v>
       </c>
@@ -21264,7 +21264,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="63">
         <v>7</v>
       </c>
@@ -21359,7 +21359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="63">
         <v>8</v>
       </c>
@@ -21454,7 +21454,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="63">
         <v>9</v>
       </c>
@@ -21549,7 +21549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="63">
         <v>10</v>
       </c>
@@ -21644,7 +21644,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="63">
         <v>11</v>
       </c>
@@ -21739,7 +21739,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="63">
         <v>12</v>
       </c>
@@ -21834,7 +21834,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="63">
         <v>13</v>
       </c>
@@ -21929,7 +21929,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="63">
         <v>14</v>
       </c>
@@ -22024,7 +22024,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="63">
         <v>15</v>
       </c>
@@ -22119,7 +22119,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="63">
         <v>16</v>
       </c>
@@ -22214,7 +22214,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="63">
         <v>17</v>
       </c>
@@ -22309,7 +22309,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="63">
         <v>18</v>
       </c>
@@ -22404,7 +22404,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="63">
         <v>19</v>
       </c>
@@ -22499,7 +22499,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="63">
         <v>20</v>
       </c>
@@ -22594,7 +22594,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="63">
         <v>21</v>
       </c>
@@ -22689,7 +22689,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="63">
         <v>22</v>
       </c>
@@ -22784,7 +22784,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="63">
         <v>23</v>
       </c>
@@ -22879,7 +22879,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="63">
         <v>24</v>
       </c>
@@ -22974,7 +22974,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="63">
         <v>25</v>
       </c>
@@ -23069,7 +23069,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="63">
         <v>26</v>
       </c>
@@ -23164,7 +23164,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="63">
         <v>27</v>
       </c>
@@ -23259,7 +23259,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="63">
         <v>28</v>
       </c>
@@ -23354,7 +23354,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="63">
         <v>29</v>
       </c>
@@ -23449,7 +23449,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="63">
         <v>30</v>
       </c>
@@ -23544,7 +23544,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="63">
         <v>31</v>
       </c>
@@ -23639,7 +23639,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="63">
         <v>32</v>
       </c>
@@ -23734,7 +23734,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="63">
         <v>33</v>
       </c>
@@ -23829,7 +23829,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="63">
         <v>34</v>
       </c>
@@ -23924,7 +23924,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="63">
         <v>35</v>
       </c>
@@ -24019,7 +24019,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="63">
         <v>36</v>
       </c>
@@ -24114,7 +24114,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="63">
         <v>37</v>
       </c>
@@ -24209,7 +24209,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="63">
         <v>38</v>
       </c>
@@ -24304,7 +24304,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="63">
         <v>39</v>
       </c>
@@ -24399,7 +24399,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="63">
         <v>40</v>
       </c>
@@ -24494,7 +24494,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="63">
         <v>41</v>
       </c>
@@ -24589,7 +24589,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="63">
         <v>42</v>
       </c>
@@ -24684,7 +24684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="63">
         <v>43</v>
       </c>
@@ -24779,7 +24779,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="63">
         <v>44</v>
       </c>
@@ -24874,7 +24874,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:31" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="63">
         <v>45</v>
       </c>
